--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_air_transport.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_air_transport.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.112</v>
+        <v>-0.0599</v>
       </c>
       <c r="G2">
-        <v>-0.1778160354156419</v>
+        <v>-0.0292271479011377</v>
       </c>
       <c r="H2">
-        <v>-0.1778160354156419</v>
+        <v>-0.0292271479011377</v>
       </c>
       <c r="I2">
-        <v>-0.1350221347761928</v>
+        <v>-0.06355433503334641</v>
       </c>
       <c r="J2">
-        <v>-0.1350221347761928</v>
+        <v>-0.06355433503334641</v>
       </c>
       <c r="K2">
-        <v>-72.40000000000001</v>
+        <v>-63.3</v>
       </c>
       <c r="L2">
-        <v>-0.1780619773733399</v>
+        <v>-0.1241663397410749</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>36.4</v>
+        <v>17.8</v>
       </c>
       <c r="V2">
-        <v>0.02459958099614786</v>
+        <v>0.01629141497345781</v>
       </c>
       <c r="W2">
-        <v>-0.1040678453356332</v>
+        <v>-0.101215222257755</v>
       </c>
       <c r="X2">
-        <v>0.0680602409249294</v>
+        <v>0.1023467458329613</v>
       </c>
       <c r="Y2">
-        <v>-0.1721280862605626</v>
+        <v>-0.2035619680907163</v>
       </c>
       <c r="Z2">
-        <v>0.801340165549862</v>
+        <v>0.6366928937179968</v>
       </c>
       <c r="AA2">
-        <v>-0.1081986598344501</v>
+        <v>-0.04046459348070438</v>
       </c>
       <c r="AB2">
-        <v>0.05919612323832309</v>
+        <v>0.0927285126939517</v>
       </c>
       <c r="AC2">
-        <v>-0.1673947830727732</v>
+        <v>-0.1331931061746561</v>
       </c>
       <c r="AD2">
-        <v>367.1</v>
+        <v>219</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>367.1</v>
+        <v>219</v>
       </c>
       <c r="AG2">
-        <v>330.7</v>
+        <v>201.2</v>
       </c>
       <c r="AH2">
-        <v>0.1987762616417587</v>
+        <v>0.166971637694419</v>
       </c>
       <c r="AI2">
-        <v>0.3698740554156171</v>
+        <v>0.2788388082505729</v>
       </c>
       <c r="AJ2">
-        <v>0.1826668139637649</v>
+        <v>0.1555108981295409</v>
       </c>
       <c r="AK2">
-        <v>0.3458843217236691</v>
+        <v>0.2621156852527358</v>
       </c>
       <c r="AL2">
-        <v>6.77</v>
+        <v>7.58</v>
       </c>
       <c r="AM2">
-        <v>6.77</v>
+        <v>7.58</v>
       </c>
       <c r="AN2">
-        <v>-14.5098814229249</v>
+        <v>-91.63179916317991</v>
       </c>
       <c r="AO2">
-        <v>-8.109305760709011</v>
+        <v>-4.274406332453825</v>
       </c>
       <c r="AP2">
-        <v>-13.07114624505929</v>
+        <v>-84.18410041841003</v>
       </c>
       <c r="AQ2">
-        <v>-8.109305760709011</v>
+        <v>-4.274406332453825</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.112</v>
+        <v>-0.0599</v>
       </c>
       <c r="G3">
-        <v>-0.1778160354156419</v>
+        <v>-0.0292271479011377</v>
       </c>
       <c r="H3">
-        <v>-0.1778160354156419</v>
+        <v>-0.0292271479011377</v>
       </c>
       <c r="I3">
-        <v>-0.1350221347761928</v>
+        <v>-0.06355433503334641</v>
       </c>
       <c r="J3">
-        <v>-0.1350221347761928</v>
+        <v>-0.06355433503334641</v>
       </c>
       <c r="K3">
-        <v>-72.40000000000001</v>
+        <v>-63.3</v>
       </c>
       <c r="L3">
-        <v>-0.1780619773733399</v>
+        <v>-0.1241663397410749</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>36.4</v>
+        <v>17.8</v>
       </c>
       <c r="V3">
-        <v>0.02459958099614786</v>
+        <v>0.01629141497345781</v>
       </c>
       <c r="W3">
-        <v>-0.1040678453356332</v>
+        <v>-0.101215222257755</v>
       </c>
       <c r="X3">
-        <v>0.0680602409249294</v>
+        <v>0.1023467458329613</v>
       </c>
       <c r="Y3">
-        <v>-0.1721280862605626</v>
+        <v>-0.2035619680907163</v>
       </c>
       <c r="Z3">
-        <v>0.801340165549862</v>
+        <v>0.6366928937179968</v>
       </c>
       <c r="AA3">
-        <v>-0.1081986598344501</v>
+        <v>-0.04046459348070438</v>
       </c>
       <c r="AB3">
-        <v>0.05919612323832309</v>
+        <v>0.0927285126939517</v>
       </c>
       <c r="AC3">
-        <v>-0.1673947830727732</v>
+        <v>-0.1331931061746561</v>
       </c>
       <c r="AD3">
-        <v>367.1</v>
+        <v>219</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>367.1</v>
+        <v>219</v>
       </c>
       <c r="AG3">
-        <v>330.7</v>
+        <v>201.2</v>
       </c>
       <c r="AH3">
-        <v>0.1987762616417587</v>
+        <v>0.166971637694419</v>
       </c>
       <c r="AI3">
-        <v>0.3698740554156171</v>
+        <v>0.2788388082505729</v>
       </c>
       <c r="AJ3">
-        <v>0.1826668139637649</v>
+        <v>0.1555108981295409</v>
       </c>
       <c r="AK3">
-        <v>0.3458843217236691</v>
+        <v>0.2621156852527358</v>
       </c>
       <c r="AL3">
-        <v>6.77</v>
+        <v>7.58</v>
       </c>
       <c r="AM3">
-        <v>6.77</v>
+        <v>7.58</v>
       </c>
       <c r="AN3">
-        <v>-14.5098814229249</v>
+        <v>-91.63179916317991</v>
       </c>
       <c r="AO3">
-        <v>-8.109305760709011</v>
+        <v>-4.274406332453825</v>
       </c>
       <c r="AP3">
-        <v>-13.07114624505929</v>
+        <v>-84.18410041841003</v>
       </c>
       <c r="AQ3">
-        <v>-8.109305760709011</v>
+        <v>-4.274406332453825</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_air_transport.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sase_4031" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0599</v>
+        <v>-0.0185</v>
+      </c>
+      <c r="E2">
+        <v>-0.355</v>
       </c>
       <c r="G2">
-        <v>-0.0292271479011377</v>
+        <v>0.0007409783480352847</v>
       </c>
       <c r="H2">
-        <v>-0.0292271479011377</v>
+        <v>0.0007409783480352847</v>
       </c>
       <c r="I2">
-        <v>-0.06355433503334641</v>
+        <v>0.03977546110665597</v>
       </c>
       <c r="J2">
-        <v>-0.06355433503334641</v>
+        <v>0.01988773055332799</v>
       </c>
       <c r="K2">
-        <v>-63.3</v>
+        <v>11.2</v>
       </c>
       <c r="L2">
-        <v>-0.1241663397410749</v>
+        <v>0.01796311146752205</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="V2">
-        <v>0.01629141497345781</v>
+        <v>0.01038575667655786</v>
       </c>
       <c r="W2">
-        <v>-0.101215222257755</v>
+        <v>0.01977401129943503</v>
       </c>
       <c r="X2">
-        <v>0.1023467458329613</v>
+        <v>0.08642773031522552</v>
       </c>
       <c r="Y2">
-        <v>-0.2035619680907163</v>
+        <v>-0.06665371901579049</v>
       </c>
       <c r="Z2">
-        <v>0.6366928937179968</v>
+        <v>1.017959183673469</v>
       </c>
       <c r="AA2">
-        <v>-0.04046459348070438</v>
+        <v>0.02024489795918367</v>
       </c>
       <c r="AB2">
-        <v>0.0927285126939517</v>
+        <v>0.08374407556083592</v>
       </c>
       <c r="AC2">
-        <v>-0.1331931061746561</v>
+        <v>-0.06349917760165225</v>
       </c>
       <c r="AD2">
-        <v>219</v>
+        <v>117.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>219</v>
+        <v>117.5</v>
       </c>
       <c r="AG2">
-        <v>201.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.166971637694419</v>
+        <v>0.06065142208227946</v>
       </c>
       <c r="AI2">
-        <v>0.2788388082505729</v>
+        <v>0.1636718205878256</v>
       </c>
       <c r="AJ2">
-        <v>0.1555108981295409</v>
+        <v>0.05139699749791493</v>
       </c>
       <c r="AK2">
-        <v>0.2621156852527358</v>
+        <v>0.1410586552217453</v>
       </c>
       <c r="AL2">
-        <v>7.58</v>
+        <v>9.24</v>
       </c>
       <c r="AM2">
-        <v>7.58</v>
+        <v>-1.26</v>
       </c>
       <c r="AN2">
-        <v>-91.63179916317991</v>
+        <v>2.144160583941606</v>
       </c>
       <c r="AO2">
-        <v>-4.274406332453825</v>
+        <v>2.683982683982684</v>
       </c>
       <c r="AP2">
-        <v>-84.18410041841003</v>
+        <v>1.799270072992701</v>
       </c>
       <c r="AQ2">
-        <v>-4.274406332453825</v>
+        <v>-19.68253968253969</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0599</v>
+        <v>-0.0185</v>
+      </c>
+      <c r="E3">
+        <v>-0.355</v>
       </c>
       <c r="G3">
-        <v>-0.0292271479011377</v>
+        <v>0.0007409783480352847</v>
       </c>
       <c r="H3">
-        <v>-0.0292271479011377</v>
+        <v>0.0007409783480352847</v>
       </c>
       <c r="I3">
-        <v>-0.06355433503334641</v>
+        <v>0.03977546110665597</v>
       </c>
       <c r="J3">
-        <v>-0.06355433503334641</v>
+        <v>0.01988773055332799</v>
       </c>
       <c r="K3">
-        <v>-63.3</v>
+        <v>11.2</v>
       </c>
       <c r="L3">
-        <v>-0.1241663397410749</v>
+        <v>0.01796311146752205</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="V3">
-        <v>0.01629141497345781</v>
+        <v>0.01038575667655786</v>
       </c>
       <c r="W3">
-        <v>-0.101215222257755</v>
+        <v>0.01977401129943503</v>
       </c>
       <c r="X3">
-        <v>0.1023467458329613</v>
+        <v>0.08642773031522552</v>
       </c>
       <c r="Y3">
-        <v>-0.2035619680907163</v>
+        <v>-0.06665371901579049</v>
       </c>
       <c r="Z3">
-        <v>0.6366928937179968</v>
+        <v>1.017959183673469</v>
       </c>
       <c r="AA3">
-        <v>-0.04046459348070438</v>
+        <v>0.02024489795918367</v>
       </c>
       <c r="AB3">
-        <v>0.0927285126939517</v>
+        <v>0.08374407556083592</v>
       </c>
       <c r="AC3">
-        <v>-0.1331931061746561</v>
+        <v>-0.06349917760165225</v>
       </c>
       <c r="AD3">
-        <v>219</v>
+        <v>117.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>219</v>
+        <v>117.5</v>
       </c>
       <c r="AG3">
-        <v>201.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.166971637694419</v>
+        <v>0.06065142208227946</v>
       </c>
       <c r="AI3">
-        <v>0.2788388082505729</v>
+        <v>0.1636718205878256</v>
       </c>
       <c r="AJ3">
-        <v>0.1555108981295409</v>
+        <v>0.05139699749791493</v>
       </c>
       <c r="AK3">
-        <v>0.2621156852527358</v>
+        <v>0.1410586552217453</v>
       </c>
       <c r="AL3">
-        <v>7.58</v>
+        <v>9.24</v>
       </c>
       <c r="AM3">
-        <v>7.58</v>
+        <v>-1.26</v>
       </c>
       <c r="AN3">
-        <v>-91.63179916317991</v>
+        <v>2.144160583941606</v>
       </c>
       <c r="AO3">
-        <v>-4.274406332453825</v>
+        <v>2.683982683982684</v>
       </c>
       <c r="AP3">
-        <v>-84.18410041841003</v>
+        <v>1.799270072992701</v>
       </c>
       <c r="AQ3">
-        <v>-4.274406332453825</v>
+        <v>-19.68253968253969</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Saudi Ground Services Company (SASE:4031)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SASE:4031</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2.68398268398268</v>
+      </c>
+      <c r="F2">
+        <v>4.88040745342925</v>
+      </c>
+      <c r="G2">
+        <v>2.14416058394161</v>
+      </c>
+      <c r="H2">
+        <v>2.82817518248175</v>
+      </c>
+      <c r="I2">
+        <v>0.0606514220822795</v>
+      </c>
+      <c r="J2">
+        <v>0.08</v>
+      </c>
+      <c r="K2">
+        <v>1819.8</v>
+      </c>
+      <c r="L2">
+        <v>1792.04103958806</v>
+      </c>
+      <c r="M2">
+        <v>1918.4</v>
+      </c>
+      <c r="N2">
+        <v>1928.12503958806</v>
+      </c>
+      <c r="O2">
+        <v>117.5</v>
+      </c>
+      <c r="P2">
+        <v>154.984</v>
+      </c>
+      <c r="Q2">
+        <v>0.08374407556083591</v>
+      </c>
+      <c r="R2">
+        <v>0.08351738750632511</v>
+      </c>
+      <c r="S2">
+        <v>0.0421805443094471</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.08642773031522551</v>
+      </c>
+      <c r="X2">
+        <v>0.0872388994633969</v>
+      </c>
+      <c r="Y2">
+        <v>0.845759921129815</v>
+      </c>
+      <c r="Z2">
+        <v>0.860164436109632</v>
+      </c>
+      <c r="AA2">
+        <v>117.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.05272568038680883</v>
+      </c>
+      <c r="AC2">
+        <v>2.683982683982684</v>
+      </c>
+      <c r="AD2">
+        <v>117.5</v>
+      </c>
+      <c r="AE2">
+        <v>9.24</v>
+      </c>
+      <c r="AF2">
+        <v>30</v>
+      </c>
+      <c r="AG2">
+        <v>54.8</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>1819.8</v>
+      </c>
+      <c r="AK2">
+        <v>0.05631353428476683</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>59.69999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>9.24</v>
+      </c>
+      <c r="AS2">
+        <v>117.5</v>
+      </c>
+      <c r="AT2">
+        <v>18.9</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08408840193732228</v>
+      </c>
+      <c r="C2">
+        <v>1922.714461707754</v>
+      </c>
+      <c r="D2">
+        <v>1903.814461707754</v>
+      </c>
+      <c r="E2">
+        <v>-117.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>18.9</v>
+      </c>
+      <c r="H2">
+        <v>1819.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K2">
+        <v>30</v>
+      </c>
+      <c r="L2">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="O2">
+        <v>7.699999999999998</v>
+      </c>
+      <c r="P2">
+        <v>30.79999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>60.79999999999998</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08408840193732228</v>
+      </c>
+      <c r="T2">
+        <v>0.8042187817285175</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08396742513344764</v>
+      </c>
+      <c r="C3">
+        <v>1908.440654058596</v>
+      </c>
+      <c r="D3">
+        <v>1908.913654058596</v>
+      </c>
+      <c r="E3">
+        <v>-98.127</v>
+      </c>
+      <c r="F3">
+        <v>19.373</v>
+      </c>
+      <c r="G3">
+        <v>18.9</v>
+      </c>
+      <c r="H3">
+        <v>1819.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K3">
+        <v>30</v>
+      </c>
+      <c r="L3">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.8659731000000002</v>
+      </c>
+      <c r="N3">
+        <v>37.63402689999999</v>
+      </c>
+      <c r="O3">
+        <v>7.526805379999998</v>
+      </c>
+      <c r="P3">
+        <v>30.10722151999999</v>
+      </c>
+      <c r="Q3">
+        <v>60.10722151999998</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08445436882166428</v>
+      </c>
+      <c r="T3">
+        <v>0.8107175193586469</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>44.4586558173689</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.083846448329573</v>
+      </c>
+      <c r="C4">
+        <v>1894.194235205485</v>
+      </c>
+      <c r="D4">
+        <v>1914.040235205485</v>
+      </c>
+      <c r="E4">
+        <v>-78.75399999999999</v>
+      </c>
+      <c r="F4">
+        <v>38.746</v>
+      </c>
+      <c r="G4">
+        <v>18.9</v>
+      </c>
+      <c r="H4">
+        <v>1819.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K4">
+        <v>30</v>
+      </c>
+      <c r="L4">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M4">
+        <v>1.7319462</v>
+      </c>
+      <c r="N4">
+        <v>36.76805379999998</v>
+      </c>
+      <c r="O4">
+        <v>7.353610759999997</v>
+      </c>
+      <c r="P4">
+        <v>29.41444303999999</v>
+      </c>
+      <c r="Q4">
+        <v>59.41444303999998</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08482780441793163</v>
+      </c>
+      <c r="T4">
+        <v>0.8173488842873504</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>22.22932790868445</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08372547152569836</v>
+      </c>
+      <c r="C5">
+        <v>1879.975426408802</v>
+      </c>
+      <c r="D5">
+        <v>1919.194426408802</v>
+      </c>
+      <c r="E5">
+        <v>-59.381</v>
+      </c>
+      <c r="F5">
+        <v>58.119</v>
+      </c>
+      <c r="G5">
+        <v>18.9</v>
+      </c>
+      <c r="H5">
+        <v>1819.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K5">
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M5">
+        <v>2.5979193</v>
+      </c>
+      <c r="N5">
+        <v>35.90208069999998</v>
+      </c>
+      <c r="O5">
+        <v>7.180416139999998</v>
+      </c>
+      <c r="P5">
+        <v>28.72166455999999</v>
+      </c>
+      <c r="Q5">
+        <v>58.72166455999998</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0852089397172148</v>
+      </c>
+      <c r="T5">
+        <v>0.8241169783898415</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>14.81955193912297</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08363969472182371</v>
+      </c>
+      <c r="C6">
+        <v>1864.273779769539</v>
+      </c>
+      <c r="D6">
+        <v>1922.865779769539</v>
+      </c>
+      <c r="E6">
+        <v>-40.008</v>
+      </c>
+      <c r="F6">
+        <v>77.492</v>
+      </c>
+      <c r="G6">
+        <v>18.9</v>
+      </c>
+      <c r="H6">
+        <v>1819.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K6">
+        <v>30</v>
+      </c>
+      <c r="L6">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M6">
+        <v>3.5491336</v>
+      </c>
+      <c r="N6">
+        <v>34.95086639999999</v>
+      </c>
+      <c r="O6">
+        <v>6.990173279999998</v>
+      </c>
+      <c r="P6">
+        <v>27.96069311999999</v>
+      </c>
+      <c r="Q6">
+        <v>57.96069311999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08559801533523304</v>
+      </c>
+      <c r="T6">
+        <v>0.8310260744528014</v>
+      </c>
+      <c r="U6">
+        <v>0.0458</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03664</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>10.84771787683619</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08361551791794906</v>
+      </c>
+      <c r="C7">
+        <v>1845.93811574142</v>
+      </c>
+      <c r="D7">
+        <v>1923.90311574142</v>
+      </c>
+      <c r="E7">
+        <v>-20.63499999999999</v>
+      </c>
+      <c r="F7">
+        <v>96.86500000000001</v>
+      </c>
+      <c r="G7">
+        <v>18.9</v>
+      </c>
+      <c r="H7">
+        <v>1819.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K7">
+        <v>30</v>
+      </c>
+      <c r="L7">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M7">
+        <v>4.649520000000001</v>
+      </c>
+      <c r="N7">
+        <v>33.85047999999998</v>
+      </c>
+      <c r="O7">
+        <v>6.770095999999997</v>
+      </c>
+      <c r="P7">
+        <v>27.08038399999999</v>
+      </c>
+      <c r="Q7">
+        <v>57.08038399999998</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08599528201889375</v>
+      </c>
+      <c r="T7">
+        <v>0.8380806251697182</v>
+      </c>
+      <c r="U7">
+        <v>0.048</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.0384</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>8.280424645984958</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08359294111407442</v>
+      </c>
+      <c r="C8">
+        <v>1827.534812801662</v>
+      </c>
+      <c r="D8">
+        <v>1924.872812801662</v>
+      </c>
+      <c r="E8">
+        <v>-1.262</v>
+      </c>
+      <c r="F8">
+        <v>116.238</v>
+      </c>
+      <c r="G8">
+        <v>18.9</v>
+      </c>
+      <c r="H8">
+        <v>1819.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K8">
+        <v>30</v>
+      </c>
+      <c r="L8">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M8">
+        <v>5.753781</v>
+      </c>
+      <c r="N8">
+        <v>32.74621899999998</v>
+      </c>
+      <c r="O8">
+        <v>6.549243799999997</v>
+      </c>
+      <c r="P8">
+        <v>26.19697519999999</v>
+      </c>
+      <c r="Q8">
+        <v>56.19697519999998</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08640100118518555</v>
+      </c>
+      <c r="T8">
+        <v>0.8452852727103992</v>
+      </c>
+      <c r="U8">
+        <v>0.0495</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.0396</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>6.691252239179764</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08358876431019978</v>
+      </c>
+      <c r="C9">
+        <v>1808.341318004507</v>
+      </c>
+      <c r="D9">
+        <v>1925.052318004507</v>
+      </c>
+      <c r="E9">
+        <v>18.11100000000002</v>
+      </c>
+      <c r="F9">
+        <v>135.611</v>
+      </c>
+      <c r="G9">
+        <v>18.9</v>
+      </c>
+      <c r="H9">
+        <v>1819.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K9">
+        <v>30</v>
+      </c>
+      <c r="L9">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M9">
+        <v>6.902599900000001</v>
+      </c>
+      <c r="N9">
+        <v>31.59740009999998</v>
+      </c>
+      <c r="O9">
+        <v>6.319480019999997</v>
+      </c>
+      <c r="P9">
+        <v>25.27792007999999</v>
+      </c>
+      <c r="Q9">
+        <v>55.27792007999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08681544549483847</v>
+      </c>
+      <c r="T9">
+        <v>0.8526448589078691</v>
+      </c>
+      <c r="U9">
+        <v>0.0509</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.577608518204855</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08351738750632513</v>
+      </c>
+      <c r="C10">
+        <v>1792.041039588057</v>
+      </c>
+      <c r="D10">
+        <v>1928.125039588057</v>
+      </c>
+      <c r="E10">
+        <v>37.48400000000001</v>
+      </c>
+      <c r="F10">
+        <v>154.984</v>
+      </c>
+      <c r="G10">
+        <v>18.9</v>
+      </c>
+      <c r="H10">
+        <v>1819.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K10">
+        <v>30</v>
+      </c>
+      <c r="L10">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M10">
+        <v>7.888685600000001</v>
+      </c>
+      <c r="N10">
+        <v>30.61131439999998</v>
+      </c>
+      <c r="O10">
+        <v>6.122262879999997</v>
+      </c>
+      <c r="P10">
+        <v>24.48905151999999</v>
+      </c>
+      <c r="Q10">
+        <v>54.48905151999998</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08723889946339689</v>
+      </c>
+      <c r="T10">
+        <v>0.8601644361096318</v>
+      </c>
+      <c r="U10">
+        <v>0.0509</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.880407453429248</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08363321070245047</v>
+      </c>
+      <c r="C11">
+        <v>1767.686874930979</v>
+      </c>
+      <c r="D11">
+        <v>1923.143874930979</v>
+      </c>
+      <c r="E11">
+        <v>56.857</v>
+      </c>
+      <c r="F11">
+        <v>174.357</v>
+      </c>
+      <c r="G11">
+        <v>18.9</v>
+      </c>
+      <c r="H11">
+        <v>1819.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K11">
+        <v>30</v>
+      </c>
+      <c r="L11">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M11">
+        <v>9.3280995</v>
+      </c>
+      <c r="N11">
+        <v>29.17190049999999</v>
+      </c>
+      <c r="O11">
+        <v>5.834380099999997</v>
+      </c>
+      <c r="P11">
+        <v>23.33752039999999</v>
+      </c>
+      <c r="Q11">
+        <v>53.33752039999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08767166011258294</v>
+      </c>
+      <c r="T11">
+        <v>0.8678492787444001</v>
+      </c>
+      <c r="U11">
+        <v>0.0535</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.0428</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>4.127314465288453</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08379863389857585</v>
+      </c>
+      <c r="C12">
+        <v>1741.244046830928</v>
+      </c>
+      <c r="D12">
+        <v>1916.074046830928</v>
+      </c>
+      <c r="E12">
+        <v>76.23000000000002</v>
+      </c>
+      <c r="F12">
+        <v>193.73</v>
+      </c>
+      <c r="G12">
+        <v>18.9</v>
+      </c>
+      <c r="H12">
+        <v>1819.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K12">
+        <v>30</v>
+      </c>
+      <c r="L12">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M12">
+        <v>10.887626</v>
+      </c>
+      <c r="N12">
+        <v>27.61237399999998</v>
+      </c>
+      <c r="O12">
+        <v>5.522474799999998</v>
+      </c>
+      <c r="P12">
+        <v>22.08989919999999</v>
+      </c>
+      <c r="Q12">
+        <v>52.08989919999998</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08811403766508427</v>
+      </c>
+      <c r="T12">
+        <v>0.8757048956599414</v>
+      </c>
+      <c r="U12">
+        <v>0.0562</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.04496</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>3.536124403979342</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.0850016570947012</v>
+      </c>
+      <c r="C13">
+        <v>1671.979296863897</v>
+      </c>
+      <c r="D13">
+        <v>1866.182296863897</v>
+      </c>
+      <c r="E13">
+        <v>95.60300000000001</v>
+      </c>
+      <c r="F13">
+        <v>213.103</v>
+      </c>
+      <c r="G13">
+        <v>18.9</v>
+      </c>
+      <c r="H13">
+        <v>1819.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K13">
+        <v>30</v>
+      </c>
+      <c r="L13">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M13">
+        <v>14.9598306</v>
+      </c>
+      <c r="N13">
+        <v>23.54016939999999</v>
+      </c>
+      <c r="O13">
+        <v>4.708033879999998</v>
+      </c>
+      <c r="P13">
+        <v>18.83213551999999</v>
+      </c>
+      <c r="Q13">
+        <v>48.83213551999998</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08856635628618112</v>
+      </c>
+      <c r="T13">
+        <v>0.8837370432926854</v>
+      </c>
+      <c r="U13">
+        <v>0.0702</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.05616</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>2.573558553530678</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08553588029082655</v>
+      </c>
+      <c r="C14">
+        <v>1631.274552067835</v>
+      </c>
+      <c r="D14">
+        <v>1844.850552067835</v>
+      </c>
+      <c r="E14">
+        <v>114.976</v>
+      </c>
+      <c r="F14">
+        <v>232.476</v>
+      </c>
+      <c r="G14">
+        <v>18.9</v>
+      </c>
+      <c r="H14">
+        <v>1819.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K14">
+        <v>30</v>
+      </c>
+      <c r="L14">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M14">
+        <v>17.4124524</v>
+      </c>
+      <c r="N14">
+        <v>21.08754759999999</v>
+      </c>
+      <c r="O14">
+        <v>4.217509519999997</v>
+      </c>
+      <c r="P14">
+        <v>16.87003807999999</v>
+      </c>
+      <c r="Q14">
+        <v>46.87003807999999</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08902895487593926</v>
+      </c>
+      <c r="T14">
+        <v>0.8919517397352649</v>
+      </c>
+      <c r="U14">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.05992</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>2.211061320690243</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08565650348695192</v>
+      </c>
+      <c r="C15">
+        <v>1607.152333637014</v>
+      </c>
+      <c r="D15">
+        <v>1840.101333637014</v>
+      </c>
+      <c r="E15">
+        <v>134.349</v>
+      </c>
+      <c r="F15">
+        <v>251.849</v>
+      </c>
+      <c r="G15">
+        <v>18.9</v>
+      </c>
+      <c r="H15">
+        <v>1819.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K15">
+        <v>30</v>
+      </c>
+      <c r="L15">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M15">
+        <v>18.8634901</v>
+      </c>
+      <c r="N15">
+        <v>19.63650989999999</v>
+      </c>
+      <c r="O15">
+        <v>3.927301979999998</v>
+      </c>
+      <c r="P15">
+        <v>15.70920791999999</v>
+      </c>
+      <c r="Q15">
+        <v>45.70920791999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08950218791603667</v>
+      </c>
+      <c r="T15">
+        <v>0.9003552797742252</v>
+      </c>
+      <c r="U15">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.05992</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>2.040979680637148</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08760272668307725</v>
+      </c>
+      <c r="C16">
+        <v>1514.397206404616</v>
+      </c>
+      <c r="D16">
+        <v>1766.719206404616</v>
+      </c>
+      <c r="E16">
+        <v>153.722</v>
+      </c>
+      <c r="F16">
+        <v>271.222</v>
+      </c>
+      <c r="G16">
+        <v>18.9</v>
+      </c>
+      <c r="H16">
+        <v>1819.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K16">
+        <v>30</v>
+      </c>
+      <c r="L16">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M16">
+        <v>24.7354464</v>
+      </c>
+      <c r="N16">
+        <v>13.76455359999998</v>
+      </c>
+      <c r="O16">
+        <v>2.752910719999996</v>
+      </c>
+      <c r="P16">
+        <v>11.01164287999999</v>
+      </c>
+      <c r="Q16">
+        <v>41.01164287999998</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08998642637567122</v>
+      </c>
+      <c r="T16">
+        <v>0.9089542509768825</v>
+      </c>
+      <c r="U16">
+        <v>0.0912</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>1.556470798117473</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09663435075221785</v>
+      </c>
+      <c r="C17">
+        <v>1219.126863381966</v>
+      </c>
+      <c r="D17">
+        <v>1490.821863381966</v>
+      </c>
+      <c r="E17">
+        <v>173.095</v>
+      </c>
+      <c r="F17">
+        <v>290.595</v>
+      </c>
+      <c r="G17">
+        <v>18.9</v>
+      </c>
+      <c r="H17">
+        <v>1819.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K17">
+        <v>30</v>
+      </c>
+      <c r="L17">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M17">
+        <v>45.507177</v>
+      </c>
+      <c r="N17">
+        <v>-7.007177000000013</v>
+      </c>
+      <c r="O17">
+        <v>-1.401435400000003</v>
+      </c>
+      <c r="P17">
+        <v>-5.605741600000011</v>
+      </c>
+      <c r="Q17">
+        <v>24.39425839999998</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09072818186151839</v>
+      </c>
+      <c r="T17">
+        <v>0.9221261375449719</v>
+      </c>
+      <c r="U17">
+        <v>0.1566</v>
+      </c>
+      <c r="V17">
+        <v>0.1692040796114423</v>
+      </c>
+      <c r="W17">
+        <v>0.1301026411328481</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.8460203980572116</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1064517125909758</v>
+      </c>
+      <c r="C18">
+        <v>983.4114071541185</v>
+      </c>
+      <c r="D18">
+        <v>1274.479407154118</v>
+      </c>
+      <c r="E18">
+        <v>192.468</v>
+      </c>
+      <c r="F18">
+        <v>309.968</v>
+      </c>
+      <c r="G18">
+        <v>18.9</v>
+      </c>
+      <c r="H18">
+        <v>1819.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K18">
+        <v>30</v>
+      </c>
+      <c r="L18">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M18">
+        <v>64.7213184</v>
+      </c>
+      <c r="N18">
+        <v>-26.22131840000002</v>
+      </c>
+      <c r="O18">
+        <v>-5.244263680000003</v>
+      </c>
+      <c r="P18">
+        <v>-20.97705472000001</v>
+      </c>
+      <c r="Q18">
+        <v>9.022945279999984</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.0916884719298197</v>
+      </c>
+      <c r="T18">
+        <v>0.939178700139344</v>
+      </c>
+      <c r="U18">
+        <v>0.2088</v>
+      </c>
+      <c r="V18">
+        <v>0.1189716184767954</v>
+      </c>
+      <c r="W18">
+        <v>0.1839587260620451</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5948580923839769</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1081517125909758</v>
+      </c>
+      <c r="C19">
+        <v>932.7974339868039</v>
+      </c>
+      <c r="D19">
+        <v>1243.238433986804</v>
+      </c>
+      <c r="E19">
+        <v>211.841</v>
+      </c>
+      <c r="F19">
+        <v>329.341</v>
+      </c>
+      <c r="G19">
+        <v>18.9</v>
+      </c>
+      <c r="H19">
+        <v>1819.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K19">
+        <v>30</v>
+      </c>
+      <c r="L19">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M19">
+        <v>68.7664008</v>
+      </c>
+      <c r="N19">
+        <v>-30.26640080000001</v>
+      </c>
+      <c r="O19">
+        <v>-6.053280160000003</v>
+      </c>
+      <c r="P19">
+        <v>-24.21312064000001</v>
+      </c>
+      <c r="Q19">
+        <v>5.786879359999986</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09232568243499825</v>
+      </c>
+      <c r="T19">
+        <v>0.9504941061651192</v>
+      </c>
+      <c r="U19">
+        <v>0.2088</v>
+      </c>
+      <c r="V19">
+        <v>0.1119732879781604</v>
+      </c>
+      <c r="W19">
+        <v>0.1854199774701601</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.5598664398908018</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1098517125909758</v>
+      </c>
+      <c r="C20">
+        <v>883.6784185748406</v>
+      </c>
+      <c r="D20">
+        <v>1213.49241857484</v>
+      </c>
+      <c r="E20">
+        <v>231.214</v>
+      </c>
+      <c r="F20">
+        <v>348.714</v>
+      </c>
+      <c r="G20">
+        <v>18.9</v>
+      </c>
+      <c r="H20">
+        <v>1819.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K20">
+        <v>30</v>
+      </c>
+      <c r="L20">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M20">
+        <v>72.8114832</v>
+      </c>
+      <c r="N20">
+        <v>-34.31148320000001</v>
+      </c>
+      <c r="O20">
+        <v>-6.862296640000003</v>
+      </c>
+      <c r="P20">
+        <v>-27.44918656000001</v>
+      </c>
+      <c r="Q20">
+        <v>2.550813439999988</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09297843465981528</v>
+      </c>
+      <c r="T20">
+        <v>0.9620854977037181</v>
+      </c>
+      <c r="U20">
+        <v>0.2088</v>
+      </c>
+      <c r="V20">
+        <v>0.1057525497571515</v>
+      </c>
+      <c r="W20">
+        <v>0.1867188676107068</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.5287627487857574</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1115517125909758</v>
+      </c>
+      <c r="C21">
+        <v>835.9495622230395</v>
+      </c>
+      <c r="D21">
+        <v>1185.136562223039</v>
+      </c>
+      <c r="E21">
+        <v>250.587</v>
+      </c>
+      <c r="F21">
+        <v>368.087</v>
+      </c>
+      <c r="G21">
+        <v>18.9</v>
+      </c>
+      <c r="H21">
+        <v>1819.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K21">
+        <v>30</v>
+      </c>
+      <c r="L21">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M21">
+        <v>76.8565656</v>
+      </c>
+      <c r="N21">
+        <v>-38.35656560000001</v>
+      </c>
+      <c r="O21">
+        <v>-7.671313120000002</v>
+      </c>
+      <c r="P21">
+        <v>-30.68525248000001</v>
+      </c>
+      <c r="Q21">
+        <v>-0.6852524800000133</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09364730422351672</v>
+      </c>
+      <c r="T21">
+        <v>0.973963096440801</v>
+      </c>
+      <c r="U21">
+        <v>0.2088</v>
+      </c>
+      <c r="V21">
+        <v>0.1001866260857224</v>
+      </c>
+      <c r="W21">
+        <v>0.1878810324733012</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.5009331304286122</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1193600147915127</v>
+      </c>
+      <c r="C22">
+        <v>701.7068660010145</v>
+      </c>
+      <c r="D22">
+        <v>1070.266866001014</v>
+      </c>
+      <c r="E22">
+        <v>269.96</v>
+      </c>
+      <c r="F22">
+        <v>387.46</v>
+      </c>
+      <c r="G22">
+        <v>18.9</v>
+      </c>
+      <c r="H22">
+        <v>1819.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K22">
+        <v>30</v>
+      </c>
+      <c r="L22">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M22">
+        <v>92.52544800000001</v>
+      </c>
+      <c r="N22">
+        <v>-54.02544800000003</v>
+      </c>
+      <c r="O22">
+        <v>-10.80508960000001</v>
+      </c>
+      <c r="P22">
+        <v>-43.22035840000002</v>
+      </c>
+      <c r="Q22">
+        <v>-13.22035840000003</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09446827327698182</v>
+      </c>
+      <c r="T22">
+        <v>0.9885416353993685</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.08322034820085385</v>
+      </c>
+      <c r="W22">
+        <v>0.2189269808496361</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.4161017410042692</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1213600147915127</v>
+      </c>
+      <c r="C23">
+        <v>656.4068632333007</v>
+      </c>
+      <c r="D23">
+        <v>1044.339863233301</v>
+      </c>
+      <c r="E23">
+        <v>289.333</v>
+      </c>
+      <c r="F23">
+        <v>406.833</v>
+      </c>
+      <c r="G23">
+        <v>18.9</v>
+      </c>
+      <c r="H23">
+        <v>1819.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K23">
+        <v>30</v>
+      </c>
+      <c r="L23">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M23">
+        <v>97.1517204</v>
+      </c>
+      <c r="N23">
+        <v>-58.65172040000002</v>
+      </c>
+      <c r="O23">
+        <v>-11.73034408</v>
+      </c>
+      <c r="P23">
+        <v>-46.92137632000001</v>
+      </c>
+      <c r="Q23">
+        <v>-16.92137632000002</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.0951729349640322</v>
+      </c>
+      <c r="T23">
+        <v>1.001054820657588</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.07925747447700368</v>
+      </c>
+      <c r="W23">
+        <v>0.2198733150948915</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3962873723850183</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1233600147915127</v>
+      </c>
+      <c r="C24">
+        <v>612.3333031445121</v>
+      </c>
+      <c r="D24">
+        <v>1019.639303144512</v>
+      </c>
+      <c r="E24">
+        <v>308.706</v>
+      </c>
+      <c r="F24">
+        <v>426.206</v>
+      </c>
+      <c r="G24">
+        <v>18.9</v>
+      </c>
+      <c r="H24">
+        <v>1819.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K24">
+        <v>30</v>
+      </c>
+      <c r="L24">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M24">
+        <v>101.7779928</v>
+      </c>
+      <c r="N24">
+        <v>-63.27799280000002</v>
+      </c>
+      <c r="O24">
+        <v>-12.65559856</v>
+      </c>
+      <c r="P24">
+        <v>-50.62239424000002</v>
+      </c>
+      <c r="Q24">
+        <v>-20.62239424000002</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09589566489946852</v>
+      </c>
+      <c r="T24">
+        <v>1.013888856819865</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.07565486200077623</v>
+      </c>
+      <c r="W24">
+        <v>0.2207336189542146</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3782743100038811</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1253600147915127</v>
+      </c>
+      <c r="C25">
+        <v>569.4011735486959</v>
+      </c>
+      <c r="D25">
+        <v>996.0801735486958</v>
+      </c>
+      <c r="E25">
+        <v>328.079</v>
+      </c>
+      <c r="F25">
+        <v>445.579</v>
+      </c>
+      <c r="G25">
+        <v>18.9</v>
+      </c>
+      <c r="H25">
+        <v>1819.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K25">
+        <v>30</v>
+      </c>
+      <c r="L25">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M25">
+        <v>106.4042652</v>
+      </c>
+      <c r="N25">
+        <v>-67.90426520000003</v>
+      </c>
+      <c r="O25">
+        <v>-13.58085304000001</v>
+      </c>
+      <c r="P25">
+        <v>-54.32341216000002</v>
+      </c>
+      <c r="Q25">
+        <v>-24.32341216000002</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09663716704102007</v>
+      </c>
+      <c r="T25">
+        <v>1.027056244570772</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.07236552017465551</v>
+      </c>
+      <c r="W25">
+        <v>0.2215191137822923</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3618276008732776</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1273600147915127</v>
+      </c>
+      <c r="C26">
+        <v>527.5331417695425</v>
+      </c>
+      <c r="D26">
+        <v>973.5851417695425</v>
+      </c>
+      <c r="E26">
+        <v>347.452</v>
+      </c>
+      <c r="F26">
+        <v>464.952</v>
+      </c>
+      <c r="G26">
+        <v>18.9</v>
+      </c>
+      <c r="H26">
+        <v>1819.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K26">
+        <v>30</v>
+      </c>
+      <c r="L26">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M26">
+        <v>111.0305376</v>
+      </c>
+      <c r="N26">
+        <v>-72.53053760000002</v>
+      </c>
+      <c r="O26">
+        <v>-14.50610752</v>
+      </c>
+      <c r="P26">
+        <v>-58.02443008000002</v>
+      </c>
+      <c r="Q26">
+        <v>-28.02443008000002</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09739818239682296</v>
+      </c>
+      <c r="T26">
+        <v>1.040570142525651</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.06935029016737822</v>
+      </c>
+      <c r="W26">
+        <v>0.2222391507080301</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3467514508368911</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1293600147915127</v>
+      </c>
+      <c r="C27">
+        <v>486.6587066381339</v>
+      </c>
+      <c r="D27">
+        <v>952.0837066381339</v>
+      </c>
+      <c r="E27">
+        <v>366.825</v>
+      </c>
+      <c r="F27">
+        <v>484.325</v>
+      </c>
+      <c r="G27">
+        <v>18.9</v>
+      </c>
+      <c r="H27">
+        <v>1819.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K27">
+        <v>30</v>
+      </c>
+      <c r="L27">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M27">
+        <v>115.65681</v>
+      </c>
+      <c r="N27">
+        <v>-77.15681000000002</v>
+      </c>
+      <c r="O27">
+        <v>-15.43136200000001</v>
+      </c>
+      <c r="P27">
+        <v>-61.72544800000001</v>
+      </c>
+      <c r="Q27">
+        <v>-31.72544800000002</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09817949149544726</v>
+      </c>
+      <c r="T27">
+        <v>1.05444441109266</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.06657627856068309</v>
+      </c>
+      <c r="W27">
+        <v>0.2229015846797089</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3328813928034154</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1313600147915127</v>
+      </c>
+      <c r="C28">
+        <v>446.7134604304674</v>
+      </c>
+      <c r="D28">
+        <v>931.5114604304674</v>
+      </c>
+      <c r="E28">
+        <v>386.198</v>
+      </c>
+      <c r="F28">
+        <v>503.698</v>
+      </c>
+      <c r="G28">
+        <v>18.9</v>
+      </c>
+      <c r="H28">
+        <v>1819.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K28">
+        <v>30</v>
+      </c>
+      <c r="L28">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M28">
+        <v>120.2830824</v>
+      </c>
+      <c r="N28">
+        <v>-81.78308240000001</v>
+      </c>
+      <c r="O28">
+        <v>-16.35661648</v>
+      </c>
+      <c r="P28">
+        <v>-65.42646592000001</v>
+      </c>
+      <c r="Q28">
+        <v>-35.42646592000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09898191705619654</v>
+      </c>
+      <c r="T28">
+        <v>1.068693659891209</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.06401565246219527</v>
+      </c>
+      <c r="W28">
+        <v>0.2235130621920278</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3200782623109764</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1333600147915127</v>
+      </c>
+      <c r="C29">
+        <v>407.6384444677102</v>
+      </c>
+      <c r="D29">
+        <v>911.8094444677103</v>
+      </c>
+      <c r="E29">
+        <v>405.571</v>
+      </c>
+      <c r="F29">
+        <v>523.071</v>
+      </c>
+      <c r="G29">
+        <v>18.9</v>
+      </c>
+      <c r="H29">
+        <v>1819.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K29">
+        <v>30</v>
+      </c>
+      <c r="L29">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M29">
+        <v>124.9093548</v>
+      </c>
+      <c r="N29">
+        <v>-86.40935480000003</v>
+      </c>
+      <c r="O29">
+        <v>-17.28187096000001</v>
+      </c>
+      <c r="P29">
+        <v>-69.12748384000002</v>
+      </c>
+      <c r="Q29">
+        <v>-39.12748384000002</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09980632687888419</v>
+      </c>
+      <c r="T29">
+        <v>1.083333299067801</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.06164470237100285</v>
+      </c>
+      <c r="W29">
+        <v>0.2240792450738045</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3082235118550143</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1353600147915127</v>
+      </c>
+      <c r="C30">
+        <v>369.3795847992657</v>
+      </c>
+      <c r="D30">
+        <v>892.9235847992658</v>
+      </c>
+      <c r="E30">
+        <v>424.9440000000001</v>
+      </c>
+      <c r="F30">
+        <v>542.4440000000001</v>
+      </c>
+      <c r="G30">
+        <v>18.9</v>
+      </c>
+      <c r="H30">
+        <v>1819.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K30">
+        <v>30</v>
+      </c>
+      <c r="L30">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M30">
+        <v>129.5356272</v>
+      </c>
+      <c r="N30">
+        <v>-91.03562720000004</v>
+      </c>
+      <c r="O30">
+        <v>-18.20712544000001</v>
+      </c>
+      <c r="P30">
+        <v>-72.82850176000002</v>
+      </c>
+      <c r="Q30">
+        <v>-42.82850176000002</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1006536369744242</v>
+      </c>
+      <c r="T30">
+        <v>1.098379594888187</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.05944310585775275</v>
+      </c>
+      <c r="W30">
+        <v>0.2246049863211687</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2972155292887637</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1373600147915127</v>
+      </c>
+      <c r="C31">
+        <v>331.8871965932457</v>
+      </c>
+      <c r="D31">
+        <v>874.8041965932456</v>
+      </c>
+      <c r="E31">
+        <v>444.3169999999999</v>
+      </c>
+      <c r="F31">
+        <v>561.8169999999999</v>
+      </c>
+      <c r="G31">
+        <v>18.9</v>
+      </c>
+      <c r="H31">
+        <v>1819.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K31">
+        <v>30</v>
+      </c>
+      <c r="L31">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M31">
+        <v>134.1618996</v>
+      </c>
+      <c r="N31">
+        <v>-95.66189959999998</v>
+      </c>
+      <c r="O31">
+        <v>-19.13237992</v>
+      </c>
+      <c r="P31">
+        <v>-76.52951967999999</v>
+      </c>
+      <c r="Q31">
+        <v>-46.52951967999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1015248149599795</v>
+      </c>
+      <c r="T31">
+        <v>1.113849730027457</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.05739334358679578</v>
+      </c>
+      <c r="W31">
+        <v>0.2250944695514732</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2869667179339789</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1393600147915127</v>
+      </c>
+      <c r="C32">
+        <v>295.1155476688804</v>
+      </c>
+      <c r="D32">
+        <v>857.4055476688803</v>
+      </c>
+      <c r="E32">
+        <v>463.6899999999999</v>
+      </c>
+      <c r="F32">
+        <v>581.1899999999999</v>
+      </c>
+      <c r="G32">
+        <v>18.9</v>
+      </c>
+      <c r="H32">
+        <v>1819.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K32">
+        <v>30</v>
+      </c>
+      <c r="L32">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M32">
+        <v>138.788172</v>
+      </c>
+      <c r="N32">
+        <v>-100.288172</v>
+      </c>
+      <c r="O32">
+        <v>-20.0576344</v>
+      </c>
+      <c r="P32">
+        <v>-80.23053760000002</v>
+      </c>
+      <c r="Q32">
+        <v>-50.23053760000002</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1024208837451221</v>
+      </c>
+      <c r="T32">
+        <v>1.12976186902785</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05548023213390257</v>
+      </c>
+      <c r="W32">
+        <v>0.2255513205664241</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2774011606695128</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1413600147915127</v>
+      </c>
+      <c r="C33">
+        <v>259.0224730976774</v>
+      </c>
+      <c r="D33">
+        <v>840.6854730976775</v>
+      </c>
+      <c r="E33">
+        <v>483.063</v>
+      </c>
+      <c r="F33">
+        <v>600.563</v>
+      </c>
+      <c r="G33">
+        <v>18.9</v>
+      </c>
+      <c r="H33">
+        <v>1819.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K33">
+        <v>30</v>
+      </c>
+      <c r="L33">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M33">
+        <v>143.4144444</v>
+      </c>
+      <c r="N33">
+        <v>-104.9144444</v>
+      </c>
+      <c r="O33">
+        <v>-20.98288888</v>
+      </c>
+      <c r="P33">
+        <v>-83.93155552000002</v>
+      </c>
+      <c r="Q33">
+        <v>-53.93155552000002</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1033429255385296</v>
+      </c>
+      <c r="T33">
+        <v>1.146135229448543</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.05369054722635733</v>
+      </c>
+      <c r="W33">
+        <v>0.2259786973223459</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2684527361317867</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1433600147915127</v>
+      </c>
+      <c r="C34">
+        <v>223.5690340354993</v>
+      </c>
+      <c r="D34">
+        <v>824.6050340354993</v>
+      </c>
+      <c r="E34">
+        <v>502.436</v>
+      </c>
+      <c r="F34">
+        <v>619.936</v>
+      </c>
+      <c r="G34">
+        <v>18.9</v>
+      </c>
+      <c r="H34">
+        <v>1819.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K34">
+        <v>30</v>
+      </c>
+      <c r="L34">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M34">
+        <v>148.0407168</v>
+      </c>
+      <c r="N34">
+        <v>-109.5407168</v>
+      </c>
+      <c r="O34">
+        <v>-21.90814336000001</v>
+      </c>
+      <c r="P34">
+        <v>-87.63257344000002</v>
+      </c>
+      <c r="Q34">
+        <v>-57.63257344000002</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1042920862082139</v>
+      </c>
+      <c r="T34">
+        <v>1.162990159293375</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05201271762553366</v>
+      </c>
+      <c r="W34">
+        <v>0.2263793630310226</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2600635881276683</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1453600147915127</v>
+      </c>
+      <c r="C35">
+        <v>188.71921497445</v>
+      </c>
+      <c r="D35">
+        <v>809.12821497445</v>
+      </c>
+      <c r="E35">
+        <v>521.809</v>
+      </c>
+      <c r="F35">
+        <v>639.309</v>
+      </c>
+      <c r="G35">
+        <v>18.9</v>
+      </c>
+      <c r="H35">
+        <v>1819.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K35">
+        <v>30</v>
+      </c>
+      <c r="L35">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M35">
+        <v>152.6669892</v>
+      </c>
+      <c r="N35">
+        <v>-114.1669892</v>
+      </c>
+      <c r="O35">
+        <v>-22.83339784</v>
+      </c>
+      <c r="P35">
+        <v>-91.33359136</v>
+      </c>
+      <c r="Q35">
+        <v>-61.33359136</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1052695800322171</v>
+      </c>
+      <c r="T35">
+        <v>1.18034822137238</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.05043657466718417</v>
+      </c>
+      <c r="W35">
+        <v>0.2267557459694764</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2521828733359208</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1473600147915127</v>
+      </c>
+      <c r="C36">
+        <v>154.4396544599111</v>
+      </c>
+      <c r="D36">
+        <v>794.2216544599112</v>
+      </c>
+      <c r="E36">
+        <v>541.182</v>
+      </c>
+      <c r="F36">
+        <v>658.682</v>
+      </c>
+      <c r="G36">
+        <v>18.9</v>
+      </c>
+      <c r="H36">
+        <v>1819.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K36">
+        <v>30</v>
+      </c>
+      <c r="L36">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M36">
+        <v>157.2932616</v>
+      </c>
+      <c r="N36">
+        <v>-118.7932616</v>
+      </c>
+      <c r="O36">
+        <v>-23.75865232000001</v>
+      </c>
+      <c r="P36">
+        <v>-95.03460928000003</v>
+      </c>
+      <c r="Q36">
+        <v>-65.03460928000003</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1062766948811901</v>
+      </c>
+      <c r="T36">
+        <v>1.198232285332568</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.04895314600050227</v>
+      </c>
+      <c r="W36">
+        <v>0.2271099887350801</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2447657300025113</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1493600147915127</v>
+      </c>
+      <c r="C37">
+        <v>120.6994050351057</v>
+      </c>
+      <c r="D37">
+        <v>779.8544050351057</v>
+      </c>
+      <c r="E37">
+        <v>560.5550000000001</v>
+      </c>
+      <c r="F37">
+        <v>678.0550000000001</v>
+      </c>
+      <c r="G37">
+        <v>18.9</v>
+      </c>
+      <c r="H37">
+        <v>1819.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K37">
+        <v>30</v>
+      </c>
+      <c r="L37">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M37">
+        <v>161.919534</v>
+      </c>
+      <c r="N37">
+        <v>-123.419534</v>
+      </c>
+      <c r="O37">
+        <v>-24.68390680000001</v>
+      </c>
+      <c r="P37">
+        <v>-98.73562720000004</v>
+      </c>
+      <c r="Q37">
+        <v>-68.73562720000004</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1073147978793622</v>
+      </c>
+      <c r="T37">
+        <v>1.216666628183838</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.0475544846862022</v>
+      </c>
+      <c r="W37">
+        <v>0.2274439890569349</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.237772423431011</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1513600147915127</v>
+      </c>
+      <c r="C38">
+        <v>87.46971877791987</v>
+      </c>
+      <c r="D38">
+        <v>765.9977187779199</v>
+      </c>
+      <c r="E38">
+        <v>579.928</v>
+      </c>
+      <c r="F38">
+        <v>697.428</v>
+      </c>
+      <c r="G38">
+        <v>18.9</v>
+      </c>
+      <c r="H38">
+        <v>1819.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K38">
+        <v>30</v>
+      </c>
+      <c r="L38">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M38">
+        <v>166.5458064</v>
+      </c>
+      <c r="N38">
+        <v>-128.0458064</v>
+      </c>
+      <c r="O38">
+        <v>-25.60916128</v>
+      </c>
+      <c r="P38">
+        <v>-102.43664512</v>
+      </c>
+      <c r="Q38">
+        <v>-72.43664512000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1083853415962273</v>
+      </c>
+      <c r="T38">
+        <v>1.23567704424921</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04623352677825215</v>
+      </c>
+      <c r="W38">
+        <v>0.2277594338053534</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2311676338912608</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1533600147915127</v>
+      </c>
+      <c r="C39">
+        <v>54.72385530244026</v>
+      </c>
+      <c r="D39">
+        <v>752.6248553024402</v>
+      </c>
+      <c r="E39">
+        <v>599.3009999999999</v>
+      </c>
+      <c r="F39">
+        <v>716.8009999999999</v>
+      </c>
+      <c r="G39">
+        <v>18.9</v>
+      </c>
+      <c r="H39">
+        <v>1819.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K39">
+        <v>30</v>
+      </c>
+      <c r="L39">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M39">
+        <v>171.1720788</v>
+      </c>
+      <c r="N39">
+        <v>-132.6720788</v>
+      </c>
+      <c r="O39">
+        <v>-26.53441576</v>
+      </c>
+      <c r="P39">
+        <v>-106.13766304</v>
+      </c>
+      <c r="Q39">
+        <v>-76.13766304000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1094898708279134</v>
+      </c>
+      <c r="T39">
+        <v>1.2552909655865</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04498397200046155</v>
+      </c>
+      <c r="W39">
+        <v>0.2280578274862898</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2249198600023077</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1553600147915127</v>
+      </c>
+      <c r="C40">
+        <v>22.43690952697602</v>
+      </c>
+      <c r="D40">
+        <v>739.710909526976</v>
+      </c>
+      <c r="E40">
+        <v>618.674</v>
+      </c>
+      <c r="F40">
+        <v>736.174</v>
+      </c>
+      <c r="G40">
+        <v>18.9</v>
+      </c>
+      <c r="H40">
+        <v>1819.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K40">
+        <v>30</v>
+      </c>
+      <c r="L40">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M40">
+        <v>175.7983512</v>
+      </c>
+      <c r="N40">
+        <v>-137.2983512</v>
+      </c>
+      <c r="O40">
+        <v>-27.45967024</v>
+      </c>
+      <c r="P40">
+        <v>-109.83868096</v>
+      </c>
+      <c r="Q40">
+        <v>-79.83868096</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1106300300348152</v>
+      </c>
+      <c r="T40">
+        <v>1.275537594063701</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.0438001832636073</v>
+      </c>
+      <c r="W40">
+        <v>0.2283405162366506</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2190009163180365</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1573600147915127</v>
+      </c>
+      <c r="C41">
+        <v>-9.414343125535083</v>
+      </c>
+      <c r="D41">
+        <v>727.232656874465</v>
+      </c>
+      <c r="E41">
+        <v>638.047</v>
+      </c>
+      <c r="F41">
+        <v>755.547</v>
+      </c>
+      <c r="G41">
+        <v>18.9</v>
+      </c>
+      <c r="H41">
+        <v>1819.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K41">
+        <v>30</v>
+      </c>
+      <c r="L41">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M41">
+        <v>180.4246236</v>
+      </c>
+      <c r="N41">
+        <v>-141.9246236</v>
+      </c>
+      <c r="O41">
+        <v>-28.38492472</v>
+      </c>
+      <c r="P41">
+        <v>-113.53969888</v>
+      </c>
+      <c r="Q41">
+        <v>-83.53969888000002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1118075715107958</v>
+      </c>
+      <c r="T41">
+        <v>1.296448046425401</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04267710164146352</v>
+      </c>
+      <c r="W41">
+        <v>0.2286087081280185</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2133855082073176</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1593600147915127</v>
+      </c>
+      <c r="C42">
+        <v>-40.85158611906979</v>
+      </c>
+      <c r="D42">
+        <v>715.1684138809303</v>
+      </c>
+      <c r="E42">
+        <v>657.4200000000001</v>
+      </c>
+      <c r="F42">
+        <v>774.9200000000001</v>
+      </c>
+      <c r="G42">
+        <v>18.9</v>
+      </c>
+      <c r="H42">
+        <v>1819.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K42">
+        <v>30</v>
+      </c>
+      <c r="L42">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M42">
+        <v>185.050896</v>
+      </c>
+      <c r="N42">
+        <v>-146.550896</v>
+      </c>
+      <c r="O42">
+        <v>-29.31017920000001</v>
+      </c>
+      <c r="P42">
+        <v>-117.2407168</v>
+      </c>
+      <c r="Q42">
+        <v>-87.24071680000002</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1130243643693091</v>
+      </c>
+      <c r="T42">
+        <v>1.318055513865825</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04161017410042692</v>
+      </c>
+      <c r="W42">
+        <v>0.2288634904248181</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2080508705021347</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1613600147915127</v>
+      </c>
+      <c r="C43">
+        <v>-71.89508754806354</v>
+      </c>
+      <c r="D43">
+        <v>703.4979124519365</v>
+      </c>
+      <c r="E43">
+        <v>676.793</v>
+      </c>
+      <c r="F43">
+        <v>794.293</v>
+      </c>
+      <c r="G43">
+        <v>18.9</v>
+      </c>
+      <c r="H43">
+        <v>1819.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K43">
+        <v>30</v>
+      </c>
+      <c r="L43">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M43">
+        <v>189.6771684</v>
+      </c>
+      <c r="N43">
+        <v>-151.1771684</v>
+      </c>
+      <c r="O43">
+        <v>-30.23543368000001</v>
+      </c>
+      <c r="P43">
+        <v>-120.94173472</v>
+      </c>
+      <c r="Q43">
+        <v>-90.94173472000003</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1142824044433652</v>
+      </c>
+      <c r="T43">
+        <v>1.340395437829652</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.04059529180529457</v>
+      </c>
+      <c r="W43">
+        <v>0.2291058443168957</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2029764590264728</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1633600147915127</v>
+      </c>
+      <c r="C44">
+        <v>-102.563813766938</v>
+      </c>
+      <c r="D44">
+        <v>692.202186233062</v>
+      </c>
+      <c r="E44">
+        <v>696.1659999999999</v>
+      </c>
+      <c r="F44">
+        <v>813.6659999999999</v>
+      </c>
+      <c r="G44">
+        <v>18.9</v>
+      </c>
+      <c r="H44">
+        <v>1819.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K44">
+        <v>30</v>
+      </c>
+      <c r="L44">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M44">
+        <v>194.3034408</v>
+      </c>
+      <c r="N44">
+        <v>-155.8034408</v>
+      </c>
+      <c r="O44">
+        <v>-31.16068816000001</v>
+      </c>
+      <c r="P44">
+        <v>-124.64275264</v>
+      </c>
+      <c r="Q44">
+        <v>-94.64275264000003</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1155838252096301</v>
+      </c>
+      <c r="T44">
+        <v>1.363505703999129</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.03962873723850184</v>
+      </c>
+      <c r="W44">
+        <v>0.2293366575474458</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1981436861925091</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1653600147915127</v>
+      </c>
+      <c r="C45">
+        <v>-132.875532245651</v>
+      </c>
+      <c r="D45">
+        <v>681.263467754349</v>
+      </c>
+      <c r="E45">
+        <v>715.539</v>
+      </c>
+      <c r="F45">
+        <v>833.039</v>
+      </c>
+      <c r="G45">
+        <v>18.9</v>
+      </c>
+      <c r="H45">
+        <v>1819.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K45">
+        <v>30</v>
+      </c>
+      <c r="L45">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M45">
+        <v>198.9297132</v>
+      </c>
+      <c r="N45">
+        <v>-160.4297132</v>
+      </c>
+      <c r="O45">
+        <v>-32.08594264000001</v>
+      </c>
+      <c r="P45">
+        <v>-128.34377056</v>
+      </c>
+      <c r="Q45">
+        <v>-98.34377056000002</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1169309098624306</v>
+      </c>
+      <c r="T45">
+        <v>1.387426856700868</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03870713869807156</v>
+      </c>
+      <c r="W45">
+        <v>0.2295567352789005</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1935356934903577</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1673600147915127</v>
+      </c>
+      <c r="C46">
+        <v>-162.8469048245461</v>
+      </c>
+      <c r="D46">
+        <v>670.665095175454</v>
+      </c>
+      <c r="E46">
+        <v>734.912</v>
+      </c>
+      <c r="F46">
+        <v>852.412</v>
+      </c>
+      <c r="G46">
+        <v>18.9</v>
+      </c>
+      <c r="H46">
+        <v>1819.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K46">
+        <v>30</v>
+      </c>
+      <c r="L46">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M46">
+        <v>203.5559856</v>
+      </c>
+      <c r="N46">
+        <v>-165.0559856</v>
+      </c>
+      <c r="O46">
+        <v>-33.01119712000001</v>
+      </c>
+      <c r="P46">
+        <v>-132.04478848</v>
+      </c>
+      <c r="Q46">
+        <v>-102.04478848</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1183261046814026</v>
+      </c>
+      <c r="T46">
+        <v>1.412202336284812</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03782743100038811</v>
+      </c>
+      <c r="W46">
+        <v>0.2297668094771073</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1891371550019405</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1693600147915127</v>
+      </c>
+      <c r="C47">
+        <v>-192.4935723979822</v>
+      </c>
+      <c r="D47">
+        <v>660.3914276020178</v>
+      </c>
+      <c r="E47">
+        <v>754.285</v>
+      </c>
+      <c r="F47">
+        <v>871.785</v>
+      </c>
+      <c r="G47">
+        <v>18.9</v>
+      </c>
+      <c r="H47">
+        <v>1819.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K47">
+        <v>30</v>
+      </c>
+      <c r="L47">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M47">
+        <v>208.182258</v>
+      </c>
+      <c r="N47">
+        <v>-169.682258</v>
+      </c>
+      <c r="O47">
+        <v>-33.9364516</v>
+      </c>
+      <c r="P47">
+        <v>-135.7458064</v>
+      </c>
+      <c r="Q47">
+        <v>-105.7458064</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1197720338574281</v>
+      </c>
+      <c r="T47">
+        <v>1.437878742399081</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03698682142260172</v>
+      </c>
+      <c r="W47">
+        <v>0.2299675470442827</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1849341071130086</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1713600147915127</v>
+      </c>
+      <c r="C48">
+        <v>-221.8302319319778</v>
+      </c>
+      <c r="D48">
+        <v>650.4277680680223</v>
+      </c>
+      <c r="E48">
+        <v>773.658</v>
+      </c>
+      <c r="F48">
+        <v>891.158</v>
+      </c>
+      <c r="G48">
+        <v>18.9</v>
+      </c>
+      <c r="H48">
+        <v>1819.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K48">
+        <v>30</v>
+      </c>
+      <c r="L48">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M48">
+        <v>212.8085304</v>
+      </c>
+      <c r="N48">
+        <v>-174.3085304000001</v>
+      </c>
+      <c r="O48">
+        <v>-34.86170608000001</v>
+      </c>
+      <c r="P48">
+        <v>-139.44682432</v>
+      </c>
+      <c r="Q48">
+        <v>-109.44682432</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.121271515965899</v>
+      </c>
+      <c r="T48">
+        <v>1.464506126517583</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03618276008732776</v>
+      </c>
+      <c r="W48">
+        <v>0.2301595568911461</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1809138004366387</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1733600147915127</v>
+      </c>
+      <c r="C49">
+        <v>-250.8707066134542</v>
+      </c>
+      <c r="D49">
+        <v>640.7602933865459</v>
+      </c>
+      <c r="E49">
+        <v>793.0310000000001</v>
+      </c>
+      <c r="F49">
+        <v>910.5310000000001</v>
+      </c>
+      <c r="G49">
+        <v>18.9</v>
+      </c>
+      <c r="H49">
+        <v>1819.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K49">
+        <v>30</v>
+      </c>
+      <c r="L49">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M49">
+        <v>217.4348028</v>
+      </c>
+      <c r="N49">
+        <v>-178.9348028000001</v>
+      </c>
+      <c r="O49">
+        <v>-35.78696056000001</v>
+      </c>
+      <c r="P49">
+        <v>-143.14784224</v>
+      </c>
+      <c r="Q49">
+        <v>-113.14784224</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1228275823048782</v>
+      </c>
+      <c r="T49">
+        <v>1.492138317583952</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03541291412802292</v>
+      </c>
+      <c r="W49">
+        <v>0.2303433961062281</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1770645706401145</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1753600147915127</v>
+      </c>
+      <c r="C50">
+        <v>-279.6280098352253</v>
+      </c>
+      <c r="D50">
+        <v>631.3759901647747</v>
+      </c>
+      <c r="E50">
+        <v>812.404</v>
+      </c>
+      <c r="F50">
+        <v>929.904</v>
+      </c>
+      <c r="G50">
+        <v>18.9</v>
+      </c>
+      <c r="H50">
+        <v>1819.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K50">
+        <v>30</v>
+      </c>
+      <c r="L50">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M50">
+        <v>222.0610752</v>
+      </c>
+      <c r="N50">
+        <v>-183.5610752</v>
+      </c>
+      <c r="O50">
+        <v>-36.71221504</v>
+      </c>
+      <c r="P50">
+        <v>-146.84886016</v>
+      </c>
+      <c r="Q50">
+        <v>-116.84886016</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1244434973492028</v>
+      </c>
+      <c r="T50">
+        <v>1.520833285229798</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03467514508368911</v>
+      </c>
+      <c r="W50">
+        <v>0.2305195753540151</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1733757254184456</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1773600147915127</v>
+      </c>
+      <c r="C51">
+        <v>-308.1144036395601</v>
+      </c>
+      <c r="D51">
+        <v>622.2625963604398</v>
+      </c>
+      <c r="E51">
+        <v>831.7769999999999</v>
+      </c>
+      <c r="F51">
+        <v>949.2769999999999</v>
+      </c>
+      <c r="G51">
+        <v>18.9</v>
+      </c>
+      <c r="H51">
+        <v>1819.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K51">
+        <v>30</v>
+      </c>
+      <c r="L51">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M51">
+        <v>226.6873476</v>
+      </c>
+      <c r="N51">
+        <v>-188.1873476</v>
+      </c>
+      <c r="O51">
+        <v>-37.63746952</v>
+      </c>
+      <c r="P51">
+        <v>-150.54987808</v>
+      </c>
+      <c r="Q51">
+        <v>-120.54987808</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1261227816109519</v>
+      </c>
+      <c r="T51">
+        <v>1.550653545724499</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03396748906157301</v>
+      </c>
+      <c r="W51">
+        <v>0.2306885636120964</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1698374453078649</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1793600147915127</v>
+      </c>
+      <c r="C52">
+        <v>-336.3414521722588</v>
+      </c>
+      <c r="D52">
+        <v>613.4085478277412</v>
+      </c>
+      <c r="E52">
+        <v>851.15</v>
+      </c>
+      <c r="F52">
+        <v>968.65</v>
+      </c>
+      <c r="G52">
+        <v>18.9</v>
+      </c>
+      <c r="H52">
+        <v>1819.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K52">
+        <v>30</v>
+      </c>
+      <c r="L52">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M52">
+        <v>231.31362</v>
+      </c>
+      <c r="N52">
+        <v>-192.81362</v>
+      </c>
+      <c r="O52">
+        <v>-38.562724</v>
+      </c>
+      <c r="P52">
+        <v>-154.250896</v>
+      </c>
+      <c r="Q52">
+        <v>-124.250896</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1278692372431709</v>
+      </c>
+      <c r="T52">
+        <v>1.581666616638989</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03328813928034154</v>
+      </c>
+      <c r="W52">
+        <v>0.2308507923398544</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1664406964017078</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1813600147915127</v>
+      </c>
+      <c r="C53">
+        <v>-364.3200706372236</v>
+      </c>
+      <c r="D53">
+        <v>604.8029293627765</v>
+      </c>
+      <c r="E53">
+        <v>870.523</v>
+      </c>
+      <c r="F53">
+        <v>988.023</v>
+      </c>
+      <c r="G53">
+        <v>18.9</v>
+      </c>
+      <c r="H53">
+        <v>1819.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K53">
+        <v>30</v>
+      </c>
+      <c r="L53">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M53">
+        <v>235.9398924</v>
+      </c>
+      <c r="N53">
+        <v>-197.4398924</v>
+      </c>
+      <c r="O53">
+        <v>-39.48797848000001</v>
+      </c>
+      <c r="P53">
+        <v>-157.95191392</v>
+      </c>
+      <c r="Q53">
+        <v>-127.95191392</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1296869767787458</v>
+      </c>
+      <c r="T53">
+        <v>1.613945527182643</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03263543066700151</v>
+      </c>
+      <c r="W53">
+        <v>0.2310066591567201</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1631771533350076</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1833600147915127</v>
+      </c>
+      <c r="C54">
+        <v>-392.0605701872897</v>
+      </c>
+      <c r="D54">
+        <v>596.4354298127103</v>
+      </c>
+      <c r="E54">
+        <v>889.896</v>
+      </c>
+      <c r="F54">
+        <v>1007.396</v>
+      </c>
+      <c r="G54">
+        <v>18.9</v>
+      </c>
+      <c r="H54">
+        <v>1819.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K54">
+        <v>30</v>
+      </c>
+      <c r="L54">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M54">
+        <v>240.5661648</v>
+      </c>
+      <c r="N54">
+        <v>-202.0661648</v>
+      </c>
+      <c r="O54">
+        <v>-40.41323296000001</v>
+      </c>
+      <c r="P54">
+        <v>-161.65293184</v>
+      </c>
+      <c r="Q54">
+        <v>-131.65293184</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1315804554616364</v>
+      </c>
+      <c r="T54">
+        <v>1.647569392332281</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03200782623109764</v>
+      </c>
+      <c r="W54">
+        <v>0.2311565310960139</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1600391311554882</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1853600147915127</v>
+      </c>
+      <c r="C55">
+        <v>-419.5726991394963</v>
+      </c>
+      <c r="D55">
+        <v>588.2963008605037</v>
+      </c>
+      <c r="E55">
+        <v>909.269</v>
+      </c>
+      <c r="F55">
+        <v>1026.769</v>
+      </c>
+      <c r="G55">
+        <v>18.9</v>
+      </c>
+      <c r="H55">
+        <v>1819.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K55">
+        <v>30</v>
+      </c>
+      <c r="L55">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M55">
+        <v>245.1924372</v>
+      </c>
+      <c r="N55">
+        <v>-206.6924372</v>
+      </c>
+      <c r="O55">
+        <v>-41.33848744000001</v>
+      </c>
+      <c r="P55">
+        <v>-165.35394976</v>
+      </c>
+      <c r="Q55">
+        <v>-135.35394976</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.133554507705501</v>
+      </c>
+      <c r="T55">
+        <v>1.682624060254244</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03140390498145428</v>
+      </c>
+      <c r="W55">
+        <v>0.2313007474904287</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1570195249072713</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1873600147915127</v>
+      </c>
+      <c r="C56">
+        <v>-446.8656808611743</v>
+      </c>
+      <c r="D56">
+        <v>580.3763191388258</v>
+      </c>
+      <c r="E56">
+        <v>928.6420000000001</v>
+      </c>
+      <c r="F56">
+        <v>1046.142</v>
+      </c>
+      <c r="G56">
+        <v>18.9</v>
+      </c>
+      <c r="H56">
+        <v>1819.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K56">
+        <v>30</v>
+      </c>
+      <c r="L56">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M56">
+        <v>249.8187096</v>
+      </c>
+      <c r="N56">
+        <v>-211.3187096</v>
+      </c>
+      <c r="O56">
+        <v>-42.26374192000001</v>
+      </c>
+      <c r="P56">
+        <v>-169.05496768</v>
+      </c>
+      <c r="Q56">
+        <v>-139.05496768</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1356143883077944</v>
+      </c>
+      <c r="T56">
+        <v>1.719202844172815</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03082235118550142</v>
+      </c>
+      <c r="W56">
+        <v>0.2314396225369023</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1541117559275071</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1893600147915127</v>
+      </c>
+      <c r="C57">
+        <v>-473.9482486364234</v>
+      </c>
+      <c r="D57">
+        <v>572.6667513635767</v>
+      </c>
+      <c r="E57">
+        <v>948.0150000000001</v>
+      </c>
+      <c r="F57">
+        <v>1065.515</v>
+      </c>
+      <c r="G57">
+        <v>18.9</v>
+      </c>
+      <c r="H57">
+        <v>1819.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K57">
+        <v>30</v>
+      </c>
+      <c r="L57">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M57">
+        <v>254.444982</v>
+      </c>
+      <c r="N57">
+        <v>-215.944982</v>
+      </c>
+      <c r="O57">
+        <v>-43.18899640000001</v>
+      </c>
+      <c r="P57">
+        <v>-172.7559856</v>
+      </c>
+      <c r="Q57">
+        <v>-142.7559856</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1377658191590788</v>
+      </c>
+      <c r="T57">
+        <v>1.7574073518211</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.03026194480031049</v>
+      </c>
+      <c r="W57">
+        <v>0.2315734475816859</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1513097240015525</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1913600147915127</v>
+      </c>
+      <c r="C58">
+        <v>-500.828677790074</v>
+      </c>
+      <c r="D58">
+        <v>565.1593222099261</v>
+      </c>
+      <c r="E58">
+        <v>967.3880000000001</v>
+      </c>
+      <c r="F58">
+        <v>1084.888</v>
+      </c>
+      <c r="G58">
+        <v>18.9</v>
+      </c>
+      <c r="H58">
+        <v>1819.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K58">
+        <v>30</v>
+      </c>
+      <c r="L58">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M58">
+        <v>259.0712544</v>
+      </c>
+      <c r="N58">
+        <v>-220.5712544</v>
+      </c>
+      <c r="O58">
+        <v>-44.11425088000001</v>
+      </c>
+      <c r="P58">
+        <v>-176.45700352</v>
+      </c>
+      <c r="Q58">
+        <v>-146.45700352</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1400150423217851</v>
+      </c>
+      <c r="T58">
+        <v>1.797348427998852</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02972155292887637</v>
+      </c>
+      <c r="W58">
+        <v>0.2317024931605843</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.148607764644382</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1933600147915127</v>
+      </c>
+      <c r="C59">
+        <v>-527.5148153175552</v>
+      </c>
+      <c r="D59">
+        <v>557.846184682445</v>
+      </c>
+      <c r="E59">
+        <v>986.7610000000002</v>
+      </c>
+      <c r="F59">
+        <v>1104.261</v>
+      </c>
+      <c r="G59">
+        <v>18.9</v>
+      </c>
+      <c r="H59">
+        <v>1819.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K59">
+        <v>30</v>
+      </c>
+      <c r="L59">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M59">
+        <v>263.6975268</v>
+      </c>
+      <c r="N59">
+        <v>-225.1975268</v>
+      </c>
+      <c r="O59">
+        <v>-45.03950536000001</v>
+      </c>
+      <c r="P59">
+        <v>-180.15802144</v>
+      </c>
+      <c r="Q59">
+        <v>-150.15802144</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.142368880515315</v>
+      </c>
+      <c r="T59">
+        <v>1.839147228649988</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02920012217573819</v>
+      </c>
+      <c r="W59">
+        <v>0.2318270108244337</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.146000610878691</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1953600147915127</v>
+      </c>
+      <c r="C60">
+        <v>-554.0141072436934</v>
+      </c>
+      <c r="D60">
+        <v>550.7198927563064</v>
+      </c>
+      <c r="E60">
+        <v>1006.134</v>
+      </c>
+      <c r="F60">
+        <v>1123.634</v>
+      </c>
+      <c r="G60">
+        <v>18.9</v>
+      </c>
+      <c r="H60">
+        <v>1819.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K60">
+        <v>30</v>
+      </c>
+      <c r="L60">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M60">
+        <v>268.3237991999999</v>
+      </c>
+      <c r="N60">
+        <v>-229.8237991999999</v>
+      </c>
+      <c r="O60">
+        <v>-45.96475983999999</v>
+      </c>
+      <c r="P60">
+        <v>-183.8590393599999</v>
+      </c>
+      <c r="Q60">
+        <v>-153.8590393599999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1448348062418701</v>
+      </c>
+      <c r="T60">
+        <v>1.882936448379749</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02869667179339789</v>
+      </c>
+      <c r="W60">
+        <v>0.2319472347757366</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1434833589669895</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1973600147915127</v>
+      </c>
+      <c r="C61">
+        <v>-580.3336239109684</v>
+      </c>
+      <c r="D61">
+        <v>543.7733760890314</v>
+      </c>
+      <c r="E61">
+        <v>1025.507</v>
+      </c>
+      <c r="F61">
+        <v>1143.007</v>
+      </c>
+      <c r="G61">
+        <v>18.9</v>
+      </c>
+      <c r="H61">
+        <v>1819.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K61">
+        <v>30</v>
+      </c>
+      <c r="L61">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M61">
+        <v>272.9500716</v>
+      </c>
+      <c r="N61">
+        <v>-234.4500716</v>
+      </c>
+      <c r="O61">
+        <v>-46.89001432000001</v>
+      </c>
+      <c r="P61">
+        <v>-187.56005728</v>
+      </c>
+      <c r="Q61">
+        <v>-157.56005728</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1474210210282572</v>
+      </c>
+      <c r="T61">
+        <v>1.928861727608524</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02821028752571317</v>
+      </c>
+      <c r="W61">
+        <v>0.2320633833388597</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1410514376285659</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1993600147915127</v>
+      </c>
+      <c r="C62">
+        <v>-606.4800833777617</v>
+      </c>
+      <c r="D62">
+        <v>536.9999166222382</v>
+      </c>
+      <c r="E62">
+        <v>1044.88</v>
+      </c>
+      <c r="F62">
+        <v>1162.38</v>
+      </c>
+      <c r="G62">
+        <v>18.9</v>
+      </c>
+      <c r="H62">
+        <v>1819.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K62">
+        <v>30</v>
+      </c>
+      <c r="L62">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M62">
+        <v>277.576344</v>
+      </c>
+      <c r="N62">
+        <v>-239.076344</v>
+      </c>
+      <c r="O62">
+        <v>-47.81526880000001</v>
+      </c>
+      <c r="P62">
+        <v>-191.2610752</v>
+      </c>
+      <c r="Q62">
+        <v>-161.2610752</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1501365465539636</v>
+      </c>
+      <c r="T62">
+        <v>1.977083270798737</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02774011606695129</v>
+      </c>
+      <c r="W62">
+        <v>0.232175660283212</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1387005803347565</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2013600147915127</v>
+      </c>
+      <c r="C63">
+        <v>-632.4598730893763</v>
+      </c>
+      <c r="D63">
+        <v>530.3931269106237</v>
+      </c>
+      <c r="E63">
+        <v>1064.253</v>
+      </c>
+      <c r="F63">
+        <v>1181.753</v>
+      </c>
+      <c r="G63">
+        <v>18.9</v>
+      </c>
+      <c r="H63">
+        <v>1819.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K63">
+        <v>30</v>
+      </c>
+      <c r="L63">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M63">
+        <v>282.2026164</v>
+      </c>
+      <c r="N63">
+        <v>-243.7026164</v>
+      </c>
+      <c r="O63">
+        <v>-48.74052328000001</v>
+      </c>
+      <c r="P63">
+        <v>-194.96209312</v>
+      </c>
+      <c r="Q63">
+        <v>-164.96209312</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.152991329798937</v>
+      </c>
+      <c r="T63">
+        <v>2.02777771363973</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02728536006585373</v>
+      </c>
+      <c r="W63">
+        <v>0.2322842560162741</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1364268003292687</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2033600147915127</v>
+      </c>
+      <c r="C64">
+        <v>-658.2790699687654</v>
+      </c>
+      <c r="D64">
+        <v>523.9469300312346</v>
+      </c>
+      <c r="E64">
+        <v>1083.626</v>
+      </c>
+      <c r="F64">
+        <v>1201.126</v>
+      </c>
+      <c r="G64">
+        <v>18.9</v>
+      </c>
+      <c r="H64">
+        <v>1819.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K64">
+        <v>30</v>
+      </c>
+      <c r="L64">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M64">
+        <v>286.8288888</v>
+      </c>
+      <c r="N64">
+        <v>-248.3288888</v>
+      </c>
+      <c r="O64">
+        <v>-49.66577776</v>
+      </c>
+      <c r="P64">
+        <v>-198.66311104</v>
+      </c>
+      <c r="Q64">
+        <v>-168.66311104</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1559963647936459</v>
+      </c>
+      <c r="T64">
+        <v>2.081140285051302</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02684527361317866</v>
+      </c>
+      <c r="W64">
+        <v>0.2323893486611729</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1342263680658934</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2053600147915127</v>
+      </c>
+      <c r="C65">
+        <v>-683.9434590598036</v>
+      </c>
+      <c r="D65">
+        <v>517.6555409401965</v>
+      </c>
+      <c r="E65">
+        <v>1102.999</v>
+      </c>
+      <c r="F65">
+        <v>1220.499</v>
+      </c>
+      <c r="G65">
+        <v>18.9</v>
+      </c>
+      <c r="H65">
+        <v>1819.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K65">
+        <v>30</v>
+      </c>
+      <c r="L65">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M65">
+        <v>291.4551612</v>
+      </c>
+      <c r="N65">
+        <v>-252.9551612</v>
+      </c>
+      <c r="O65">
+        <v>-50.59103224</v>
+      </c>
+      <c r="P65">
+        <v>-202.36412896</v>
+      </c>
+      <c r="Q65">
+        <v>-172.36412896</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1591638341123931</v>
+      </c>
+      <c r="T65">
+        <v>2.137387319782418</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02641915815900122</v>
+      </c>
+      <c r="W65">
+        <v>0.2324911050316305</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1320957907950061</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2073600147915127</v>
+      </c>
+      <c r="C66">
+        <v>-709.4585508433202</v>
+      </c>
+      <c r="D66">
+        <v>511.5134491566799</v>
+      </c>
+      <c r="E66">
+        <v>1122.372</v>
+      </c>
+      <c r="F66">
+        <v>1239.872</v>
+      </c>
+      <c r="G66">
+        <v>18.9</v>
+      </c>
+      <c r="H66">
+        <v>1819.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K66">
+        <v>30</v>
+      </c>
+      <c r="L66">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M66">
+        <v>296.0814336</v>
+      </c>
+      <c r="N66">
+        <v>-257.5814336</v>
+      </c>
+      <c r="O66">
+        <v>-51.51628672000001</v>
+      </c>
+      <c r="P66">
+        <v>-206.06514688</v>
+      </c>
+      <c r="Q66">
+        <v>-176.06514688</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1625072739488485</v>
+      </c>
+      <c r="T66">
+        <v>2.196759189776374</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02600635881276683</v>
+      </c>
+      <c r="W66">
+        <v>0.2325896815155113</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1300317940638341</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2093600147915127</v>
+      </c>
+      <c r="C67">
+        <v>-734.8295973348373</v>
+      </c>
+      <c r="D67">
+        <v>505.5154026651628</v>
+      </c>
+      <c r="E67">
+        <v>1141.745</v>
+      </c>
+      <c r="F67">
+        <v>1259.245</v>
+      </c>
+      <c r="G67">
+        <v>18.9</v>
+      </c>
+      <c r="H67">
+        <v>1819.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K67">
+        <v>30</v>
+      </c>
+      <c r="L67">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M67">
+        <v>300.707706</v>
+      </c>
+      <c r="N67">
+        <v>-262.207706</v>
+      </c>
+      <c r="O67">
+        <v>-52.44154120000001</v>
+      </c>
+      <c r="P67">
+        <v>-209.7661648</v>
+      </c>
+      <c r="Q67">
+        <v>-179.7661648</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1660417674902442</v>
+      </c>
+      <c r="T67">
+        <v>2.2595237380557</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02560626098487811</v>
+      </c>
+      <c r="W67">
+        <v>0.2326852248768111</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1280313049243906</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2113600147915127</v>
+      </c>
+      <c r="C68">
+        <v>-760.061607062855</v>
+      </c>
+      <c r="D68">
+        <v>499.6563929371449</v>
+      </c>
+      <c r="E68">
+        <v>1161.118</v>
+      </c>
+      <c r="F68">
+        <v>1278.618</v>
+      </c>
+      <c r="G68">
+        <v>18.9</v>
+      </c>
+      <c r="H68">
+        <v>1819.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K68">
+        <v>30</v>
+      </c>
+      <c r="L68">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M68">
+        <v>305.3339784</v>
+      </c>
+      <c r="N68">
+        <v>-266.8339784</v>
+      </c>
+      <c r="O68">
+        <v>-53.36679568</v>
+      </c>
+      <c r="P68">
+        <v>-213.46718272</v>
+      </c>
+      <c r="Q68">
+        <v>-183.46718272</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1697841724164278</v>
+      </c>
+      <c r="T68">
+        <v>2.325980318586749</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02521828733359208</v>
+      </c>
+      <c r="W68">
+        <v>0.2327778729847382</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1260914366679604</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2133600147915127</v>
+      </c>
+      <c r="C69">
+        <v>-785.1593590174639</v>
+      </c>
+      <c r="D69">
+        <v>493.9316409825361</v>
+      </c>
+      <c r="E69">
+        <v>1180.491</v>
+      </c>
+      <c r="F69">
+        <v>1297.991</v>
+      </c>
+      <c r="G69">
+        <v>18.9</v>
+      </c>
+      <c r="H69">
+        <v>1819.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K69">
+        <v>30</v>
+      </c>
+      <c r="L69">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M69">
+        <v>309.9602508</v>
+      </c>
+      <c r="N69">
+        <v>-271.4602508</v>
+      </c>
+      <c r="O69">
+        <v>-54.29205016000001</v>
+      </c>
+      <c r="P69">
+        <v>-217.16820064</v>
+      </c>
+      <c r="Q69">
+        <v>-187.16820064</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1737533897623802</v>
+      </c>
+      <c r="T69">
+        <v>2.396464570665136</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02484189498532951</v>
+      </c>
+      <c r="W69">
+        <v>0.2328677554775033</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1242094749266476</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2153600147915127</v>
+      </c>
+      <c r="C70">
+        <v>-810.1274156509355</v>
+      </c>
+      <c r="D70">
+        <v>488.3365843490645</v>
+      </c>
+      <c r="E70">
+        <v>1199.864</v>
+      </c>
+      <c r="F70">
+        <v>1317.364</v>
+      </c>
+      <c r="G70">
+        <v>18.9</v>
+      </c>
+      <c r="H70">
+        <v>1819.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K70">
+        <v>30</v>
+      </c>
+      <c r="L70">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M70">
+        <v>314.5865232</v>
+      </c>
+      <c r="N70">
+        <v>-276.0865232</v>
+      </c>
+      <c r="O70">
+        <v>-55.21730464000001</v>
+      </c>
+      <c r="P70">
+        <v>-220.86921856</v>
+      </c>
+      <c r="Q70">
+        <v>-190.86921856</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1779706831924545</v>
+      </c>
+      <c r="T70">
+        <v>2.471354088498421</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02447657300025113</v>
+      </c>
+      <c r="W70">
+        <v>0.23295499436754</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1223828650012557</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2173600147915127</v>
+      </c>
+      <c r="C71">
+        <v>-834.9701350046134</v>
+      </c>
+      <c r="D71">
+        <v>482.8668649953866</v>
+      </c>
+      <c r="E71">
+        <v>1219.237</v>
+      </c>
+      <c r="F71">
+        <v>1336.737</v>
+      </c>
+      <c r="G71">
+        <v>18.9</v>
+      </c>
+      <c r="H71">
+        <v>1819.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K71">
+        <v>30</v>
+      </c>
+      <c r="L71">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M71">
+        <v>319.2127956</v>
+      </c>
+      <c r="N71">
+        <v>-280.7127956</v>
+      </c>
+      <c r="O71">
+        <v>-56.14255912000002</v>
+      </c>
+      <c r="P71">
+        <v>-224.57023648</v>
+      </c>
+      <c r="Q71">
+        <v>-194.57023648</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1824600600696305</v>
+      </c>
+      <c r="T71">
+        <v>2.551075188127403</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0241218400582185</v>
+      </c>
+      <c r="W71">
+        <v>0.2330397045940974</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1206092002910926</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2193600147915127</v>
+      </c>
+      <c r="C72">
+        <v>-859.6916820298554</v>
+      </c>
+      <c r="D72">
+        <v>477.5183179701447</v>
+      </c>
+      <c r="E72">
+        <v>1238.61</v>
+      </c>
+      <c r="F72">
+        <v>1356.11</v>
+      </c>
+      <c r="G72">
+        <v>18.9</v>
+      </c>
+      <c r="H72">
+        <v>1819.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K72">
+        <v>30</v>
+      </c>
+      <c r="L72">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M72">
+        <v>323.8390680000001</v>
+      </c>
+      <c r="N72">
+        <v>-285.3390680000001</v>
+      </c>
+      <c r="O72">
+        <v>-57.06781360000002</v>
+      </c>
+      <c r="P72">
+        <v>-228.2712544</v>
+      </c>
+      <c r="Q72">
+        <v>-198.2712544</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1872487287386182</v>
+      </c>
+      <c r="T72">
+        <v>2.63611102773165</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0237772423431011</v>
+      </c>
+      <c r="W72">
+        <v>0.2331219945284675</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1188862117155055</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2213600147915127</v>
+      </c>
+      <c r="C73">
+        <v>-884.2960391648279</v>
+      </c>
+      <c r="D73">
+        <v>472.2869608351721</v>
+      </c>
+      <c r="E73">
+        <v>1257.983</v>
+      </c>
+      <c r="F73">
+        <v>1375.483</v>
+      </c>
+      <c r="G73">
+        <v>18.9</v>
+      </c>
+      <c r="H73">
+        <v>1819.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K73">
+        <v>30</v>
+      </c>
+      <c r="L73">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M73">
+        <v>328.4653404</v>
+      </c>
+      <c r="N73">
+        <v>-289.9653404</v>
+      </c>
+      <c r="O73">
+        <v>-57.99306808</v>
+      </c>
+      <c r="P73">
+        <v>-231.97227232</v>
+      </c>
+      <c r="Q73">
+        <v>-201.97227232</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1923676504192602</v>
+      </c>
+      <c r="T73">
+        <v>2.727011407998257</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02344235160587433</v>
+      </c>
+      <c r="W73">
+        <v>0.2332019664365172</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1172117580293717</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2233600147915127</v>
+      </c>
+      <c r="C74">
+        <v>-908.787016223604</v>
+      </c>
+      <c r="D74">
+        <v>467.168983776396</v>
+      </c>
+      <c r="E74">
+        <v>1277.356</v>
+      </c>
+      <c r="F74">
+        <v>1394.856</v>
+      </c>
+      <c r="G74">
+        <v>18.9</v>
+      </c>
+      <c r="H74">
+        <v>1819.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K74">
+        <v>30</v>
+      </c>
+      <c r="L74">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M74">
+        <v>333.0916128</v>
+      </c>
+      <c r="N74">
+        <v>-294.5916128</v>
+      </c>
+      <c r="O74">
+        <v>-58.91832256000001</v>
+      </c>
+      <c r="P74">
+        <v>-235.67329024</v>
+      </c>
+      <c r="Q74">
+        <v>-205.67329024</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1978522093628051</v>
+      </c>
+      <c r="T74">
+        <v>2.824404672569624</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02311676338912607</v>
+      </c>
+      <c r="W74">
+        <v>0.2332797169026767</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1155838169456304</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2253600147915127</v>
+      </c>
+      <c r="C75">
+        <v>-933.1682596491685</v>
+      </c>
+      <c r="D75">
+        <v>462.1607403508316</v>
+      </c>
+      <c r="E75">
+        <v>1296.729</v>
+      </c>
+      <c r="F75">
+        <v>1414.229</v>
+      </c>
+      <c r="G75">
+        <v>18.9</v>
+      </c>
+      <c r="H75">
+        <v>1819.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K75">
+        <v>30</v>
+      </c>
+      <c r="L75">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M75">
+        <v>337.7178852</v>
+      </c>
+      <c r="N75">
+        <v>-299.2178852</v>
+      </c>
+      <c r="O75">
+        <v>-59.84357704000001</v>
+      </c>
+      <c r="P75">
+        <v>-239.37430816</v>
+      </c>
+      <c r="Q75">
+        <v>-209.37430816</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2037430319317979</v>
+      </c>
+      <c r="T75">
+        <v>2.929012253035165</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02280009539749421</v>
+      </c>
+      <c r="W75">
+        <v>0.2333553372190784</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1140004769874711</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2273600147915127</v>
+      </c>
+      <c r="C76">
+        <v>-957.4432611775605</v>
+      </c>
+      <c r="D76">
+        <v>457.2587388224393</v>
+      </c>
+      <c r="E76">
+        <v>1316.102</v>
+      </c>
+      <c r="F76">
+        <v>1433.602</v>
+      </c>
+      <c r="G76">
+        <v>18.9</v>
+      </c>
+      <c r="H76">
+        <v>1819.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K76">
+        <v>30</v>
+      </c>
+      <c r="L76">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M76">
+        <v>342.3441576</v>
+      </c>
+      <c r="N76">
+        <v>-303.8441576</v>
+      </c>
+      <c r="O76">
+        <v>-60.76883151999999</v>
+      </c>
+      <c r="P76">
+        <v>-243.07532608</v>
+      </c>
+      <c r="Q76">
+        <v>-213.07532608</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2100869946984056</v>
+      </c>
+      <c r="T76">
+        <v>3.041666570459595</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02249198600023078</v>
+      </c>
+      <c r="W76">
+        <v>0.2334289137431449</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.112459930001154</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2293600147915127</v>
+      </c>
+      <c r="C77">
+        <v>-981.6153659564166</v>
+      </c>
+      <c r="D77">
+        <v>452.4596340435834</v>
+      </c>
+      <c r="E77">
+        <v>1335.475</v>
+      </c>
+      <c r="F77">
+        <v>1452.975</v>
+      </c>
+      <c r="G77">
+        <v>18.9</v>
+      </c>
+      <c r="H77">
+        <v>1819.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K77">
+        <v>30</v>
+      </c>
+      <c r="L77">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M77">
+        <v>346.97043</v>
+      </c>
+      <c r="N77">
+        <v>-308.47043</v>
+      </c>
+      <c r="O77">
+        <v>-61.69408600000001</v>
+      </c>
+      <c r="P77">
+        <v>-246.776344</v>
+      </c>
+      <c r="Q77">
+        <v>-216.776344</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2169384744863418</v>
+      </c>
+      <c r="T77">
+        <v>3.163333233277978</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02219209285356103</v>
+      </c>
+      <c r="W77">
+        <v>0.2335005282265696</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1109604642678051</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2313600147915127</v>
+      </c>
+      <c r="C78">
+        <v>-1005.687780157579</v>
+      </c>
+      <c r="D78">
+        <v>447.7602198424212</v>
+      </c>
+      <c r="E78">
+        <v>1354.848</v>
+      </c>
+      <c r="F78">
+        <v>1472.348</v>
+      </c>
+      <c r="G78">
+        <v>18.9</v>
+      </c>
+      <c r="H78">
+        <v>1819.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K78">
+        <v>30</v>
+      </c>
+      <c r="L78">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M78">
+        <v>351.5967024</v>
+      </c>
+      <c r="N78">
+        <v>-313.0967024</v>
+      </c>
+      <c r="O78">
+        <v>-62.61934048000001</v>
+      </c>
+      <c r="P78">
+        <v>-250.47736192</v>
+      </c>
+      <c r="Q78">
+        <v>-220.47736192</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2243609109232727</v>
+      </c>
+      <c r="T78">
+        <v>3.295138784664561</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02190009163180365</v>
+      </c>
+      <c r="W78">
+        <v>0.2335702581183253</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1095004581590183</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2333600147915127</v>
+      </c>
+      <c r="C79">
+        <v>-1029.663578120174</v>
+      </c>
+      <c r="D79">
+        <v>443.1574218798261</v>
+      </c>
+      <c r="E79">
+        <v>1374.221</v>
+      </c>
+      <c r="F79">
+        <v>1491.721</v>
+      </c>
+      <c r="G79">
+        <v>18.9</v>
+      </c>
+      <c r="H79">
+        <v>1819.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K79">
+        <v>30</v>
+      </c>
+      <c r="L79">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M79">
+        <v>356.2229748</v>
+      </c>
+      <c r="N79">
+        <v>-317.7229748</v>
+      </c>
+      <c r="O79">
+        <v>-63.54459496000001</v>
+      </c>
+      <c r="P79">
+        <v>-254.17837984</v>
+      </c>
+      <c r="Q79">
+        <v>-224.17837984</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2324287766155889</v>
+      </c>
+      <c r="T79">
+        <v>3.438405688345629</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02161567485736464</v>
+      </c>
+      <c r="W79">
+        <v>0.2336381768440614</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1080783742868232</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2353600147915127</v>
+      </c>
+      <c r="C80">
+        <v>-1053.545709057612</v>
+      </c>
+      <c r="D80">
+        <v>438.6482909423882</v>
+      </c>
+      <c r="E80">
+        <v>1393.594</v>
+      </c>
+      <c r="F80">
+        <v>1511.094</v>
+      </c>
+      <c r="G80">
+        <v>18.9</v>
+      </c>
+      <c r="H80">
+        <v>1819.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K80">
+        <v>30</v>
+      </c>
+      <c r="L80">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M80">
+        <v>360.8492472</v>
+      </c>
+      <c r="N80">
+        <v>-322.3492472</v>
+      </c>
+      <c r="O80">
+        <v>-64.46984944</v>
+      </c>
+      <c r="P80">
+        <v>-257.87939776</v>
+      </c>
+      <c r="Q80">
+        <v>-227.87939776</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2412300846435703</v>
+      </c>
+      <c r="T80">
+        <v>3.594696855997704</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02133855082073176</v>
+      </c>
+      <c r="W80">
+        <v>0.2337043540640093</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1066927541036589</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2373600147915127</v>
+      </c>
+      <c r="C81">
+        <v>-1077.337003359241</v>
+      </c>
+      <c r="D81">
+        <v>434.2299966407588</v>
+      </c>
+      <c r="E81">
+        <v>1412.967</v>
+      </c>
+      <c r="F81">
+        <v>1530.467</v>
+      </c>
+      <c r="G81">
+        <v>18.9</v>
+      </c>
+      <c r="H81">
+        <v>1819.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K81">
+        <v>30</v>
+      </c>
+      <c r="L81">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M81">
+        <v>365.4755196</v>
+      </c>
+      <c r="N81">
+        <v>-326.9755196</v>
+      </c>
+      <c r="O81">
+        <v>-65.39510392000001</v>
+      </c>
+      <c r="P81">
+        <v>-261.58041568</v>
+      </c>
+      <c r="Q81">
+        <v>-231.58041568</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2508696124837403</v>
+      </c>
+      <c r="T81">
+        <v>3.765872896759499</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02106844258249465</v>
+      </c>
+      <c r="W81">
+        <v>0.2337688559113003</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1053422129124733</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2393600147915127</v>
+      </c>
+      <c r="C82">
+        <v>-1101.040178514963</v>
+      </c>
+      <c r="D82">
+        <v>429.899821485037</v>
+      </c>
+      <c r="E82">
+        <v>1432.34</v>
+      </c>
+      <c r="F82">
+        <v>1549.84</v>
+      </c>
+      <c r="G82">
+        <v>18.9</v>
+      </c>
+      <c r="H82">
+        <v>1819.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K82">
+        <v>30</v>
+      </c>
+      <c r="L82">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M82">
+        <v>370.101792</v>
+      </c>
+      <c r="N82">
+        <v>-331.601792</v>
+      </c>
+      <c r="O82">
+        <v>-66.32035840000002</v>
+      </c>
+      <c r="P82">
+        <v>-265.2814336</v>
+      </c>
+      <c r="Q82">
+        <v>-235.2814336</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2614730931079273</v>
+      </c>
+      <c r="T82">
+        <v>3.954166541597474</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02080508705021346</v>
+      </c>
+      <c r="W82">
+        <v>0.233831745212409</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1040254352510673</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2413600147915127</v>
+      </c>
+      <c r="C83">
+        <v>-1124.657844688862</v>
+      </c>
+      <c r="D83">
+        <v>425.6551553111376</v>
+      </c>
+      <c r="E83">
+        <v>1451.713</v>
+      </c>
+      <c r="F83">
+        <v>1569.213</v>
+      </c>
+      <c r="G83">
+        <v>18.9</v>
+      </c>
+      <c r="H83">
+        <v>1819.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K83">
+        <v>30</v>
+      </c>
+      <c r="L83">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M83">
+        <v>374.7280644</v>
+      </c>
+      <c r="N83">
+        <v>-336.2280644</v>
+      </c>
+      <c r="O83">
+        <v>-67.24561288</v>
+      </c>
+      <c r="P83">
+        <v>-268.98245152</v>
+      </c>
+      <c r="Q83">
+        <v>-238.98245152</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2731927295872919</v>
+      </c>
+      <c r="T83">
+        <v>4.162280570102605</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02054823412366762</v>
+      </c>
+      <c r="W83">
+        <v>0.2338930816912682</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1027411706183381</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2433600147915127</v>
+      </c>
+      <c r="C84">
+        <v>-1148.192509965872</v>
+      </c>
+      <c r="D84">
+        <v>421.4934900341286</v>
+      </c>
+      <c r="E84">
+        <v>1471.086</v>
+      </c>
+      <c r="F84">
+        <v>1588.586</v>
+      </c>
+      <c r="G84">
+        <v>18.9</v>
+      </c>
+      <c r="H84">
+        <v>1819.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K84">
+        <v>30</v>
+      </c>
+      <c r="L84">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M84">
+        <v>379.3543368</v>
+      </c>
+      <c r="N84">
+        <v>-340.8543368</v>
+      </c>
+      <c r="O84">
+        <v>-68.17086736</v>
+      </c>
+      <c r="P84">
+        <v>-272.68346944</v>
+      </c>
+      <c r="Q84">
+        <v>-242.68346944</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.286214547897697</v>
+      </c>
+      <c r="T84">
+        <v>4.393518379552749</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02029764590264728</v>
+      </c>
+      <c r="W84">
+        <v>0.2339529221584478</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1014882295132364</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2453600147915127</v>
+      </c>
+      <c r="C85">
+        <v>-1171.646585293636</v>
+      </c>
+      <c r="D85">
+        <v>417.4124147063645</v>
+      </c>
+      <c r="E85">
+        <v>1490.459</v>
+      </c>
+      <c r="F85">
+        <v>1607.959</v>
+      </c>
+      <c r="G85">
+        <v>18.9</v>
+      </c>
+      <c r="H85">
+        <v>1819.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K85">
+        <v>30</v>
+      </c>
+      <c r="L85">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M85">
+        <v>383.9806092000001</v>
+      </c>
+      <c r="N85">
+        <v>-345.4806092000001</v>
+      </c>
+      <c r="O85">
+        <v>-69.09612184000001</v>
+      </c>
+      <c r="P85">
+        <v>-276.38448736</v>
+      </c>
+      <c r="Q85">
+        <v>-246.38448736</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3007683448328556</v>
+      </c>
+      <c r="T85">
+        <v>4.6519606371735</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02005309595201298</v>
+      </c>
+      <c r="W85">
+        <v>0.2340113206866593</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1002654797600649</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2473600147915127</v>
+      </c>
+      <c r="C86">
+        <v>-1195.022389140036</v>
+      </c>
+      <c r="D86">
+        <v>413.4096108599641</v>
+      </c>
+      <c r="E86">
+        <v>1509.832</v>
+      </c>
+      <c r="F86">
+        <v>1627.332</v>
+      </c>
+      <c r="G86">
+        <v>18.9</v>
+      </c>
+      <c r="H86">
+        <v>1819.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K86">
+        <v>30</v>
+      </c>
+      <c r="L86">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M86">
+        <v>388.6068816</v>
+      </c>
+      <c r="N86">
+        <v>-350.1068816</v>
+      </c>
+      <c r="O86">
+        <v>-70.02137632</v>
+      </c>
+      <c r="P86">
+        <v>-280.08550528</v>
+      </c>
+      <c r="Q86">
+        <v>-250.08550528</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.317141366384909</v>
+      </c>
+      <c r="T86">
+        <v>4.942708176996842</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01981436861925092</v>
+      </c>
+      <c r="W86">
+        <v>0.2340683287737229</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.09907184309625461</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2493600147915127</v>
+      </c>
+      <c r="C87">
+        <v>-1218.322151885273</v>
+      </c>
+      <c r="D87">
+        <v>409.4828481147268</v>
+      </c>
+      <c r="E87">
+        <v>1529.205</v>
+      </c>
+      <c r="F87">
+        <v>1646.705</v>
+      </c>
+      <c r="G87">
+        <v>18.9</v>
+      </c>
+      <c r="H87">
+        <v>1819.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K87">
+        <v>30</v>
+      </c>
+      <c r="L87">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M87">
+        <v>393.233154</v>
+      </c>
+      <c r="N87">
+        <v>-354.733154</v>
+      </c>
+      <c r="O87">
+        <v>-70.94663080000001</v>
+      </c>
+      <c r="P87">
+        <v>-283.7865232</v>
+      </c>
+      <c r="Q87">
+        <v>-253.7865232</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3356974574772363</v>
+      </c>
+      <c r="T87">
+        <v>5.272222055463298</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01958125840020091</v>
+      </c>
+      <c r="W87">
+        <v>0.234123995494032</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.09790629200100454</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2513600147915127</v>
+      </c>
+      <c r="C88">
+        <v>-1241.548019966002</v>
+      </c>
+      <c r="D88">
+        <v>405.6299800339979</v>
+      </c>
+      <c r="E88">
+        <v>1548.578</v>
+      </c>
+      <c r="F88">
+        <v>1666.078</v>
+      </c>
+      <c r="G88">
+        <v>18.9</v>
+      </c>
+      <c r="H88">
+        <v>1819.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K88">
+        <v>30</v>
+      </c>
+      <c r="L88">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M88">
+        <v>397.8594264</v>
+      </c>
+      <c r="N88">
+        <v>-359.3594264</v>
+      </c>
+      <c r="O88">
+        <v>-71.87188528</v>
+      </c>
+      <c r="P88">
+        <v>-287.48754112</v>
+      </c>
+      <c r="Q88">
+        <v>-257.48754112</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3569044187256103</v>
+      </c>
+      <c r="T88">
+        <v>5.648809345139248</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01935356934903578</v>
+      </c>
+      <c r="W88">
+        <v>0.2341783676394503</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.09676784674517891</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2533600147915127</v>
+      </c>
+      <c r="C89">
+        <v>-1264.702059787687</v>
+      </c>
+      <c r="D89">
+        <v>401.848940212313</v>
+      </c>
+      <c r="E89">
+        <v>1567.951</v>
+      </c>
+      <c r="F89">
+        <v>1685.451</v>
+      </c>
+      <c r="G89">
+        <v>18.9</v>
+      </c>
+      <c r="H89">
+        <v>1819.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K89">
+        <v>30</v>
+      </c>
+      <c r="L89">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M89">
+        <v>402.4856988</v>
+      </c>
+      <c r="N89">
+        <v>-363.9856988</v>
+      </c>
+      <c r="O89">
+        <v>-72.79713976000001</v>
+      </c>
+      <c r="P89">
+        <v>-291.18855904</v>
+      </c>
+      <c r="Q89">
+        <v>-261.18855904</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3813739893968111</v>
+      </c>
+      <c r="T89">
+        <v>6.08333314091919</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01913111452893192</v>
+      </c>
+      <c r="W89">
+        <v>0.2342314898504911</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.09565557264465963</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2553600147915127</v>
+      </c>
+      <c r="C90">
+        <v>-1287.786261420169</v>
+      </c>
+      <c r="D90">
+        <v>398.1377385798309</v>
+      </c>
+      <c r="E90">
+        <v>1587.324</v>
+      </c>
+      <c r="F90">
+        <v>1704.824</v>
+      </c>
+      <c r="G90">
+        <v>18.9</v>
+      </c>
+      <c r="H90">
+        <v>1819.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K90">
+        <v>30</v>
+      </c>
+      <c r="L90">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M90">
+        <v>407.1119712</v>
+      </c>
+      <c r="N90">
+        <v>-368.6119712</v>
+      </c>
+      <c r="O90">
+        <v>-73.72239424000001</v>
+      </c>
+      <c r="P90">
+        <v>-294.88957696</v>
+      </c>
+      <c r="Q90">
+        <v>-264.88957696</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4099218218465454</v>
+      </c>
+      <c r="T90">
+        <v>6.590277569329123</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01891371550019406</v>
+      </c>
+      <c r="W90">
+        <v>0.2342834047385537</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.09456857750097036</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2573600147915127</v>
+      </c>
+      <c r="C91">
+        <v>-1310.802542090328</v>
+      </c>
+      <c r="D91">
+        <v>394.4944579096715</v>
+      </c>
+      <c r="E91">
+        <v>1606.697</v>
+      </c>
+      <c r="F91">
+        <v>1724.197</v>
+      </c>
+      <c r="G91">
+        <v>18.9</v>
+      </c>
+      <c r="H91">
+        <v>1819.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K91">
+        <v>30</v>
+      </c>
+      <c r="L91">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M91">
+        <v>411.7382436</v>
+      </c>
+      <c r="N91">
+        <v>-373.2382436</v>
+      </c>
+      <c r="O91">
+        <v>-74.64764871999999</v>
+      </c>
+      <c r="P91">
+        <v>-298.59059488</v>
+      </c>
+      <c r="Q91">
+        <v>-268.59059488</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4436601692871405</v>
+      </c>
+      <c r="T91">
+        <v>7.189393711995408</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01870120184288851</v>
+      </c>
+      <c r="W91">
+        <v>0.2343341529999182</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.09350600921444263</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2593600147915127</v>
+      </c>
+      <c r="C92">
+        <v>-1333.75274948472</v>
+      </c>
+      <c r="D92">
+        <v>390.9172505152797</v>
+      </c>
+      <c r="E92">
+        <v>1626.07</v>
+      </c>
+      <c r="F92">
+        <v>1743.57</v>
+      </c>
+      <c r="G92">
+        <v>18.9</v>
+      </c>
+      <c r="H92">
+        <v>1819.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K92">
+        <v>30</v>
+      </c>
+      <c r="L92">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M92">
+        <v>416.364516</v>
+      </c>
+      <c r="N92">
+        <v>-377.864516</v>
+      </c>
+      <c r="O92">
+        <v>-75.5729032</v>
+      </c>
+      <c r="P92">
+        <v>-302.2916128</v>
+      </c>
+      <c r="Q92">
+        <v>-272.2916128</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4841461862158545</v>
+      </c>
+      <c r="T92">
+        <v>7.908333083194949</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01849341071130086</v>
+      </c>
+      <c r="W92">
+        <v>0.2343837735221414</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.09246705355650431</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2613600147915127</v>
+      </c>
+      <c r="C93">
+        <v>-1356.63866487414</v>
+      </c>
+      <c r="D93">
+        <v>387.4043351258602</v>
+      </c>
+      <c r="E93">
+        <v>1645.443</v>
+      </c>
+      <c r="F93">
+        <v>1762.943</v>
+      </c>
+      <c r="G93">
+        <v>18.9</v>
+      </c>
+      <c r="H93">
+        <v>1819.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K93">
+        <v>30</v>
+      </c>
+      <c r="L93">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M93">
+        <v>420.9907884</v>
+      </c>
+      <c r="N93">
+        <v>-382.4907884</v>
+      </c>
+      <c r="O93">
+        <v>-76.49815768000001</v>
+      </c>
+      <c r="P93">
+        <v>-305.99263072</v>
+      </c>
+      <c r="Q93">
+        <v>-275.99263072</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.533629095795394</v>
+      </c>
+      <c r="T93">
+        <v>8.787036759105499</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01829018641777008</v>
+      </c>
+      <c r="W93">
+        <v>0.2344323034834365</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.09145093208885047</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2633600147915127</v>
+      </c>
+      <c r="C94">
+        <v>-1379.462006071218</v>
+      </c>
+      <c r="D94">
+        <v>383.9539939287816</v>
+      </c>
+      <c r="E94">
+        <v>1664.816</v>
+      </c>
+      <c r="F94">
+        <v>1782.316</v>
+      </c>
+      <c r="G94">
+        <v>18.9</v>
+      </c>
+      <c r="H94">
+        <v>1819.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K94">
+        <v>30</v>
+      </c>
+      <c r="L94">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M94">
+        <v>425.6170608</v>
+      </c>
+      <c r="N94">
+        <v>-387.1170608</v>
+      </c>
+      <c r="O94">
+        <v>-77.42341216000001</v>
+      </c>
+      <c r="P94">
+        <v>-309.69364864</v>
+      </c>
+      <c r="Q94">
+        <v>-279.69364864</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5954827327698184</v>
+      </c>
+      <c r="T94">
+        <v>9.885416353993691</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01809138004366388</v>
+      </c>
+      <c r="W94">
+        <v>0.2344797784455731</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.09045690021831942</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2653600147915127</v>
+      </c>
+      <c r="C95">
+        <v>-1402.224430231365</v>
+      </c>
+      <c r="D95">
+        <v>380.5645697686348</v>
+      </c>
+      <c r="E95">
+        <v>1684.189</v>
+      </c>
+      <c r="F95">
+        <v>1801.689</v>
+      </c>
+      <c r="G95">
+        <v>18.9</v>
+      </c>
+      <c r="H95">
+        <v>1819.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K95">
+        <v>30</v>
+      </c>
+      <c r="L95">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M95">
+        <v>430.2433332000001</v>
+      </c>
+      <c r="N95">
+        <v>-391.7433332000001</v>
+      </c>
+      <c r="O95">
+        <v>-78.34866664000002</v>
+      </c>
+      <c r="P95">
+        <v>-313.39466656</v>
+      </c>
+      <c r="Q95">
+        <v>-283.39466656</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6750088374512211</v>
+      </c>
+      <c r="T95">
+        <v>11.2976186902785</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01789684907545244</v>
+      </c>
+      <c r="W95">
+        <v>0.234526232440782</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.08948424537726218</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2673600147915127</v>
+      </c>
+      <c r="C96">
+        <v>-1424.927536506654</v>
+      </c>
+      <c r="D96">
+        <v>377.2344634933464</v>
+      </c>
+      <c r="E96">
+        <v>1703.562</v>
+      </c>
+      <c r="F96">
+        <v>1821.062</v>
+      </c>
+      <c r="G96">
+        <v>18.9</v>
+      </c>
+      <c r="H96">
+        <v>1819.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K96">
+        <v>30</v>
+      </c>
+      <c r="L96">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M96">
+        <v>434.8696056000001</v>
+      </c>
+      <c r="N96">
+        <v>-396.3696056000001</v>
+      </c>
+      <c r="O96">
+        <v>-79.27392112000001</v>
+      </c>
+      <c r="P96">
+        <v>-317.09568448</v>
+      </c>
+      <c r="Q96">
+        <v>-287.09568448</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7810436436930914</v>
+      </c>
+      <c r="T96">
+        <v>13.18055513865826</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01770645706401146</v>
+      </c>
+      <c r="W96">
+        <v>0.2345716980531141</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.0885322853200573</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2693600147915127</v>
+      </c>
+      <c r="C97">
+        <v>-1447.572868561581</v>
+      </c>
+      <c r="D97">
+        <v>373.9621314384194</v>
+      </c>
+      <c r="E97">
+        <v>1722.935</v>
+      </c>
+      <c r="F97">
+        <v>1840.435</v>
+      </c>
+      <c r="G97">
+        <v>18.9</v>
+      </c>
+      <c r="H97">
+        <v>1819.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K97">
+        <v>30</v>
+      </c>
+      <c r="L97">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M97">
+        <v>439.4958780000001</v>
+      </c>
+      <c r="N97">
+        <v>-400.9958780000001</v>
+      </c>
+      <c r="O97">
+        <v>-80.19917560000002</v>
+      </c>
+      <c r="P97">
+        <v>-320.7967024000001</v>
+      </c>
+      <c r="Q97">
+        <v>-290.7967024000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9294923724317103</v>
+      </c>
+      <c r="T97">
+        <v>15.81666616638992</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01752007330544291</v>
+      </c>
+      <c r="W97">
+        <v>0.2346162064946603</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.08760036652721459</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2713600147915127</v>
+      </c>
+      <c r="C98">
+        <v>-1470.161916959012</v>
+      </c>
+      <c r="D98">
+        <v>370.7460830409883</v>
+      </c>
+      <c r="E98">
+        <v>1742.308</v>
+      </c>
+      <c r="F98">
+        <v>1859.808</v>
+      </c>
+      <c r="G98">
+        <v>18.9</v>
+      </c>
+      <c r="H98">
+        <v>1819.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K98">
+        <v>30</v>
+      </c>
+      <c r="L98">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M98">
+        <v>444.1221504</v>
+      </c>
+      <c r="N98">
+        <v>-405.6221504</v>
+      </c>
+      <c r="O98">
+        <v>-81.12443008000001</v>
+      </c>
+      <c r="P98">
+        <v>-324.49772032</v>
+      </c>
+      <c r="Q98">
+        <v>-294.49772032</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.152165465539635</v>
+      </c>
+      <c r="T98">
+        <v>19.77083270798735</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01733757254184455</v>
+      </c>
+      <c r="W98">
+        <v>0.2346597876770075</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.0866878627092228</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2733600147915126</v>
+      </c>
+      <c r="C99">
+        <v>-1492.696121424065</v>
+      </c>
+      <c r="D99">
+        <v>367.5848785759347</v>
+      </c>
+      <c r="E99">
+        <v>1761.681</v>
+      </c>
+      <c r="F99">
+        <v>1879.181</v>
+      </c>
+      <c r="G99">
+        <v>18.9</v>
+      </c>
+      <c r="H99">
+        <v>1819.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K99">
+        <v>30</v>
+      </c>
+      <c r="L99">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M99">
+        <v>448.7484228</v>
+      </c>
+      <c r="N99">
+        <v>-410.2484228</v>
+      </c>
+      <c r="O99">
+        <v>-82.04968456</v>
+      </c>
+      <c r="P99">
+        <v>-328.19873824</v>
+      </c>
+      <c r="Q99">
+        <v>-298.19873824</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.52328728738618</v>
+      </c>
+      <c r="T99">
+        <v>26.36111027731647</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01715883468058843</v>
+      </c>
+      <c r="W99">
+        <v>0.2347024702782755</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.08579417340294215</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2753600147915127</v>
+      </c>
+      <c r="C100">
+        <v>-1515.176872993154</v>
+      </c>
+      <c r="D100">
+        <v>364.4771270068462</v>
+      </c>
+      <c r="E100">
+        <v>1781.054</v>
+      </c>
+      <c r="F100">
+        <v>1898.554</v>
+      </c>
+      <c r="G100">
+        <v>18.9</v>
+      </c>
+      <c r="H100">
+        <v>1819.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K100">
+        <v>30</v>
+      </c>
+      <c r="L100">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M100">
+        <v>453.3746952</v>
+      </c>
+      <c r="N100">
+        <v>-414.8746952</v>
+      </c>
+      <c r="O100">
+        <v>-82.97493904</v>
+      </c>
+      <c r="P100">
+        <v>-331.89975616</v>
+      </c>
+      <c r="Q100">
+        <v>-301.89975616</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.265530931079271</v>
+      </c>
+      <c r="T100">
+        <v>39.54166541597471</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0169837445307865</v>
+      </c>
+      <c r="W100">
+        <v>0.2347442818060482</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.08491872265393252</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2773600147915127</v>
+      </c>
+      <c r="C101">
+        <v>-1537.605516054925</v>
+      </c>
+      <c r="D101">
+        <v>361.4214839450752</v>
+      </c>
+      <c r="E101">
+        <v>1800.427</v>
+      </c>
+      <c r="F101">
+        <v>1917.927</v>
+      </c>
+      <c r="G101">
+        <v>18.9</v>
+      </c>
+      <c r="H101">
+        <v>1819.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>68.49999999999999</v>
+      </c>
+      <c r="K101">
+        <v>30</v>
+      </c>
+      <c r="L101">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="M101">
+        <v>458.0009676</v>
+      </c>
+      <c r="N101">
+        <v>-419.5009676</v>
+      </c>
+      <c r="O101">
+        <v>-83.90019352000002</v>
+      </c>
+      <c r="P101">
+        <v>-335.60077408</v>
+      </c>
+      <c r="Q101">
+        <v>-305.60077408</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.492261862158541</v>
+      </c>
+      <c r="T101">
+        <v>79.08333083194941</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01681219155572805</v>
+      </c>
+      <c r="W101">
+        <v>0.2347852486564922</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.08406095777864031</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_air_transport.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_air_transport.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08705920913303966</v>
+        <v>0.08692109071477358</v>
       </c>
       <c r="C2">
-        <v>2595.856727934788</v>
+        <v>2578.527793562579</v>
       </c>
       <c r="D2">
-        <v>2584.556727934788</v>
+        <v>2593.237793562579</v>
       </c>
       <c r="E2">
-        <v>-42.1</v>
+        <v>-16.09</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.01</v>
       </c>
       <c r="G2">
         <v>11.3</v>
@@ -1457,28 +1457,28 @@
         <v>81.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.308303</v>
       </c>
       <c r="N2">
-        <v>81.2</v>
+        <v>79.89169700000001</v>
       </c>
       <c r="O2">
-        <v>16.24</v>
+        <v>15.9783394</v>
       </c>
       <c r="P2">
-        <v>64.96000000000001</v>
+        <v>63.9133576</v>
       </c>
       <c r="Q2">
-        <v>96.56</v>
+        <v>95.51335760000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08705920913303966</v>
+        <v>0.08739261688360968</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8107175193586469</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>62.06513322984049</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08692109071477358</v>
+        <v>0.0867829722965075</v>
       </c>
       <c r="C3">
-        <v>2578.527793562579</v>
+        <v>2561.257372030518</v>
       </c>
       <c r="D3">
-        <v>2593.237793562579</v>
+        <v>2601.977372030518</v>
       </c>
       <c r="E3">
-        <v>-16.09</v>
+        <v>9.920000000000002</v>
       </c>
       <c r="F3">
-        <v>26.01</v>
+        <v>52.02</v>
       </c>
       <c r="G3">
         <v>11.3</v>
@@ -1539,28 +1539,28 @@
         <v>81.2</v>
       </c>
       <c r="M3">
-        <v>1.308303</v>
+        <v>2.616606</v>
       </c>
       <c r="N3">
-        <v>79.89169700000001</v>
+        <v>78.583394</v>
       </c>
       <c r="O3">
-        <v>15.9783394</v>
+        <v>15.7166788</v>
       </c>
       <c r="P3">
-        <v>63.9133576</v>
+        <v>62.8667152</v>
       </c>
       <c r="Q3">
-        <v>95.51335760000001</v>
+        <v>94.4667152</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08739261688360968</v>
+        <v>0.08773282887398726</v>
       </c>
       <c r="T3">
-        <v>0.8107175193586469</v>
+        <v>0.8173488842873504</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>62.06513322984049</v>
+        <v>31.03256661492024</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0867829722965075</v>
+        <v>0.08664485387824143</v>
       </c>
       <c r="C4">
-        <v>2561.257372030518</v>
+        <v>2544.04605692875</v>
       </c>
       <c r="D4">
-        <v>2601.977372030518</v>
+        <v>2610.77605692875</v>
       </c>
       <c r="E4">
-        <v>9.920000000000002</v>
+        <v>35.93</v>
       </c>
       <c r="F4">
-        <v>52.02</v>
+        <v>78.03</v>
       </c>
       <c r="G4">
         <v>11.3</v>
@@ -1621,28 +1621,28 @@
         <v>81.2</v>
       </c>
       <c r="M4">
-        <v>2.616606</v>
+        <v>3.924909</v>
       </c>
       <c r="N4">
-        <v>78.583394</v>
+        <v>77.275091</v>
       </c>
       <c r="O4">
-        <v>15.7166788</v>
+        <v>15.4550182</v>
       </c>
       <c r="P4">
-        <v>62.8667152</v>
+        <v>61.82007280000001</v>
       </c>
       <c r="Q4">
-        <v>94.4667152</v>
+        <v>93.4200728</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08773282887398726</v>
+        <v>0.08808005554457879</v>
       </c>
       <c r="T4">
-        <v>0.8173488842873504</v>
+        <v>0.8241169783898415</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>31.03256661492024</v>
+        <v>20.68837774328016</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08664485387824143</v>
+        <v>0.08650673545997535</v>
       </c>
       <c r="C5">
-        <v>2544.04605692875</v>
+        <v>2526.894449903654</v>
       </c>
       <c r="D5">
-        <v>2610.77605692875</v>
+        <v>2619.634449903654</v>
       </c>
       <c r="E5">
-        <v>35.93</v>
+        <v>61.94</v>
       </c>
       <c r="F5">
-        <v>78.03</v>
+        <v>104.04</v>
       </c>
       <c r="G5">
         <v>11.3</v>
@@ -1703,28 +1703,28 @@
         <v>81.2</v>
       </c>
       <c r="M5">
-        <v>3.924909</v>
+        <v>5.233212</v>
       </c>
       <c r="N5">
-        <v>77.275091</v>
+        <v>75.96678800000001</v>
       </c>
       <c r="O5">
-        <v>15.4550182</v>
+        <v>15.1933576</v>
       </c>
       <c r="P5">
-        <v>61.82007280000001</v>
+        <v>60.77343040000001</v>
       </c>
       <c r="Q5">
-        <v>93.4200728</v>
+        <v>92.3734304</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08808005554457879</v>
+        <v>0.08843451610414099</v>
       </c>
       <c r="T5">
-        <v>0.8241169783898415</v>
+        <v>0.8310260744528014</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.68837774328016</v>
+        <v>15.51628330746012</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08650673545997535</v>
+        <v>0.08642861704170926</v>
       </c>
       <c r="C6">
-        <v>2526.894449903654</v>
+        <v>2505.9213355907</v>
       </c>
       <c r="D6">
-        <v>2619.634449903654</v>
+        <v>2624.6713355907</v>
       </c>
       <c r="E6">
-        <v>61.94</v>
+        <v>87.95000000000002</v>
       </c>
       <c r="F6">
-        <v>104.04</v>
+        <v>130.05</v>
       </c>
       <c r="G6">
         <v>11.3</v>
@@ -1785,45 +1785,45 @@
         <v>81.2</v>
       </c>
       <c r="M6">
-        <v>5.233212</v>
+        <v>6.736590000000001</v>
       </c>
       <c r="N6">
-        <v>75.96678800000001</v>
+        <v>74.46341</v>
       </c>
       <c r="O6">
-        <v>15.1933576</v>
+        <v>14.892682</v>
       </c>
       <c r="P6">
-        <v>60.77343040000001</v>
+        <v>59.570728</v>
       </c>
       <c r="Q6">
-        <v>92.3734304</v>
+        <v>91.170728</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08843451610414099</v>
+        <v>0.0887964389912729</v>
       </c>
       <c r="T6">
-        <v>0.8310260744528014</v>
+        <v>0.8380806251697182</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>15.51628330746012</v>
+        <v>12.0535760674169</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08642861704170926</v>
+        <v>0.08630249862344318</v>
       </c>
       <c r="C7">
-        <v>2505.9213355907</v>
+        <v>2488.084149825953</v>
       </c>
       <c r="D7">
-        <v>2624.6713355907</v>
+        <v>2632.844149825953</v>
       </c>
       <c r="E7">
-        <v>87.95000000000002</v>
+        <v>113.96</v>
       </c>
       <c r="F7">
-        <v>130.05</v>
+        <v>156.06</v>
       </c>
       <c r="G7">
         <v>11.3</v>
@@ -1867,28 +1867,28 @@
         <v>81.2</v>
       </c>
       <c r="M7">
-        <v>6.736590000000001</v>
+        <v>8.083907999999999</v>
       </c>
       <c r="N7">
-        <v>74.46341</v>
+        <v>73.11609200000001</v>
       </c>
       <c r="O7">
-        <v>14.892682</v>
+        <v>14.6232184</v>
       </c>
       <c r="P7">
-        <v>59.570728</v>
+        <v>58.49287360000001</v>
       </c>
       <c r="Q7">
-        <v>91.170728</v>
+        <v>90.0928736</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0887964389912729</v>
+        <v>0.08916606236536509</v>
       </c>
       <c r="T7">
-        <v>0.8380806251697182</v>
+        <v>0.8452852727103992</v>
       </c>
       <c r="U7">
         <v>0.0518</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.0535760674169</v>
+        <v>10.04464672284742</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08630249862344318</v>
+        <v>0.08627158020517711</v>
       </c>
       <c r="C8">
-        <v>2488.084149825953</v>
+        <v>2464.085521169523</v>
       </c>
       <c r="D8">
-        <v>2632.844149825953</v>
+        <v>2634.855521169523</v>
       </c>
       <c r="E8">
-        <v>113.96</v>
+        <v>139.97</v>
       </c>
       <c r="F8">
-        <v>156.06</v>
+        <v>182.07</v>
       </c>
       <c r="G8">
         <v>11.3</v>
@@ -1949,45 +1949,45 @@
         <v>81.2</v>
       </c>
       <c r="M8">
-        <v>8.083907999999999</v>
+        <v>9.740744999999999</v>
       </c>
       <c r="N8">
-        <v>73.11609200000001</v>
+        <v>71.459255</v>
       </c>
       <c r="O8">
-        <v>14.6232184</v>
+        <v>14.291851</v>
       </c>
       <c r="P8">
-        <v>58.49287360000001</v>
+        <v>57.167404</v>
       </c>
       <c r="Q8">
-        <v>90.0928736</v>
+        <v>88.767404</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08916606236536509</v>
+        <v>0.0895436346292227</v>
       </c>
       <c r="T8">
-        <v>0.8452852727103992</v>
+        <v>0.8526448589078691</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.04464672284742</v>
+        <v>8.336118027933182</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0862715802051771</v>
+        <v>0.08621026178691103</v>
       </c>
       <c r="C9">
-        <v>2464.085521169524</v>
+        <v>2442.073643571445</v>
       </c>
       <c r="D9">
-        <v>2634.855521169524</v>
+        <v>2638.853643571445</v>
       </c>
       <c r="E9">
-        <v>139.97</v>
+        <v>165.98</v>
       </c>
       <c r="F9">
-        <v>182.07</v>
+        <v>208.08</v>
       </c>
       <c r="G9">
         <v>11.3</v>
@@ -2031,45 +2031,45 @@
         <v>81.2</v>
       </c>
       <c r="M9">
-        <v>9.740745</v>
+        <v>11.298744</v>
       </c>
       <c r="N9">
-        <v>71.459255</v>
+        <v>69.901256</v>
       </c>
       <c r="O9">
-        <v>14.291851</v>
+        <v>13.9802512</v>
       </c>
       <c r="P9">
-        <v>57.167404</v>
+        <v>55.92100480000001</v>
       </c>
       <c r="Q9">
-        <v>88.767404</v>
+        <v>87.5210048</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0895436346292227</v>
+        <v>0.08992941498577287</v>
       </c>
       <c r="T9">
-        <v>0.8526448589078691</v>
+        <v>0.8601644361096318</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.336118027933182</v>
+        <v>7.186639506125636</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08621026178691103</v>
+        <v>0.08610414336864494</v>
       </c>
       <c r="C10">
-        <v>2442.073643571445</v>
+        <v>2423.011588653175</v>
       </c>
       <c r="D10">
-        <v>2638.853643571445</v>
+        <v>2645.801588653175</v>
       </c>
       <c r="E10">
-        <v>165.98</v>
+        <v>191.99</v>
       </c>
       <c r="F10">
-        <v>208.08</v>
+        <v>234.09</v>
       </c>
       <c r="G10">
         <v>11.3</v>
@@ -2113,28 +2113,28 @@
         <v>81.2</v>
       </c>
       <c r="M10">
-        <v>11.298744</v>
+        <v>12.711087</v>
       </c>
       <c r="N10">
-        <v>69.901256</v>
+        <v>68.488913</v>
       </c>
       <c r="O10">
-        <v>13.9802512</v>
+        <v>13.6977826</v>
       </c>
       <c r="P10">
-        <v>55.92100480000001</v>
+        <v>54.7911304</v>
       </c>
       <c r="Q10">
-        <v>87.5210048</v>
+        <v>86.39113039999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08992941498577287</v>
+        <v>0.09032367403147795</v>
       </c>
       <c r="T10">
-        <v>0.8601644361096318</v>
+        <v>0.8678492787444001</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.186639506125636</v>
+        <v>6.388124005445009</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08610414336864494</v>
+        <v>0.08607802495037886</v>
       </c>
       <c r="C11">
-        <v>2423.011588653175</v>
+        <v>2398.71726742905</v>
       </c>
       <c r="D11">
-        <v>2645.801588653175</v>
+        <v>2647.517267429049</v>
       </c>
       <c r="E11">
-        <v>191.99</v>
+        <v>218</v>
       </c>
       <c r="F11">
-        <v>234.09</v>
+        <v>260.1</v>
       </c>
       <c r="G11">
         <v>11.3</v>
@@ -2195,45 +2195,45 @@
         <v>81.2</v>
       </c>
       <c r="M11">
-        <v>12.711087</v>
+        <v>14.38353</v>
       </c>
       <c r="N11">
-        <v>68.488913</v>
+        <v>66.81647000000001</v>
       </c>
       <c r="O11">
-        <v>13.6977826</v>
+        <v>13.363294</v>
       </c>
       <c r="P11">
-        <v>54.7911304</v>
+        <v>53.45317600000001</v>
       </c>
       <c r="Q11">
-        <v>86.39113039999999</v>
+        <v>85.05317600000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09032367403147795</v>
+        <v>0.09072669438930984</v>
       </c>
       <c r="T11">
-        <v>0.8678492787444001</v>
+        <v>0.8757048956599411</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.388124005445009</v>
+        <v>5.645345753093991</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08607802495037888</v>
+        <v>0.08597990653211279</v>
       </c>
       <c r="C12">
-        <v>2398.717267429049</v>
+        <v>2379.172444405124</v>
       </c>
       <c r="D12">
-        <v>2647.517267429048</v>
+        <v>2653.982444405124</v>
       </c>
       <c r="E12">
-        <v>218</v>
+        <v>244.01</v>
       </c>
       <c r="F12">
-        <v>260.1</v>
+        <v>286.11</v>
       </c>
       <c r="G12">
         <v>11.3</v>
@@ -2277,28 +2277,28 @@
         <v>81.2</v>
       </c>
       <c r="M12">
-        <v>14.38353</v>
+        <v>15.821883</v>
       </c>
       <c r="N12">
-        <v>66.81647</v>
+        <v>65.378117</v>
       </c>
       <c r="O12">
-        <v>13.363294</v>
+        <v>13.0756234</v>
       </c>
       <c r="P12">
-        <v>53.453176</v>
+        <v>52.30249360000001</v>
       </c>
       <c r="Q12">
-        <v>85.05317599999999</v>
+        <v>83.9024936</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09072669438930986</v>
+        <v>0.09113877138439638</v>
       </c>
       <c r="T12">
-        <v>0.8757048956599414</v>
+        <v>0.8837370432926854</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.645345753093989</v>
+        <v>5.132132502812718</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08597990653211279</v>
+        <v>0.08588178811384671</v>
       </c>
       <c r="C13">
-        <v>2379.172444405124</v>
+        <v>2359.659274307307</v>
       </c>
       <c r="D13">
-        <v>2653.982444405124</v>
+        <v>2660.479274307306</v>
       </c>
       <c r="E13">
-        <v>244.01</v>
+        <v>270.02</v>
       </c>
       <c r="F13">
-        <v>286.11</v>
+        <v>312.12</v>
       </c>
       <c r="G13">
         <v>11.3</v>
@@ -2359,28 +2359,28 @@
         <v>81.2</v>
       </c>
       <c r="M13">
-        <v>15.821883</v>
+        <v>17.260236</v>
       </c>
       <c r="N13">
-        <v>65.378117</v>
+        <v>63.939764</v>
       </c>
       <c r="O13">
-        <v>13.0756234</v>
+        <v>12.7879528</v>
       </c>
       <c r="P13">
-        <v>52.30249360000001</v>
+        <v>51.1518112</v>
       </c>
       <c r="Q13">
-        <v>83.9024936</v>
+        <v>82.75181119999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09113877138439638</v>
+        <v>0.09156021376573489</v>
       </c>
       <c r="T13">
-        <v>0.8837370432926854</v>
+        <v>0.8919517397352649</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.132132502812718</v>
+        <v>4.704454794244992</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08588178811384671</v>
+        <v>0.08604366969558061</v>
       </c>
       <c r="C14">
-        <v>2359.659274307307</v>
+        <v>2322.947402525906</v>
       </c>
       <c r="D14">
-        <v>2660.479274307306</v>
+        <v>2649.777402525906</v>
       </c>
       <c r="E14">
-        <v>270.02</v>
+        <v>296.03</v>
       </c>
       <c r="F14">
-        <v>312.12</v>
+        <v>338.13</v>
       </c>
       <c r="G14">
         <v>11.3</v>
@@ -2441,45 +2441,45 @@
         <v>81.2</v>
       </c>
       <c r="M14">
-        <v>17.260236</v>
+        <v>19.543914</v>
       </c>
       <c r="N14">
-        <v>63.939764</v>
+        <v>61.656086</v>
       </c>
       <c r="O14">
-        <v>12.7879528</v>
+        <v>12.3312172</v>
       </c>
       <c r="P14">
-        <v>51.1518112</v>
+        <v>49.3248688</v>
       </c>
       <c r="Q14">
-        <v>82.75181119999999</v>
+        <v>80.9248688</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09156021376573489</v>
+        <v>0.09199134447767887</v>
       </c>
       <c r="T14">
-        <v>0.8919517397352649</v>
+        <v>0.9003552797742252</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.704454794244992</v>
+        <v>4.154746075939548</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08604366969558061</v>
+        <v>0.08635755127731455</v>
       </c>
       <c r="C15">
-        <v>2322.947402525906</v>
+        <v>2276.430337968167</v>
       </c>
       <c r="D15">
-        <v>2649.777402525906</v>
+        <v>2629.270337968167</v>
       </c>
       <c r="E15">
-        <v>296.03</v>
+        <v>322.04</v>
       </c>
       <c r="F15">
-        <v>338.13</v>
+        <v>364.14</v>
       </c>
       <c r="G15">
         <v>11.3</v>
@@ -2523,45 +2523,45 @@
         <v>81.2</v>
       </c>
       <c r="M15">
-        <v>19.543914</v>
+        <v>22.321782</v>
       </c>
       <c r="N15">
-        <v>61.656086</v>
+        <v>58.878218</v>
       </c>
       <c r="O15">
-        <v>12.3312172</v>
+        <v>11.7756436</v>
       </c>
       <c r="P15">
-        <v>49.3248688</v>
+        <v>47.1025744</v>
       </c>
       <c r="Q15">
-        <v>80.9248688</v>
+        <v>78.7025744</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09199134447767887</v>
+        <v>0.09243250148524948</v>
       </c>
       <c r="T15">
-        <v>0.9003552797742252</v>
+        <v>0.9089542509768825</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.154746075939548</v>
+        <v>3.637702402075246</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08635755127731455</v>
+        <v>0.08664343285904848</v>
       </c>
       <c r="C16">
-        <v>2276.430337968167</v>
+        <v>2232.016890696279</v>
       </c>
       <c r="D16">
-        <v>2629.270337968167</v>
+        <v>2610.866890696278</v>
       </c>
       <c r="E16">
-        <v>322.04</v>
+        <v>348.05</v>
       </c>
       <c r="F16">
-        <v>364.14</v>
+        <v>390.15</v>
       </c>
       <c r="G16">
         <v>11.3</v>
@@ -2605,45 +2605,45 @@
         <v>81.2</v>
       </c>
       <c r="M16">
-        <v>22.321782</v>
+        <v>25.008615</v>
       </c>
       <c r="N16">
-        <v>58.878218</v>
+        <v>56.191385</v>
       </c>
       <c r="O16">
-        <v>11.7756436</v>
+        <v>11.238277</v>
       </c>
       <c r="P16">
-        <v>47.1025744</v>
+        <v>44.953108</v>
       </c>
       <c r="Q16">
-        <v>78.7025744</v>
+        <v>76.55310799999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09243250148524948</v>
+        <v>0.09288403865770409</v>
       </c>
       <c r="T16">
-        <v>0.9089542509768825</v>
+        <v>0.9177555509137199</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.637702402075246</v>
+        <v>3.246881124764406</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08664343285904848</v>
+        <v>0.08661571444078238</v>
       </c>
       <c r="C17">
-        <v>2232.016890696279</v>
+        <v>2207.779960248165</v>
       </c>
       <c r="D17">
-        <v>2610.866890696278</v>
+        <v>2612.639960248164</v>
       </c>
       <c r="E17">
-        <v>348.05</v>
+        <v>374.06</v>
       </c>
       <c r="F17">
-        <v>390.15</v>
+        <v>416.16</v>
       </c>
       <c r="G17">
         <v>11.3</v>
@@ -2687,28 +2687,28 @@
         <v>81.2</v>
       </c>
       <c r="M17">
-        <v>25.008615</v>
+        <v>26.675856</v>
       </c>
       <c r="N17">
-        <v>56.191385</v>
+        <v>54.524144</v>
       </c>
       <c r="O17">
-        <v>11.238277</v>
+        <v>10.9048288</v>
       </c>
       <c r="P17">
-        <v>44.953108</v>
+        <v>43.6193152</v>
       </c>
       <c r="Q17">
-        <v>76.55310799999999</v>
+        <v>75.2193152</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09288403865770409</v>
+        <v>0.09334632671521713</v>
       </c>
       <c r="T17">
-        <v>0.9177555509137199</v>
+        <v>0.9267664056109581</v>
       </c>
       <c r="U17">
         <v>0.0641</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.246881124764406</v>
+        <v>3.043951054466631</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08661571444078238</v>
+        <v>0.08764879602251631</v>
       </c>
       <c r="C18">
-        <v>2207.779960248165</v>
+        <v>2117.274192647533</v>
       </c>
       <c r="D18">
-        <v>2612.639960248164</v>
+        <v>2548.144192647533</v>
       </c>
       <c r="E18">
-        <v>374.06</v>
+        <v>400.07</v>
       </c>
       <c r="F18">
-        <v>416.16</v>
+        <v>442.17</v>
       </c>
       <c r="G18">
         <v>11.3</v>
@@ -2769,45 +2769,45 @@
         <v>81.2</v>
       </c>
       <c r="M18">
-        <v>26.675856</v>
+        <v>31.792023</v>
       </c>
       <c r="N18">
-        <v>54.524144</v>
+        <v>49.407977</v>
       </c>
       <c r="O18">
-        <v>10.9048288</v>
+        <v>9.881595400000002</v>
       </c>
       <c r="P18">
-        <v>43.6193152</v>
+        <v>39.5263816</v>
       </c>
       <c r="Q18">
-        <v>75.2193152</v>
+        <v>71.1263816</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09334632671521713</v>
+        <v>0.09381975424399555</v>
       </c>
       <c r="T18">
-        <v>0.9267664056109581</v>
+        <v>0.9359943893370456</v>
       </c>
       <c r="U18">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.043951054466631</v>
+        <v>2.554099813025425</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08764879602251631</v>
+        <v>0.08824507760425022</v>
       </c>
       <c r="C19">
-        <v>2117.274192647533</v>
+        <v>2055.467074690896</v>
       </c>
       <c r="D19">
-        <v>2548.144192647533</v>
+        <v>2512.347074690896</v>
       </c>
       <c r="E19">
-        <v>400.07</v>
+        <v>426.08</v>
       </c>
       <c r="F19">
-        <v>442.17</v>
+        <v>468.1800000000001</v>
       </c>
       <c r="G19">
         <v>11.3</v>
@@ -2851,45 +2851,45 @@
         <v>81.2</v>
       </c>
       <c r="M19">
-        <v>31.792023</v>
+        <v>35.48804400000001</v>
       </c>
       <c r="N19">
-        <v>49.407977</v>
+        <v>45.71195599999999</v>
       </c>
       <c r="O19">
-        <v>9.881595400000002</v>
+        <v>9.142391199999999</v>
       </c>
       <c r="P19">
-        <v>39.5263816</v>
+        <v>36.56956479999999</v>
       </c>
       <c r="Q19">
-        <v>71.1263816</v>
+        <v>68.16956479999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09381975424399555</v>
+        <v>0.09430472878567102</v>
       </c>
       <c r="T19">
-        <v>0.9359943893370456</v>
+        <v>0.9454474458369402</v>
       </c>
       <c r="U19">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.554099813025425</v>
+        <v>2.288094548124433</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08824507760425022</v>
+        <v>0.08831095918598417</v>
       </c>
       <c r="C20">
-        <v>2055.467074690896</v>
+        <v>2025.563551648493</v>
       </c>
       <c r="D20">
-        <v>2512.347074690896</v>
+        <v>2508.453551648493</v>
       </c>
       <c r="E20">
-        <v>426.08</v>
+        <v>452.09</v>
       </c>
       <c r="F20">
-        <v>468.18</v>
+        <v>494.19</v>
       </c>
       <c r="G20">
         <v>11.3</v>
@@ -2933,28 +2933,28 @@
         <v>81.2</v>
       </c>
       <c r="M20">
-        <v>35.488044</v>
+        <v>37.459602</v>
       </c>
       <c r="N20">
-        <v>45.711956</v>
+        <v>43.740398</v>
       </c>
       <c r="O20">
-        <v>9.1423912</v>
+        <v>8.748079600000001</v>
       </c>
       <c r="P20">
-        <v>36.5695648</v>
+        <v>34.9923184</v>
       </c>
       <c r="Q20">
-        <v>68.16956479999999</v>
+        <v>66.5923184</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.094304728785671</v>
+        <v>0.09480167800738784</v>
       </c>
       <c r="T20">
-        <v>0.94544744583694</v>
+        <v>0.9551339111393011</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.288094548124433</v>
+        <v>2.167668519275779</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08831095918598417</v>
+        <v>0.08837684076771808</v>
       </c>
       <c r="C21">
-        <v>2025.563551648493</v>
+        <v>1995.672077948031</v>
       </c>
       <c r="D21">
-        <v>2508.453551648493</v>
+        <v>2504.572077948031</v>
       </c>
       <c r="E21">
-        <v>452.09</v>
+        <v>478.1</v>
       </c>
       <c r="F21">
-        <v>494.19</v>
+        <v>520.2</v>
       </c>
       <c r="G21">
         <v>11.3</v>
@@ -3015,28 +3015,28 @@
         <v>81.2</v>
       </c>
       <c r="M21">
-        <v>37.459602</v>
+        <v>39.43116000000001</v>
       </c>
       <c r="N21">
-        <v>43.740398</v>
+        <v>41.76884</v>
       </c>
       <c r="O21">
-        <v>8.748079600000001</v>
+        <v>8.353768000000001</v>
       </c>
       <c r="P21">
-        <v>34.9923184</v>
+        <v>33.415072</v>
       </c>
       <c r="Q21">
-        <v>66.5923184</v>
+        <v>65.01507199999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09480167800738784</v>
+        <v>0.09531105095964759</v>
       </c>
       <c r="T21">
-        <v>0.9551339111393011</v>
+        <v>0.9650625380742209</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.167668519275779</v>
+        <v>2.059285093311989</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08837684076771808</v>
+        <v>0.09082832234945198</v>
       </c>
       <c r="C22">
-        <v>1995.672077948031</v>
+        <v>1833.305402885512</v>
       </c>
       <c r="D22">
-        <v>2504.572077948031</v>
+        <v>2368.215402885512</v>
       </c>
       <c r="E22">
-        <v>478.1</v>
+        <v>504.11</v>
       </c>
       <c r="F22">
-        <v>520.2</v>
+        <v>546.21</v>
       </c>
       <c r="G22">
         <v>11.3</v>
@@ -3097,45 +3097,45 @@
         <v>81.2</v>
       </c>
       <c r="M22">
-        <v>39.43116000000001</v>
+        <v>49.1589</v>
       </c>
       <c r="N22">
-        <v>41.76884</v>
+        <v>32.0411</v>
       </c>
       <c r="O22">
-        <v>8.353768000000001</v>
+        <v>6.40822</v>
       </c>
       <c r="P22">
-        <v>33.415072</v>
+        <v>25.63288</v>
       </c>
       <c r="Q22">
-        <v>65.01507199999999</v>
+        <v>57.23287999999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09531105095964759</v>
+        <v>0.09583331942968606</v>
       </c>
       <c r="T22">
-        <v>0.9650625380742209</v>
+        <v>0.975242522653063</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.059285093311989</v>
+        <v>1.651786349979353</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09082832234945198</v>
+        <v>0.09100780393118593</v>
       </c>
       <c r="C23">
-        <v>1833.305402885512</v>
+        <v>1797.893241987725</v>
       </c>
       <c r="D23">
-        <v>2368.215402885512</v>
+        <v>2358.813241987725</v>
       </c>
       <c r="E23">
-        <v>504.11</v>
+        <v>530.12</v>
       </c>
       <c r="F23">
-        <v>546.21</v>
+        <v>572.22</v>
       </c>
       <c r="G23">
         <v>11.3</v>
@@ -3179,28 +3179,28 @@
         <v>81.2</v>
       </c>
       <c r="M23">
-        <v>49.1589</v>
+        <v>51.4998</v>
       </c>
       <c r="N23">
-        <v>32.0411</v>
+        <v>29.7002</v>
       </c>
       <c r="O23">
-        <v>6.40822</v>
+        <v>5.940040000000001</v>
       </c>
       <c r="P23">
-        <v>25.63288</v>
+        <v>23.76016</v>
       </c>
       <c r="Q23">
-        <v>57.23287999999999</v>
+        <v>55.36015999999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09583331942968606</v>
+        <v>0.09636897939895631</v>
       </c>
       <c r="T23">
-        <v>0.975242522653063</v>
+        <v>0.9856835324775164</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.651786349979353</v>
+        <v>1.576705152253019</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09100780393118593</v>
+        <v>0.09118728551291985</v>
       </c>
       <c r="C24">
-        <v>1797.893241987725</v>
+        <v>1762.555441770055</v>
       </c>
       <c r="D24">
-        <v>2358.813241987725</v>
+        <v>2349.485441770055</v>
       </c>
       <c r="E24">
-        <v>530.12</v>
+        <v>556.13</v>
       </c>
       <c r="F24">
-        <v>572.22</v>
+        <v>598.23</v>
       </c>
       <c r="G24">
         <v>11.3</v>
@@ -3261,28 +3261,28 @@
         <v>81.2</v>
       </c>
       <c r="M24">
-        <v>51.4998</v>
+        <v>53.8407</v>
       </c>
       <c r="N24">
-        <v>29.7002</v>
+        <v>27.3593</v>
       </c>
       <c r="O24">
-        <v>5.940040000000001</v>
+        <v>5.471860000000001</v>
       </c>
       <c r="P24">
-        <v>23.76016</v>
+        <v>21.88744000000001</v>
       </c>
       <c r="Q24">
-        <v>55.36015999999999</v>
+        <v>53.48744</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09636897939895631</v>
+        <v>0.09691855261418161</v>
       </c>
       <c r="T24">
-        <v>0.9856835324775164</v>
+        <v>0.9963957373623451</v>
       </c>
       <c r="U24">
         <v>0.09</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.576705152253019</v>
+        <v>1.508152754328974</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09118728551291985</v>
+        <v>0.1033006046445109</v>
       </c>
       <c r="C25">
-        <v>1762.555441770055</v>
+        <v>1241.592960363327</v>
       </c>
       <c r="D25">
-        <v>2349.485441770055</v>
+        <v>1854.532960363327</v>
       </c>
       <c r="E25">
-        <v>556.13</v>
+        <v>582.14</v>
       </c>
       <c r="F25">
-        <v>598.23</v>
+        <v>624.24</v>
       </c>
       <c r="G25">
         <v>11.3</v>
@@ -3343,45 +3343,45 @@
         <v>81.2</v>
       </c>
       <c r="M25">
-        <v>53.8407</v>
+        <v>91.63843200000001</v>
       </c>
       <c r="N25">
-        <v>27.3593</v>
+        <v>-10.43843200000001</v>
       </c>
       <c r="O25">
-        <v>5.471860000000001</v>
+        <v>-2.087686400000001</v>
       </c>
       <c r="P25">
-        <v>21.88744000000001</v>
+        <v>-8.350745600000005</v>
       </c>
       <c r="Q25">
-        <v>53.48744</v>
+        <v>23.24925439999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09691855261418161</v>
+        <v>0.09777941716767485</v>
       </c>
       <c r="T25">
-        <v>0.9963957373623451</v>
+        <v>1.013175589836279</v>
       </c>
       <c r="U25">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.2</v>
+        <v>0.1772182221537793</v>
       </c>
       <c r="W25">
-        <v>0.07199999999999999</v>
+        <v>0.1207843649878252</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y25">
-        <v>1.508152754328974</v>
+        <v>0.8860911107688966</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1033006046445109</v>
+        <v>0.1043106046445109</v>
       </c>
       <c r="C26">
-        <v>1241.592960363327</v>
+        <v>1183.570331176753</v>
       </c>
       <c r="D26">
-        <v>1854.532960363327</v>
+        <v>1822.520331176753</v>
       </c>
       <c r="E26">
-        <v>582.14</v>
+        <v>608.15</v>
       </c>
       <c r="F26">
-        <v>624.24</v>
+        <v>650.25</v>
       </c>
       <c r="G26">
         <v>11.3</v>
@@ -3425,37 +3425,37 @@
         <v>81.2</v>
       </c>
       <c r="M26">
-        <v>91.63843200000001</v>
+        <v>95.45670000000001</v>
       </c>
       <c r="N26">
-        <v>-10.43843200000001</v>
+        <v>-14.25670000000001</v>
       </c>
       <c r="O26">
-        <v>-2.087686400000001</v>
+        <v>-2.851340000000002</v>
       </c>
       <c r="P26">
-        <v>-8.350745600000005</v>
+        <v>-11.40536000000001</v>
       </c>
       <c r="Q26">
-        <v>23.24925439999999</v>
+        <v>20.19463999999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09777941716767483</v>
+        <v>0.09847247606324383</v>
       </c>
       <c r="T26">
-        <v>1.013175589836279</v>
+        <v>1.026684597700763</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.1772182221537793</v>
+        <v>0.1701294932676282</v>
       </c>
       <c r="W26">
-        <v>0.1207843649878252</v>
+        <v>0.1218249903883122</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8860911107688966</v>
+        <v>0.8506474663381407</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1043106046445109</v>
+        <v>0.1053206046445109</v>
       </c>
       <c r="C27">
-        <v>1183.570331176753</v>
+        <v>1126.634141070277</v>
       </c>
       <c r="D27">
-        <v>1822.520331176753</v>
+        <v>1791.594141070277</v>
       </c>
       <c r="E27">
-        <v>608.15</v>
+        <v>634.16</v>
       </c>
       <c r="F27">
-        <v>650.25</v>
+        <v>676.26</v>
       </c>
       <c r="G27">
         <v>11.3</v>
@@ -3507,37 +3507,37 @@
         <v>81.2</v>
       </c>
       <c r="M27">
-        <v>95.45670000000001</v>
+        <v>99.274968</v>
       </c>
       <c r="N27">
-        <v>-14.25670000000001</v>
+        <v>-18.074968</v>
       </c>
       <c r="O27">
-        <v>-2.851340000000002</v>
+        <v>-3.6149936</v>
       </c>
       <c r="P27">
-        <v>-11.40536000000001</v>
+        <v>-14.4599744</v>
       </c>
       <c r="Q27">
-        <v>20.19463999999999</v>
+        <v>17.14002559999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09847247606324383</v>
+        <v>0.0991842662803147</v>
       </c>
       <c r="T27">
-        <v>1.026684597700763</v>
+        <v>1.040558713885908</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.1701294932676282</v>
+        <v>0.1635860512188732</v>
       </c>
       <c r="W27">
-        <v>0.1218249903883122</v>
+        <v>0.1227855676810694</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8506474663381407</v>
+        <v>0.8179302560943661</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1053206046445109</v>
+        <v>0.1213825270181303</v>
       </c>
       <c r="C28">
-        <v>1126.634141070277</v>
+        <v>719.8953251099521</v>
       </c>
       <c r="D28">
-        <v>1791.594141070277</v>
+        <v>1410.865325109952</v>
       </c>
       <c r="E28">
-        <v>634.16</v>
+        <v>660.1700000000001</v>
       </c>
       <c r="F28">
-        <v>676.26</v>
+        <v>702.2700000000001</v>
       </c>
       <c r="G28">
         <v>11.3</v>
@@ -3589,45 +3589,45 @@
         <v>81.2</v>
       </c>
       <c r="M28">
-        <v>99.274968</v>
+        <v>141.015816</v>
       </c>
       <c r="N28">
-        <v>-18.074968</v>
+        <v>-59.81581600000003</v>
       </c>
       <c r="O28">
-        <v>-3.6149936</v>
+        <v>-11.96316320000001</v>
       </c>
       <c r="P28">
-        <v>-14.4599744</v>
+        <v>-47.85265280000002</v>
       </c>
       <c r="Q28">
-        <v>17.14002559999999</v>
+        <v>-16.25265280000003</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0991842662803147</v>
+        <v>0.1005620266041811</v>
       </c>
       <c r="T28">
-        <v>1.040558713885908</v>
+        <v>1.067413827022007</v>
       </c>
       <c r="U28">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1635860512188732</v>
+        <v>0.1151643869507517</v>
       </c>
       <c r="W28">
-        <v>0.1227855676810694</v>
+        <v>0.1776749911002891</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.8179302560943661</v>
+        <v>0.5758219347537583</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1213825270181303</v>
+        <v>0.1229325270181303</v>
       </c>
       <c r="C29">
-        <v>719.8953251099521</v>
+        <v>665.5335863758322</v>
       </c>
       <c r="D29">
-        <v>1410.865325109952</v>
+        <v>1382.513586375832</v>
       </c>
       <c r="E29">
-        <v>660.1700000000001</v>
+        <v>686.1800000000001</v>
       </c>
       <c r="F29">
-        <v>702.2700000000001</v>
+        <v>728.2800000000001</v>
       </c>
       <c r="G29">
         <v>11.3</v>
@@ -3671,37 +3671,37 @@
         <v>81.2</v>
       </c>
       <c r="M29">
-        <v>141.015816</v>
+        <v>146.238624</v>
       </c>
       <c r="N29">
-        <v>-59.81581600000003</v>
+        <v>-65.03862400000001</v>
       </c>
       <c r="O29">
-        <v>-11.96316320000001</v>
+        <v>-13.0077248</v>
       </c>
       <c r="P29">
-        <v>-47.85265280000002</v>
+        <v>-52.03089920000001</v>
       </c>
       <c r="Q29">
-        <v>-16.25265280000003</v>
+        <v>-20.43089920000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1005620266041811</v>
+        <v>0.101322610307017</v>
       </c>
       <c r="T29">
-        <v>1.067413827022007</v>
+        <v>1.08223901906398</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.1151643869507517</v>
+        <v>0.111051373131082</v>
       </c>
       <c r="W29">
-        <v>0.1776749911002891</v>
+        <v>0.1785008842752787</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.5758219347537583</v>
+        <v>0.5552568656554098</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1229325270181303</v>
+        <v>0.1244825270181303</v>
       </c>
       <c r="C30">
-        <v>665.5335863758322</v>
+        <v>612.2888731543218</v>
       </c>
       <c r="D30">
-        <v>1382.513586375832</v>
+        <v>1355.278873154322</v>
       </c>
       <c r="E30">
-        <v>686.1800000000001</v>
+        <v>712.1900000000001</v>
       </c>
       <c r="F30">
-        <v>728.2800000000001</v>
+        <v>754.2900000000001</v>
       </c>
       <c r="G30">
         <v>11.3</v>
@@ -3753,37 +3753,37 @@
         <v>81.2</v>
       </c>
       <c r="M30">
-        <v>146.238624</v>
+        <v>151.461432</v>
       </c>
       <c r="N30">
-        <v>-65.03862400000001</v>
+        <v>-70.26143200000003</v>
       </c>
       <c r="O30">
-        <v>-13.0077248</v>
+        <v>-14.05228640000001</v>
       </c>
       <c r="P30">
-        <v>-52.03089920000001</v>
+        <v>-56.20914560000002</v>
       </c>
       <c r="Q30">
-        <v>-20.43089920000001</v>
+        <v>-24.60914560000003</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.101322610307017</v>
+        <v>0.1021046189028905</v>
       </c>
       <c r="T30">
-        <v>1.08223901906398</v>
+        <v>1.097481822149388</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.111051373131082</v>
+        <v>0.1072220154369067</v>
       </c>
       <c r="W30">
-        <v>0.1785008842752787</v>
+        <v>0.1792698193002691</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5552568656554098</v>
+        <v>0.5361100771845335</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1244825270181303</v>
+        <v>0.1260325270181303</v>
       </c>
       <c r="C31">
-        <v>612.2888731543226</v>
+        <v>560.0964465069039</v>
       </c>
       <c r="D31">
-        <v>1355.278873154323</v>
+        <v>1329.096446506904</v>
       </c>
       <c r="E31">
-        <v>712.1899999999999</v>
+        <v>738.1999999999999</v>
       </c>
       <c r="F31">
-        <v>754.29</v>
+        <v>780.3</v>
       </c>
       <c r="G31">
         <v>11.3</v>
@@ -3835,37 +3835,37 @@
         <v>81.2</v>
       </c>
       <c r="M31">
-        <v>151.461432</v>
+        <v>156.68424</v>
       </c>
       <c r="N31">
-        <v>-70.261432</v>
+        <v>-75.48423999999999</v>
       </c>
       <c r="O31">
-        <v>-14.0522864</v>
+        <v>-15.096848</v>
       </c>
       <c r="P31">
-        <v>-56.2091456</v>
+        <v>-60.38739199999999</v>
       </c>
       <c r="Q31">
-        <v>-24.60914560000001</v>
+        <v>-28.787392</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1021046189028905</v>
+        <v>0.1029089706015032</v>
       </c>
       <c r="T31">
-        <v>1.097481822149388</v>
+        <v>1.113160133894379</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1072220154369068</v>
+        <v>0.1036479482556765</v>
       </c>
       <c r="W31">
-        <v>0.1792698193002691</v>
+        <v>0.1799874919902602</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5361100771845337</v>
+        <v>0.5182397412783826</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1260325270181303</v>
+        <v>0.1275825270181303</v>
       </c>
       <c r="C32">
-        <v>560.0964465069039</v>
+        <v>508.8964754067322</v>
       </c>
       <c r="D32">
-        <v>1329.096446506904</v>
+        <v>1303.906475406732</v>
       </c>
       <c r="E32">
-        <v>738.1999999999999</v>
+        <v>764.2099999999999</v>
       </c>
       <c r="F32">
-        <v>780.3</v>
+        <v>806.3099999999999</v>
       </c>
       <c r="G32">
         <v>11.3</v>
@@ -3917,37 +3917,37 @@
         <v>81.2</v>
       </c>
       <c r="M32">
-        <v>156.68424</v>
+        <v>161.907048</v>
       </c>
       <c r="N32">
-        <v>-75.48423999999999</v>
+        <v>-80.707048</v>
       </c>
       <c r="O32">
-        <v>-15.096848</v>
+        <v>-16.1414096</v>
       </c>
       <c r="P32">
-        <v>-60.38739199999999</v>
+        <v>-64.5656384</v>
       </c>
       <c r="Q32">
-        <v>-28.787392</v>
+        <v>-32.9656384</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1029089706015032</v>
+        <v>0.1037366368421047</v>
       </c>
       <c r="T32">
-        <v>1.113160133894379</v>
+        <v>1.129292889458066</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1036479482556765</v>
+        <v>0.1003044660538805</v>
       </c>
       <c r="W32">
-        <v>0.1799874919902602</v>
+        <v>0.1806588632163808</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5182397412783826</v>
+        <v>0.5015223302694025</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1275825270181303</v>
+        <v>0.1405229533960758</v>
       </c>
       <c r="C33">
-        <v>508.8964754067322</v>
+        <v>304.7553557173588</v>
       </c>
       <c r="D33">
-        <v>1303.906475406732</v>
+        <v>1125.775355717359</v>
       </c>
       <c r="E33">
-        <v>764.2099999999999</v>
+        <v>790.22</v>
       </c>
       <c r="F33">
-        <v>806.3099999999999</v>
+        <v>832.3200000000001</v>
       </c>
       <c r="G33">
         <v>11.3</v>
@@ -3999,45 +3999,45 @@
         <v>81.2</v>
       </c>
       <c r="M33">
-        <v>161.907048</v>
+        <v>196.261056</v>
       </c>
       <c r="N33">
-        <v>-80.707048</v>
+        <v>-115.061056</v>
       </c>
       <c r="O33">
-        <v>-16.1414096</v>
+        <v>-23.01221120000001</v>
       </c>
       <c r="P33">
-        <v>-64.5656384</v>
+        <v>-92.04884480000001</v>
       </c>
       <c r="Q33">
-        <v>-32.9656384</v>
+        <v>-60.44884480000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1037366368421047</v>
+        <v>0.1048686849985261</v>
       </c>
       <c r="T33">
-        <v>1.129292889458066</v>
+        <v>1.151358615106846</v>
       </c>
       <c r="U33">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.1003044660538805</v>
+        <v>0.08274693070030154</v>
       </c>
       <c r="W33">
-        <v>0.1806588632163808</v>
+        <v>0.2162882737408689</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.5015223302694025</v>
+        <v>0.4137346535015076</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1405229533960758</v>
+        <v>0.1424229533960758</v>
       </c>
       <c r="C34">
-        <v>304.7553557173588</v>
+        <v>256.6080363674229</v>
       </c>
       <c r="D34">
-        <v>1125.775355717359</v>
+        <v>1103.638036367423</v>
       </c>
       <c r="E34">
-        <v>790.22</v>
+        <v>816.23</v>
       </c>
       <c r="F34">
-        <v>832.3200000000001</v>
+        <v>858.33</v>
       </c>
       <c r="G34">
         <v>11.3</v>
@@ -4081,37 +4081,37 @@
         <v>81.2</v>
       </c>
       <c r="M34">
-        <v>196.261056</v>
+        <v>202.394214</v>
       </c>
       <c r="N34">
-        <v>-115.061056</v>
+        <v>-121.194214</v>
       </c>
       <c r="O34">
-        <v>-23.01221120000001</v>
+        <v>-24.2388428</v>
       </c>
       <c r="P34">
-        <v>-92.04884480000001</v>
+        <v>-96.9553712</v>
       </c>
       <c r="Q34">
-        <v>-60.44884480000002</v>
+        <v>-65.35537120000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1048686849985261</v>
+        <v>0.1057503071626833</v>
       </c>
       <c r="T34">
-        <v>1.151358615106846</v>
+        <v>1.168543072048739</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08274693070030154</v>
+        <v>0.08023944795180755</v>
       </c>
       <c r="W34">
-        <v>0.2162882737408689</v>
+        <v>0.2168795381729638</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.4137346535015076</v>
+        <v>0.4011972397590378</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1424229533960758</v>
+        <v>0.1443229533960758</v>
       </c>
       <c r="C35">
-        <v>256.6080363674229</v>
+        <v>209.3145466138398</v>
       </c>
       <c r="D35">
-        <v>1103.638036367423</v>
+        <v>1082.35454661384</v>
       </c>
       <c r="E35">
-        <v>816.23</v>
+        <v>842.24</v>
       </c>
       <c r="F35">
-        <v>858.33</v>
+        <v>884.34</v>
       </c>
       <c r="G35">
         <v>11.3</v>
@@ -4163,37 +4163,37 @@
         <v>81.2</v>
       </c>
       <c r="M35">
-        <v>202.394214</v>
+        <v>208.527372</v>
       </c>
       <c r="N35">
-        <v>-121.194214</v>
+        <v>-127.327372</v>
       </c>
       <c r="O35">
-        <v>-24.2388428</v>
+        <v>-25.46547440000001</v>
       </c>
       <c r="P35">
-        <v>-96.9553712</v>
+        <v>-101.8618976</v>
       </c>
       <c r="Q35">
-        <v>-65.35537120000001</v>
+        <v>-70.26189760000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1057503071626833</v>
+        <v>0.1066586451499966</v>
       </c>
       <c r="T35">
-        <v>1.168543072048739</v>
+        <v>1.186248270110083</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.08023944795180755</v>
+        <v>0.0778794641885191</v>
       </c>
       <c r="W35">
-        <v>0.2168795381729638</v>
+        <v>0.2174360223443472</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.4011972397590378</v>
+        <v>0.3893973209425955</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1443229533960758</v>
+        <v>0.1462229533960758</v>
       </c>
       <c r="C36">
-        <v>209.3145466138398</v>
+        <v>162.8264231468329</v>
       </c>
       <c r="D36">
-        <v>1082.35454661384</v>
+        <v>1061.876423146833</v>
       </c>
       <c r="E36">
-        <v>842.24</v>
+        <v>868.2500000000001</v>
       </c>
       <c r="F36">
-        <v>884.34</v>
+        <v>910.3500000000001</v>
       </c>
       <c r="G36">
         <v>11.3</v>
@@ -4245,37 +4245,37 @@
         <v>81.2</v>
       </c>
       <c r="M36">
-        <v>208.527372</v>
+        <v>214.6605300000001</v>
       </c>
       <c r="N36">
-        <v>-127.327372</v>
+        <v>-133.4605300000001</v>
       </c>
       <c r="O36">
-        <v>-25.46547440000001</v>
+        <v>-26.69210600000001</v>
       </c>
       <c r="P36">
-        <v>-101.8618976</v>
+        <v>-106.7684240000001</v>
       </c>
       <c r="Q36">
-        <v>-70.26189760000001</v>
+        <v>-75.16842400000006</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1066586451499966</v>
+        <v>0.1075949319984581</v>
       </c>
       <c r="T36">
-        <v>1.186248270110083</v>
+        <v>1.204498243496392</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0778794641885191</v>
+        <v>0.07565433664027568</v>
       </c>
       <c r="W36">
-        <v>0.2174360223443472</v>
+        <v>0.217960707420223</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3893973209425955</v>
+        <v>0.3782716832013784</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1462229533960758</v>
+        <v>0.1481229533960758</v>
       </c>
       <c r="C37">
-        <v>162.8264231468329</v>
+        <v>117.098802251262</v>
       </c>
       <c r="D37">
-        <v>1061.876423146833</v>
+        <v>1042.158802251262</v>
       </c>
       <c r="E37">
-        <v>868.2500000000001</v>
+        <v>894.2600000000001</v>
       </c>
       <c r="F37">
-        <v>910.3500000000001</v>
+        <v>936.3600000000001</v>
       </c>
       <c r="G37">
         <v>11.3</v>
@@ -4327,37 +4327,37 @@
         <v>81.2</v>
       </c>
       <c r="M37">
-        <v>214.6605300000001</v>
+        <v>220.793688</v>
       </c>
       <c r="N37">
-        <v>-133.4605300000001</v>
+        <v>-139.593688</v>
       </c>
       <c r="O37">
-        <v>-26.69210600000001</v>
+        <v>-27.91873760000001</v>
       </c>
       <c r="P37">
-        <v>-106.7684240000001</v>
+        <v>-111.6749504</v>
       </c>
       <c r="Q37">
-        <v>-75.16842400000006</v>
+        <v>-80.07495040000003</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1075949319984581</v>
+        <v>0.108560477810934</v>
       </c>
       <c r="T37">
-        <v>1.204498243496392</v>
+        <v>1.223318528551024</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07565433664027568</v>
+        <v>0.07355282728915692</v>
       </c>
       <c r="W37">
-        <v>0.217960707420223</v>
+        <v>0.2184562433252168</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3782716832013784</v>
+        <v>0.3677641364457845</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1481229533960758</v>
+        <v>0.1500229533960758</v>
       </c>
       <c r="C38">
-        <v>117.0988022512621</v>
+        <v>72.09009170088609</v>
       </c>
       <c r="D38">
-        <v>1042.158802251262</v>
+        <v>1023.160091700886</v>
       </c>
       <c r="E38">
-        <v>894.26</v>
+        <v>920.27</v>
       </c>
       <c r="F38">
-        <v>936.36</v>
+        <v>962.37</v>
       </c>
       <c r="G38">
         <v>11.3</v>
@@ -4409,37 +4409,37 @@
         <v>81.2</v>
       </c>
       <c r="M38">
-        <v>220.793688</v>
+        <v>226.926846</v>
       </c>
       <c r="N38">
-        <v>-139.593688</v>
+        <v>-145.726846</v>
       </c>
       <c r="O38">
-        <v>-27.9187376</v>
+        <v>-29.1453692</v>
       </c>
       <c r="P38">
-        <v>-111.6749504</v>
+        <v>-116.5814768</v>
       </c>
       <c r="Q38">
-        <v>-80.07495039999999</v>
+        <v>-84.98147680000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.108560477810934</v>
+        <v>0.109556675871425</v>
       </c>
       <c r="T38">
-        <v>1.223318528551023</v>
+        <v>1.242736282972468</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07355282728915694</v>
+        <v>0.07156491303809863</v>
       </c>
       <c r="W38">
-        <v>0.2184562433252168</v>
+        <v>0.2189249935056163</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3677641364457847</v>
+        <v>0.3578245651904931</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1500229533960758</v>
+        <v>0.1519229533960758</v>
       </c>
       <c r="C39">
-        <v>72.09009170088609</v>
+        <v>27.76167789858448</v>
       </c>
       <c r="D39">
-        <v>1023.160091700886</v>
+        <v>1004.841677898585</v>
       </c>
       <c r="E39">
-        <v>920.27</v>
+        <v>946.28</v>
       </c>
       <c r="F39">
-        <v>962.37</v>
+        <v>988.38</v>
       </c>
       <c r="G39">
         <v>11.3</v>
@@ -4491,37 +4491,37 @@
         <v>81.2</v>
       </c>
       <c r="M39">
-        <v>226.926846</v>
+        <v>233.060004</v>
       </c>
       <c r="N39">
-        <v>-145.726846</v>
+        <v>-151.860004</v>
       </c>
       <c r="O39">
-        <v>-29.1453692</v>
+        <v>-30.3720008</v>
       </c>
       <c r="P39">
-        <v>-116.5814768</v>
+        <v>-121.4880032</v>
       </c>
       <c r="Q39">
-        <v>-84.98147680000002</v>
+        <v>-89.88800320000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.109556675871425</v>
+        <v>0.1105850093532222</v>
       </c>
       <c r="T39">
-        <v>1.242736282972468</v>
+        <v>1.262780416568798</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.07156491303809863</v>
+        <v>0.06968162585288551</v>
       </c>
       <c r="W39">
-        <v>0.2189249935056163</v>
+        <v>0.2193690726238896</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3578245651904931</v>
+        <v>0.3484081292644275</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1519229533960758</v>
+        <v>0.1538229533960758</v>
       </c>
       <c r="C40">
-        <v>27.76167789858448</v>
+        <v>-15.92233607701098</v>
       </c>
       <c r="D40">
-        <v>1004.841677898585</v>
+        <v>987.167663922989</v>
       </c>
       <c r="E40">
-        <v>946.28</v>
+        <v>972.29</v>
       </c>
       <c r="F40">
-        <v>988.38</v>
+        <v>1014.39</v>
       </c>
       <c r="G40">
         <v>11.3</v>
@@ -4573,37 +4573,37 @@
         <v>81.2</v>
       </c>
       <c r="M40">
-        <v>233.060004</v>
+        <v>239.193162</v>
       </c>
       <c r="N40">
-        <v>-151.860004</v>
+        <v>-157.993162</v>
       </c>
       <c r="O40">
-        <v>-30.3720008</v>
+        <v>-31.5986324</v>
       </c>
       <c r="P40">
-        <v>-121.4880032</v>
+        <v>-126.3945296</v>
       </c>
       <c r="Q40">
-        <v>-89.88800320000001</v>
+        <v>-94.79452959999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1105850093532222</v>
+        <v>0.1116470586868816</v>
       </c>
       <c r="T40">
-        <v>1.262780416568798</v>
+        <v>1.283481734873205</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06968162585288551</v>
+        <v>0.06789491749768332</v>
       </c>
       <c r="W40">
-        <v>0.2193690726238896</v>
+        <v>0.2197903784540463</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3484081292644275</v>
+        <v>0.3394745874884166</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1538229533960758</v>
+        <v>0.1557229533960758</v>
       </c>
       <c r="C41">
-        <v>-15.92233607701098</v>
+        <v>-58.99536525796316</v>
       </c>
       <c r="D41">
-        <v>987.167663922989</v>
+        <v>970.104634742037</v>
       </c>
       <c r="E41">
-        <v>972.29</v>
+        <v>998.3000000000001</v>
       </c>
       <c r="F41">
-        <v>1014.39</v>
+        <v>1040.4</v>
       </c>
       <c r="G41">
         <v>11.3</v>
@@ -4655,37 +4655,37 @@
         <v>81.2</v>
       </c>
       <c r="M41">
-        <v>239.193162</v>
+        <v>245.32632</v>
       </c>
       <c r="N41">
-        <v>-157.993162</v>
+        <v>-164.12632</v>
       </c>
       <c r="O41">
-        <v>-31.5986324</v>
+        <v>-32.825264</v>
       </c>
       <c r="P41">
-        <v>-126.3945296</v>
+        <v>-131.301056</v>
       </c>
       <c r="Q41">
-        <v>-94.79452959999999</v>
+        <v>-99.70105600000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1116470586868816</v>
+        <v>0.1127445096649963</v>
       </c>
       <c r="T41">
-        <v>1.283481734873205</v>
+        <v>1.304873097121092</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06789491749768332</v>
+        <v>0.06619754456024123</v>
       </c>
       <c r="W41">
-        <v>0.2197903784540463</v>
+        <v>0.2201906189926951</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3394745874884166</v>
+        <v>0.3309877228012061</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1557229533960758</v>
+        <v>0.1576229533960758</v>
       </c>
       <c r="C42">
-        <v>-58.99536525796316</v>
+        <v>-101.4885536377343</v>
       </c>
       <c r="D42">
-        <v>970.104634742037</v>
+        <v>953.6214463622658</v>
       </c>
       <c r="E42">
-        <v>998.3000000000001</v>
+        <v>1024.31</v>
       </c>
       <c r="F42">
-        <v>1040.4</v>
+        <v>1066.41</v>
       </c>
       <c r="G42">
         <v>11.3</v>
@@ -4737,37 +4737,37 @@
         <v>81.2</v>
       </c>
       <c r="M42">
-        <v>245.32632</v>
+        <v>251.459478</v>
       </c>
       <c r="N42">
-        <v>-164.12632</v>
+        <v>-170.259478</v>
       </c>
       <c r="O42">
-        <v>-32.825264</v>
+        <v>-34.0518956</v>
       </c>
       <c r="P42">
-        <v>-131.301056</v>
+        <v>-136.2075824</v>
       </c>
       <c r="Q42">
-        <v>-99.70105600000002</v>
+        <v>-104.6075824</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1127445096649963</v>
+        <v>0.1138791623711827</v>
       </c>
       <c r="T42">
-        <v>1.304873097121092</v>
+        <v>1.326989590292635</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06619754456024123</v>
+        <v>0.06458297030267438</v>
       </c>
       <c r="W42">
-        <v>0.2201906189926951</v>
+        <v>0.2205713356026294</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3309877228012061</v>
+        <v>0.322914851513372</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1576229533960758</v>
+        <v>0.1595229533960758</v>
       </c>
       <c r="C43">
-        <v>-101.4885536377343</v>
+        <v>-143.4309638854513</v>
       </c>
       <c r="D43">
-        <v>953.6214463622658</v>
+        <v>937.6890361145488</v>
       </c>
       <c r="E43">
-        <v>1024.31</v>
+        <v>1050.32</v>
       </c>
       <c r="F43">
-        <v>1066.41</v>
+        <v>1092.42</v>
       </c>
       <c r="G43">
         <v>11.3</v>
@@ -4819,37 +4819,37 @@
         <v>81.2</v>
       </c>
       <c r="M43">
-        <v>251.459478</v>
+        <v>257.592636</v>
       </c>
       <c r="N43">
-        <v>-170.259478</v>
+        <v>-176.392636</v>
       </c>
       <c r="O43">
-        <v>-34.0518956</v>
+        <v>-35.27852720000001</v>
       </c>
       <c r="P43">
-        <v>-136.2075824</v>
+        <v>-141.1141088</v>
       </c>
       <c r="Q43">
-        <v>-104.6075824</v>
+        <v>-109.5141088</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1138791623711827</v>
+        <v>0.1150529410327548</v>
       </c>
       <c r="T43">
-        <v>1.326989590292635</v>
+        <v>1.34986872115975</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06458297030267438</v>
+        <v>0.06304528053356308</v>
       </c>
       <c r="W43">
-        <v>0.2205713356026294</v>
+        <v>0.2209339228501858</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.322914851513372</v>
+        <v>0.3152264026678153</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1595229533960758</v>
+        <v>0.1614229533960758</v>
       </c>
       <c r="C44">
-        <v>-143.4309638854513</v>
+        <v>-184.8497483550417</v>
       </c>
       <c r="D44">
-        <v>937.6890361145488</v>
+        <v>922.2802516449584</v>
       </c>
       <c r="E44">
-        <v>1050.32</v>
+        <v>1076.33</v>
       </c>
       <c r="F44">
-        <v>1092.42</v>
+        <v>1118.43</v>
       </c>
       <c r="G44">
         <v>11.3</v>
@@ -4901,37 +4901,37 @@
         <v>81.2</v>
       </c>
       <c r="M44">
-        <v>257.592636</v>
+        <v>263.725794</v>
       </c>
       <c r="N44">
-        <v>-176.392636</v>
+        <v>-182.525794</v>
       </c>
       <c r="O44">
-        <v>-35.27852720000001</v>
+        <v>-36.5051588</v>
       </c>
       <c r="P44">
-        <v>-141.1141088</v>
+        <v>-146.0206352</v>
       </c>
       <c r="Q44">
-        <v>-109.5141088</v>
+        <v>-114.4206352</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1150529410327548</v>
+        <v>0.1162679049105224</v>
       </c>
       <c r="T44">
-        <v>1.34986872115975</v>
+        <v>1.373550628548517</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06304528053356308</v>
+        <v>0.06157911121882906</v>
       </c>
       <c r="W44">
-        <v>0.2209339228501858</v>
+        <v>0.2212796455746001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3152264026678153</v>
+        <v>0.3078955560941452</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1614229533960758</v>
+        <v>0.1633229533960758</v>
       </c>
       <c r="C45">
-        <v>-184.8497483550417</v>
+        <v>-225.7703035060829</v>
       </c>
       <c r="D45">
-        <v>922.2802516449584</v>
+        <v>907.3696964939172</v>
       </c>
       <c r="E45">
-        <v>1076.33</v>
+        <v>1102.34</v>
       </c>
       <c r="F45">
-        <v>1118.43</v>
+        <v>1144.44</v>
       </c>
       <c r="G45">
         <v>11.3</v>
@@ -4983,37 +4983,37 @@
         <v>81.2</v>
       </c>
       <c r="M45">
-        <v>263.725794</v>
+        <v>269.858952</v>
       </c>
       <c r="N45">
-        <v>-182.525794</v>
+        <v>-188.6589520000001</v>
       </c>
       <c r="O45">
-        <v>-36.5051588</v>
+        <v>-37.73179040000002</v>
       </c>
       <c r="P45">
-        <v>-146.0206352</v>
+        <v>-150.9271616</v>
       </c>
       <c r="Q45">
-        <v>-114.4206352</v>
+        <v>-119.3271616</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1162679049105224</v>
+        <v>0.1175262603553532</v>
       </c>
       <c r="T45">
-        <v>1.373550628548517</v>
+        <v>1.398078318344027</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06157911121882906</v>
+        <v>0.06017958596385566</v>
       </c>
       <c r="W45">
-        <v>0.2212796455746001</v>
+        <v>0.2216096536297228</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3078955560941452</v>
+        <v>0.3008979298192782</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1633229533960758</v>
+        <v>0.1652229533960758</v>
       </c>
       <c r="C46">
-        <v>-225.7703035060829</v>
+        <v>-266.2164095837869</v>
       </c>
       <c r="D46">
-        <v>907.3696964939172</v>
+        <v>892.9335904162132</v>
       </c>
       <c r="E46">
-        <v>1102.34</v>
+        <v>1128.35</v>
       </c>
       <c r="F46">
-        <v>1144.44</v>
+        <v>1170.45</v>
       </c>
       <c r="G46">
         <v>11.3</v>
@@ -5065,37 +5065,37 @@
         <v>81.2</v>
       </c>
       <c r="M46">
-        <v>269.858952</v>
+        <v>275.99211</v>
       </c>
       <c r="N46">
-        <v>-188.6589520000001</v>
+        <v>-194.79211</v>
       </c>
       <c r="O46">
-        <v>-37.73179040000002</v>
+        <v>-38.95842200000001</v>
       </c>
       <c r="P46">
-        <v>-150.9271616</v>
+        <v>-155.833688</v>
       </c>
       <c r="Q46">
-        <v>-119.3271616</v>
+        <v>-124.233688</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1175262603553532</v>
+        <v>0.118830374179996</v>
       </c>
       <c r="T46">
-        <v>1.398078318344027</v>
+        <v>1.4234979241321</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06017958596385566</v>
+        <v>0.05884226183132554</v>
       </c>
       <c r="W46">
-        <v>0.2216096536297228</v>
+        <v>0.2219249946601734</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3008979298192782</v>
+        <v>0.2942113091566276</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1652229533960758</v>
+        <v>0.1671229533960759</v>
       </c>
       <c r="C47">
-        <v>-266.2164095837869</v>
+        <v>-306.2103571740845</v>
       </c>
       <c r="D47">
-        <v>892.9335904162132</v>
+        <v>878.9496428259156</v>
       </c>
       <c r="E47">
-        <v>1128.35</v>
+        <v>1154.36</v>
       </c>
       <c r="F47">
-        <v>1170.45</v>
+        <v>1196.46</v>
       </c>
       <c r="G47">
         <v>11.3</v>
@@ -5147,37 +5147,37 @@
         <v>81.2</v>
       </c>
       <c r="M47">
-        <v>275.99211</v>
+        <v>282.125268</v>
       </c>
       <c r="N47">
-        <v>-194.79211</v>
+        <v>-200.925268</v>
       </c>
       <c r="O47">
-        <v>-38.95842200000001</v>
+        <v>-40.1850536</v>
       </c>
       <c r="P47">
-        <v>-155.833688</v>
+        <v>-160.7402144</v>
       </c>
       <c r="Q47">
-        <v>-124.233688</v>
+        <v>-129.1402144</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.118830374179996</v>
+        <v>0.1201827885166626</v>
       </c>
       <c r="T47">
-        <v>1.4234979241321</v>
+        <v>1.449858996801213</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05884226183132554</v>
+        <v>0.05756308222629673</v>
       </c>
       <c r="W47">
-        <v>0.2219249946601734</v>
+        <v>0.2222266252110393</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2942113091566276</v>
+        <v>0.2878154111314836</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1671229533960759</v>
+        <v>0.1690229533960758</v>
       </c>
       <c r="C48">
-        <v>-306.2103571740845</v>
+        <v>-345.7730620504341</v>
       </c>
       <c r="D48">
-        <v>878.9496428259156</v>
+        <v>865.396937949566</v>
       </c>
       <c r="E48">
-        <v>1154.36</v>
+        <v>1180.37</v>
       </c>
       <c r="F48">
-        <v>1196.46</v>
+        <v>1222.47</v>
       </c>
       <c r="G48">
         <v>11.3</v>
@@ -5229,37 +5229,37 @@
         <v>81.2</v>
       </c>
       <c r="M48">
-        <v>282.125268</v>
+        <v>288.258426</v>
       </c>
       <c r="N48">
-        <v>-200.925268</v>
+        <v>-207.0584260000001</v>
       </c>
       <c r="O48">
-        <v>-40.1850536</v>
+        <v>-41.41168520000002</v>
       </c>
       <c r="P48">
-        <v>-160.7402144</v>
+        <v>-165.6467408</v>
       </c>
       <c r="Q48">
-        <v>-129.1402144</v>
+        <v>-134.0467408</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1201827885166626</v>
+        <v>0.1215862373565996</v>
       </c>
       <c r="T48">
-        <v>1.449858996801213</v>
+        <v>1.477214826929538</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05756308222629673</v>
+        <v>0.05633833579594998</v>
       </c>
       <c r="W48">
-        <v>0.2222266252110393</v>
+        <v>0.222515420419315</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2878154111314836</v>
+        <v>0.2816916789797499</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1690229533960758</v>
+        <v>0.1709229533960758</v>
       </c>
       <c r="C49">
-        <v>-345.7730620504341</v>
+        <v>-384.9241695568986</v>
       </c>
       <c r="D49">
-        <v>865.396937949566</v>
+        <v>852.2558304431014</v>
       </c>
       <c r="E49">
-        <v>1180.37</v>
+        <v>1206.38</v>
       </c>
       <c r="F49">
-        <v>1222.47</v>
+        <v>1248.48</v>
       </c>
       <c r="G49">
         <v>11.3</v>
@@ -5311,37 +5311,37 @@
         <v>81.2</v>
       </c>
       <c r="M49">
-        <v>288.258426</v>
+        <v>294.391584</v>
       </c>
       <c r="N49">
-        <v>-207.0584260000001</v>
+        <v>-213.191584</v>
       </c>
       <c r="O49">
-        <v>-41.41168520000002</v>
+        <v>-42.63831680000001</v>
       </c>
       <c r="P49">
-        <v>-165.6467408</v>
+        <v>-170.5532672</v>
       </c>
       <c r="Q49">
-        <v>-134.0467408</v>
+        <v>-138.9532672</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1215862373565996</v>
+        <v>0.1230436649980726</v>
       </c>
       <c r="T49">
-        <v>1.477214826929538</v>
+        <v>1.50562280437049</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05633833579594998</v>
+        <v>0.05516462046686769</v>
       </c>
       <c r="W49">
-        <v>0.222515420419315</v>
+        <v>0.2227921824939126</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2816916789797499</v>
+        <v>0.2758231023343384</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1709229533960758</v>
+        <v>0.1728229533960758</v>
       </c>
       <c r="C50">
-        <v>-384.9241695568986</v>
+        <v>-423.6821496230897</v>
       </c>
       <c r="D50">
-        <v>852.2558304431014</v>
+        <v>839.5078503769104</v>
       </c>
       <c r="E50">
-        <v>1206.38</v>
+        <v>1232.39</v>
       </c>
       <c r="F50">
-        <v>1248.48</v>
+        <v>1274.49</v>
       </c>
       <c r="G50">
         <v>11.3</v>
@@ -5393,37 +5393,37 @@
         <v>81.2</v>
       </c>
       <c r="M50">
-        <v>294.391584</v>
+        <v>300.524742</v>
       </c>
       <c r="N50">
-        <v>-213.191584</v>
+        <v>-219.324742</v>
       </c>
       <c r="O50">
-        <v>-42.63831680000001</v>
+        <v>-43.8649484</v>
       </c>
       <c r="P50">
-        <v>-170.5532672</v>
+        <v>-175.4597936</v>
       </c>
       <c r="Q50">
-        <v>-138.9532672</v>
+        <v>-143.8597936</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1230436649980726</v>
+        <v>0.1245582466647015</v>
       </c>
       <c r="T50">
-        <v>1.50562280437049</v>
+        <v>1.53514482014246</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05516462046686769</v>
+        <v>0.05403881188591121</v>
       </c>
       <c r="W50">
-        <v>0.2227921824939126</v>
+        <v>0.2230576481573021</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2758231023343384</v>
+        <v>0.270194059429556</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1728229533960758</v>
+        <v>0.1747229533960758</v>
       </c>
       <c r="C51">
-        <v>-423.6821496230897</v>
+        <v>-462.0643833774296</v>
       </c>
       <c r="D51">
-        <v>839.5078503769104</v>
+        <v>827.1356166225704</v>
       </c>
       <c r="E51">
-        <v>1232.39</v>
+        <v>1258.4</v>
       </c>
       <c r="F51">
-        <v>1274.49</v>
+        <v>1300.5</v>
       </c>
       <c r="G51">
         <v>11.3</v>
@@ -5475,37 +5475,37 @@
         <v>81.2</v>
       </c>
       <c r="M51">
-        <v>300.524742</v>
+        <v>306.6579</v>
       </c>
       <c r="N51">
-        <v>-219.324742</v>
+        <v>-225.4579000000001</v>
       </c>
       <c r="O51">
-        <v>-43.8649484</v>
+        <v>-45.09158000000001</v>
       </c>
       <c r="P51">
-        <v>-175.4597936</v>
+        <v>-180.36632</v>
       </c>
       <c r="Q51">
-        <v>-143.8597936</v>
+        <v>-148.76632</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1245582466647015</v>
+        <v>0.1261334115979955</v>
       </c>
       <c r="T51">
-        <v>1.53514482014246</v>
+        <v>1.56584771654531</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05403881188591121</v>
+        <v>0.05295803564819299</v>
       </c>
       <c r="W51">
-        <v>0.2230576481573021</v>
+        <v>0.2233124951941561</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.270194059429556</v>
+        <v>0.2647901782409648</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1747229533960758</v>
+        <v>0.1766229533960758</v>
       </c>
       <c r="C52">
-        <v>-462.0643833774296</v>
+        <v>-500.0872422128732</v>
       </c>
       <c r="D52">
-        <v>827.1356166225704</v>
+        <v>815.1227577871268</v>
       </c>
       <c r="E52">
-        <v>1258.4</v>
+        <v>1284.41</v>
       </c>
       <c r="F52">
-        <v>1300.5</v>
+        <v>1326.51</v>
       </c>
       <c r="G52">
         <v>11.3</v>
@@ -5557,37 +5557,37 @@
         <v>81.2</v>
       </c>
       <c r="M52">
-        <v>306.6579</v>
+        <v>312.791058</v>
       </c>
       <c r="N52">
-        <v>-225.4579000000001</v>
+        <v>-231.591058</v>
       </c>
       <c r="O52">
-        <v>-45.09158000000001</v>
+        <v>-46.31821160000001</v>
       </c>
       <c r="P52">
-        <v>-180.36632</v>
+        <v>-185.2728464</v>
       </c>
       <c r="Q52">
-        <v>-148.76632</v>
+        <v>-153.6728464</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1261334115979955</v>
+        <v>0.1277728689775465</v>
       </c>
       <c r="T52">
-        <v>1.56584771654531</v>
+        <v>1.597803792393173</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05295803564819299</v>
+        <v>0.05191964279234607</v>
       </c>
       <c r="W52">
-        <v>0.2233124951941561</v>
+        <v>0.2235573482295648</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2647901782409648</v>
+        <v>0.2595982139617302</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1766229533960758</v>
+        <v>0.1785229533960758</v>
       </c>
       <c r="C53">
-        <v>-500.0872422128732</v>
+        <v>-537.7661600614216</v>
       </c>
       <c r="D53">
-        <v>815.1227577871268</v>
+        <v>803.4538399385784</v>
       </c>
       <c r="E53">
-        <v>1284.41</v>
+        <v>1310.42</v>
       </c>
       <c r="F53">
-        <v>1326.51</v>
+        <v>1352.52</v>
       </c>
       <c r="G53">
         <v>11.3</v>
@@ -5639,37 +5639,37 @@
         <v>81.2</v>
       </c>
       <c r="M53">
-        <v>312.791058</v>
+        <v>318.924216</v>
       </c>
       <c r="N53">
-        <v>-231.591058</v>
+        <v>-237.724216</v>
       </c>
       <c r="O53">
-        <v>-46.31821160000001</v>
+        <v>-47.5448432</v>
       </c>
       <c r="P53">
-        <v>-185.2728464</v>
+        <v>-190.1793728</v>
       </c>
       <c r="Q53">
-        <v>-153.6728464</v>
+        <v>-158.5793728</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1277728689775465</v>
+        <v>0.1294806370812454</v>
       </c>
       <c r="T53">
-        <v>1.597803792393173</v>
+        <v>1.631091371401364</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05191964279234607</v>
+        <v>0.05092118812326249</v>
       </c>
       <c r="W53">
-        <v>0.2235573482295648</v>
+        <v>0.2237927838405347</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2595982139617302</v>
+        <v>0.2546059406163124</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1785229533960758</v>
+        <v>0.1804229533960758</v>
       </c>
       <c r="C54">
-        <v>-537.7661600614216</v>
+        <v>-575.1156995483619</v>
       </c>
       <c r="D54">
-        <v>803.4538399385784</v>
+        <v>792.1143004516381</v>
       </c>
       <c r="E54">
-        <v>1310.42</v>
+        <v>1336.43</v>
       </c>
       <c r="F54">
-        <v>1352.52</v>
+        <v>1378.53</v>
       </c>
       <c r="G54">
         <v>11.3</v>
@@ -5721,37 +5721,37 @@
         <v>81.2</v>
       </c>
       <c r="M54">
-        <v>318.924216</v>
+        <v>325.057374</v>
       </c>
       <c r="N54">
-        <v>-237.724216</v>
+        <v>-243.857374</v>
       </c>
       <c r="O54">
-        <v>-47.5448432</v>
+        <v>-48.7714748</v>
       </c>
       <c r="P54">
-        <v>-190.1793728</v>
+        <v>-195.0858992</v>
       </c>
       <c r="Q54">
-        <v>-158.5793728</v>
+        <v>-163.4858992</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1294806370812454</v>
+        <v>0.1312610761680804</v>
       </c>
       <c r="T54">
-        <v>1.631091371401364</v>
+        <v>1.665795443133309</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05092118812326249</v>
+        <v>0.04996041098886132</v>
       </c>
       <c r="W54">
-        <v>0.2237927838405347</v>
+        <v>0.2240193350888265</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2546059406163124</v>
+        <v>0.2498020549443065</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1804229533960758</v>
+        <v>0.1823229533960758</v>
       </c>
       <c r="C55">
-        <v>-575.1156995483619</v>
+        <v>-612.1496126224649</v>
       </c>
       <c r="D55">
-        <v>792.1143004516381</v>
+        <v>781.0903873775353</v>
       </c>
       <c r="E55">
-        <v>1336.43</v>
+        <v>1362.44</v>
       </c>
       <c r="F55">
-        <v>1378.53</v>
+        <v>1404.54</v>
       </c>
       <c r="G55">
         <v>11.3</v>
@@ -5803,37 +5803,37 @@
         <v>81.2</v>
       </c>
       <c r="M55">
-        <v>325.057374</v>
+        <v>331.1905320000001</v>
       </c>
       <c r="N55">
-        <v>-243.857374</v>
+        <v>-249.9905320000001</v>
       </c>
       <c r="O55">
-        <v>-48.7714748</v>
+        <v>-49.99810640000002</v>
       </c>
       <c r="P55">
-        <v>-195.0858992</v>
+        <v>-199.9924256000001</v>
       </c>
       <c r="Q55">
-        <v>-163.4858992</v>
+        <v>-168.3924256000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1312610761680804</v>
+        <v>0.1331189256499952</v>
       </c>
       <c r="T55">
-        <v>1.665795443133309</v>
+        <v>1.70200838754925</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04996041098886132</v>
+        <v>0.04903521819277128</v>
       </c>
       <c r="W55">
-        <v>0.2240193350888265</v>
+        <v>0.2242374955501445</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2498020549443065</v>
+        <v>0.2451760909638563</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1823229533960758</v>
+        <v>0.1842229533960758</v>
       </c>
       <c r="C56">
-        <v>-612.1496126224649</v>
+        <v>-648.8808961929062</v>
       </c>
       <c r="D56">
-        <v>781.0903873775353</v>
+        <v>770.369103807094</v>
       </c>
       <c r="E56">
-        <v>1362.44</v>
+        <v>1388.45</v>
       </c>
       <c r="F56">
-        <v>1404.54</v>
+        <v>1430.55</v>
       </c>
       <c r="G56">
         <v>11.3</v>
@@ -5885,37 +5885,37 @@
         <v>81.2</v>
       </c>
       <c r="M56">
-        <v>331.1905320000001</v>
+        <v>337.3236900000001</v>
       </c>
       <c r="N56">
-        <v>-249.9905320000001</v>
+        <v>-256.1236900000001</v>
       </c>
       <c r="O56">
-        <v>-49.99810640000002</v>
+        <v>-51.22473800000002</v>
       </c>
       <c r="P56">
-        <v>-199.9924256000001</v>
+        <v>-204.8989520000001</v>
       </c>
       <c r="Q56">
-        <v>-168.3924256000001</v>
+        <v>-173.2989520000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1331189256499952</v>
+        <v>0.1350593462199951</v>
       </c>
       <c r="T56">
-        <v>1.70200838754925</v>
+        <v>1.739830796161455</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04903521819277128</v>
+        <v>0.04814366877108453</v>
       </c>
       <c r="W56">
-        <v>0.2242374955501445</v>
+        <v>0.2244477229037783</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2451760909638563</v>
+        <v>0.2407183438554226</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1842229533960758</v>
+        <v>0.1861229533960758</v>
       </c>
       <c r="C57">
-        <v>-648.8808961929062</v>
+        <v>-685.3218432461799</v>
       </c>
       <c r="D57">
-        <v>770.369103807094</v>
+        <v>759.9381567538203</v>
       </c>
       <c r="E57">
-        <v>1388.45</v>
+        <v>1414.46</v>
       </c>
       <c r="F57">
-        <v>1430.55</v>
+        <v>1456.56</v>
       </c>
       <c r="G57">
         <v>11.3</v>
@@ -5967,37 +5967,37 @@
         <v>81.2</v>
       </c>
       <c r="M57">
-        <v>337.3236900000001</v>
+        <v>343.456848</v>
       </c>
       <c r="N57">
-        <v>-256.1236900000001</v>
+        <v>-262.256848</v>
       </c>
       <c r="O57">
-        <v>-51.22473800000002</v>
+        <v>-52.45136960000001</v>
       </c>
       <c r="P57">
-        <v>-204.8989520000001</v>
+        <v>-209.8054784</v>
       </c>
       <c r="Q57">
-        <v>-173.2989520000001</v>
+        <v>-178.2054784</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1350593462199951</v>
+        <v>0.137087967724995</v>
       </c>
       <c r="T57">
-        <v>1.739830796161455</v>
+        <v>1.779372405165125</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04814366877108453</v>
+        <v>0.0472839604001723</v>
       </c>
       <c r="W57">
-        <v>0.2244477229037783</v>
+        <v>0.2246504421376394</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2407183438554226</v>
+        <v>0.2364198020008614</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1861229533960758</v>
+        <v>0.1880229533960758</v>
       </c>
       <c r="C58">
-        <v>-685.3218432461799</v>
+        <v>-721.4840898656914</v>
       </c>
       <c r="D58">
-        <v>759.9381567538203</v>
+        <v>749.7859101343088</v>
       </c>
       <c r="E58">
-        <v>1414.46</v>
+        <v>1440.47</v>
       </c>
       <c r="F58">
-        <v>1456.56</v>
+        <v>1482.57</v>
       </c>
       <c r="G58">
         <v>11.3</v>
@@ -6049,37 +6049,37 @@
         <v>81.2</v>
       </c>
       <c r="M58">
-        <v>343.456848</v>
+        <v>349.5900060000001</v>
       </c>
       <c r="N58">
-        <v>-262.256848</v>
+        <v>-268.3900060000001</v>
       </c>
       <c r="O58">
-        <v>-52.45136960000001</v>
+        <v>-53.67800120000002</v>
       </c>
       <c r="P58">
-        <v>-209.8054784</v>
+        <v>-214.7120048000001</v>
       </c>
       <c r="Q58">
-        <v>-178.2054784</v>
+        <v>-183.1120048000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.137087967724995</v>
+        <v>0.1392109437185995</v>
       </c>
       <c r="T58">
-        <v>1.779372405165125</v>
+        <v>1.820753158773616</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0472839604001723</v>
+        <v>0.046454417235257</v>
       </c>
       <c r="W58">
-        <v>0.2246504421376394</v>
+        <v>0.2248460484159264</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2364198020008614</v>
+        <v>0.2322720861762849</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1880229533960758</v>
+        <v>0.1899229533960758</v>
       </c>
       <c r="C59">
-        <v>-721.4840898656914</v>
+        <v>-757.3786585321421</v>
       </c>
       <c r="D59">
-        <v>749.7859101343088</v>
+        <v>739.9013414678581</v>
       </c>
       <c r="E59">
-        <v>1440.47</v>
+        <v>1466.48</v>
       </c>
       <c r="F59">
-        <v>1482.57</v>
+        <v>1508.58</v>
       </c>
       <c r="G59">
         <v>11.3</v>
@@ -6131,37 +6131,37 @@
         <v>81.2</v>
       </c>
       <c r="M59">
-        <v>349.5900060000001</v>
+        <v>355.7231640000001</v>
       </c>
       <c r="N59">
-        <v>-268.3900060000001</v>
+        <v>-274.5231640000001</v>
       </c>
       <c r="O59">
-        <v>-53.67800120000002</v>
+        <v>-54.90463280000002</v>
       </c>
       <c r="P59">
-        <v>-214.7120048000001</v>
+        <v>-219.6185312000001</v>
       </c>
       <c r="Q59">
-        <v>-183.1120048000001</v>
+        <v>-188.0185312000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1392109437185995</v>
+        <v>0.1414350138071376</v>
       </c>
       <c r="T59">
-        <v>1.820753158773616</v>
+        <v>1.864104424458702</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.046454417235257</v>
+        <v>0.04565347900706292</v>
       </c>
       <c r="W59">
-        <v>0.2248460484159264</v>
+        <v>0.2250349096501346</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2322720861762849</v>
+        <v>0.2282673950353146</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1899229533960758</v>
+        <v>0.1918229533960758</v>
       </c>
       <c r="C60">
-        <v>-757.3786585321419</v>
+        <v>-793.0159980434566</v>
       </c>
       <c r="D60">
-        <v>739.9013414678581</v>
+        <v>730.2740019565433</v>
       </c>
       <c r="E60">
-        <v>1466.48</v>
+        <v>1492.49</v>
       </c>
       <c r="F60">
-        <v>1508.58</v>
+        <v>1534.59</v>
       </c>
       <c r="G60">
         <v>11.3</v>
@@ -6213,37 +6213,37 @@
         <v>81.2</v>
       </c>
       <c r="M60">
-        <v>355.723164</v>
+        <v>361.856322</v>
       </c>
       <c r="N60">
-        <v>-274.523164</v>
+        <v>-280.656322</v>
       </c>
       <c r="O60">
-        <v>-54.9046328</v>
+        <v>-56.1312644</v>
       </c>
       <c r="P60">
-        <v>-219.6185312</v>
+        <v>-224.5250576</v>
       </c>
       <c r="Q60">
-        <v>-188.0185312</v>
+        <v>-192.9250576</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1414350138071375</v>
+        <v>0.1437675751195067</v>
       </c>
       <c r="T60">
-        <v>1.864104424458702</v>
+        <v>1.909570386030865</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04565347900706292</v>
+        <v>0.0448796912272822</v>
       </c>
       <c r="W60">
-        <v>0.2250349096501346</v>
+        <v>0.2252173688086069</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2282673950353146</v>
+        <v>0.224398456136411</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1918229533960758</v>
+        <v>0.1937229533960758</v>
       </c>
       <c r="C61">
-        <v>-793.0159980434566</v>
+        <v>-828.4060203581969</v>
       </c>
       <c r="D61">
-        <v>730.2740019565433</v>
+        <v>720.8939796418031</v>
       </c>
       <c r="E61">
-        <v>1492.49</v>
+        <v>1518.5</v>
       </c>
       <c r="F61">
-        <v>1534.59</v>
+        <v>1560.6</v>
       </c>
       <c r="G61">
         <v>11.3</v>
@@ -6295,37 +6295,37 @@
         <v>81.2</v>
       </c>
       <c r="M61">
-        <v>361.856322</v>
+        <v>367.98948</v>
       </c>
       <c r="N61">
-        <v>-280.656322</v>
+        <v>-286.78948</v>
       </c>
       <c r="O61">
-        <v>-56.1312644</v>
+        <v>-57.35789600000001</v>
       </c>
       <c r="P61">
-        <v>-224.5250576</v>
+        <v>-229.431584</v>
       </c>
       <c r="Q61">
-        <v>-192.9250576</v>
+        <v>-197.831584</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1437675751195067</v>
+        <v>0.1462167644974944</v>
       </c>
       <c r="T61">
-        <v>1.909570386030865</v>
+        <v>1.957309645681637</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0448796912272822</v>
+        <v>0.04413169637349416</v>
       </c>
       <c r="W61">
-        <v>0.2252173688086069</v>
+        <v>0.2253937459951301</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.224398456136411</v>
+        <v>0.2206584818674707</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1937229533960758</v>
+        <v>0.1956229533960758</v>
       </c>
       <c r="C62">
-        <v>-828.4060203581969</v>
+        <v>-863.5581346355627</v>
       </c>
       <c r="D62">
-        <v>720.8939796418031</v>
+        <v>711.7518653644372</v>
       </c>
       <c r="E62">
-        <v>1518.5</v>
+        <v>1544.51</v>
       </c>
       <c r="F62">
-        <v>1560.6</v>
+        <v>1586.61</v>
       </c>
       <c r="G62">
         <v>11.3</v>
@@ -6377,37 +6377,37 @@
         <v>81.2</v>
       </c>
       <c r="M62">
-        <v>367.98948</v>
+        <v>374.122638</v>
       </c>
       <c r="N62">
-        <v>-286.78948</v>
+        <v>-292.922638</v>
       </c>
       <c r="O62">
-        <v>-57.35789600000001</v>
+        <v>-58.5845276</v>
       </c>
       <c r="P62">
-        <v>-229.431584</v>
+        <v>-234.3381104</v>
       </c>
       <c r="Q62">
-        <v>-197.831584</v>
+        <v>-202.7381104</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1462167644974944</v>
+        <v>0.1487915533307635</v>
       </c>
       <c r="T62">
-        <v>1.957309645681637</v>
+        <v>2.007497072493987</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04413169637349416</v>
+        <v>0.0434082259411418</v>
       </c>
       <c r="W62">
-        <v>0.2253937459951301</v>
+        <v>0.2255643403230788</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2206584818674707</v>
+        <v>0.2170411297057089</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1956229533960758</v>
+        <v>0.1975229533960758</v>
       </c>
       <c r="C63">
-        <v>-863.5581346355627</v>
+        <v>-898.4812787177383</v>
       </c>
       <c r="D63">
-        <v>711.7518653644372</v>
+        <v>702.8387212822616</v>
       </c>
       <c r="E63">
-        <v>1544.51</v>
+        <v>1570.52</v>
       </c>
       <c r="F63">
-        <v>1586.61</v>
+        <v>1612.62</v>
       </c>
       <c r="G63">
         <v>11.3</v>
@@ -6459,37 +6459,37 @@
         <v>81.2</v>
       </c>
       <c r="M63">
-        <v>374.122638</v>
+        <v>380.255796</v>
       </c>
       <c r="N63">
-        <v>-292.922638</v>
+        <v>-299.055796</v>
       </c>
       <c r="O63">
-        <v>-58.5845276</v>
+        <v>-59.8111592</v>
       </c>
       <c r="P63">
-        <v>-234.3381104</v>
+        <v>-239.2446368</v>
       </c>
       <c r="Q63">
-        <v>-202.7381104</v>
+        <v>-207.6446368</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1487915533307635</v>
+        <v>0.1515018573657836</v>
       </c>
       <c r="T63">
-        <v>2.007497072493987</v>
+        <v>2.060325942822776</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0434082259411418</v>
+        <v>0.04270809326467177</v>
       </c>
       <c r="W63">
-        <v>0.2255643403230788</v>
+        <v>0.2257294316081904</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2170411297057089</v>
+        <v>0.2135404663233588</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1975229533960758</v>
+        <v>0.1994229533960758</v>
       </c>
       <c r="C64">
-        <v>-898.4812787177383</v>
+        <v>-933.1839482760003</v>
       </c>
       <c r="D64">
-        <v>702.8387212822616</v>
+        <v>694.1460517239999</v>
       </c>
       <c r="E64">
-        <v>1570.52</v>
+        <v>1596.53</v>
       </c>
       <c r="F64">
-        <v>1612.62</v>
+        <v>1638.63</v>
       </c>
       <c r="G64">
         <v>11.3</v>
@@ -6541,37 +6541,37 @@
         <v>81.2</v>
       </c>
       <c r="M64">
-        <v>380.255796</v>
+        <v>386.3889540000001</v>
       </c>
       <c r="N64">
-        <v>-299.055796</v>
+        <v>-305.1889540000001</v>
       </c>
       <c r="O64">
-        <v>-59.8111592</v>
+        <v>-61.03779080000002</v>
       </c>
       <c r="P64">
-        <v>-239.2446368</v>
+        <v>-244.1511632000001</v>
       </c>
       <c r="Q64">
-        <v>-207.6446368</v>
+        <v>-212.5511632000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1515018573657836</v>
+        <v>0.1543586643216156</v>
       </c>
       <c r="T64">
-        <v>2.060325942822776</v>
+        <v>2.116010427763932</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04270809326467177</v>
+        <v>0.04203018702237538</v>
       </c>
       <c r="W64">
-        <v>0.2257294316081904</v>
+        <v>0.2258892819001239</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2135404663233588</v>
+        <v>0.2101509351118769</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1994229533960758</v>
+        <v>0.2013229533960758</v>
       </c>
       <c r="C65">
-        <v>-933.1839482760003</v>
+        <v>-967.6742238203874</v>
       </c>
       <c r="D65">
-        <v>694.1460517239999</v>
+        <v>685.6657761796127</v>
       </c>
       <c r="E65">
-        <v>1596.53</v>
+        <v>1622.54</v>
       </c>
       <c r="F65">
-        <v>1638.63</v>
+        <v>1664.64</v>
       </c>
       <c r="G65">
         <v>11.3</v>
@@ -6623,37 +6623,37 @@
         <v>81.2</v>
       </c>
       <c r="M65">
-        <v>386.3889540000001</v>
+        <v>392.522112</v>
       </c>
       <c r="N65">
-        <v>-305.1889540000001</v>
+        <v>-311.3221120000001</v>
       </c>
       <c r="O65">
-        <v>-61.03779080000002</v>
+        <v>-62.26442240000002</v>
       </c>
       <c r="P65">
-        <v>-244.1511632000001</v>
+        <v>-249.0576896000001</v>
       </c>
       <c r="Q65">
-        <v>-212.5511632000001</v>
+        <v>-217.4576896000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1543586643216156</v>
+        <v>0.1573741827749938</v>
       </c>
       <c r="T65">
-        <v>2.116010427763932</v>
+        <v>2.174788495201819</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04203018702237538</v>
+        <v>0.04137346535015077</v>
       </c>
       <c r="W65">
-        <v>0.2258892819001239</v>
+        <v>0.2260441368704345</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2101509351118769</v>
+        <v>0.2068673267507538</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2013229533960758</v>
+        <v>0.2032229533960758</v>
       </c>
       <c r="C66">
-        <v>-967.6742238203874</v>
+        <v>-1001.95979575343</v>
       </c>
       <c r="D66">
-        <v>685.6657761796127</v>
+        <v>677.3902042465701</v>
       </c>
       <c r="E66">
-        <v>1622.54</v>
+        <v>1648.55</v>
       </c>
       <c r="F66">
-        <v>1664.64</v>
+        <v>1690.65</v>
       </c>
       <c r="G66">
         <v>11.3</v>
@@ -6705,37 +6705,37 @@
         <v>81.2</v>
       </c>
       <c r="M66">
-        <v>392.522112</v>
+        <v>398.65527</v>
       </c>
       <c r="N66">
-        <v>-311.3221120000001</v>
+        <v>-317.45527</v>
       </c>
       <c r="O66">
-        <v>-62.26442240000002</v>
+        <v>-63.49105400000001</v>
       </c>
       <c r="P66">
-        <v>-249.0576896000001</v>
+        <v>-253.964216</v>
       </c>
       <c r="Q66">
-        <v>-217.4576896000001</v>
+        <v>-222.364216</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1573741827749938</v>
+        <v>0.1605620165685651</v>
       </c>
       <c r="T66">
-        <v>2.174788495201819</v>
+        <v>2.236925309350443</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04137346535015077</v>
+        <v>0.04073695049860999</v>
       </c>
       <c r="W66">
-        <v>0.2260441368704345</v>
+        <v>0.2261942270724278</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2068673267507538</v>
+        <v>0.20368475249305</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2032229533960758</v>
+        <v>0.2051229533960758</v>
       </c>
       <c r="C67">
-        <v>-1001.95979575343</v>
+        <v>-1036.047987631212</v>
       </c>
       <c r="D67">
-        <v>677.3902042465701</v>
+        <v>669.3120123687877</v>
       </c>
       <c r="E67">
-        <v>1648.55</v>
+        <v>1674.56</v>
       </c>
       <c r="F67">
-        <v>1690.65</v>
+        <v>1716.66</v>
       </c>
       <c r="G67">
         <v>11.3</v>
@@ -6787,37 +6787,37 @@
         <v>81.2</v>
       </c>
       <c r="M67">
-        <v>398.65527</v>
+        <v>404.788428</v>
       </c>
       <c r="N67">
-        <v>-317.45527</v>
+        <v>-323.588428</v>
       </c>
       <c r="O67">
-        <v>-63.49105400000001</v>
+        <v>-64.71768560000001</v>
       </c>
       <c r="P67">
-        <v>-253.964216</v>
+        <v>-258.8707424</v>
       </c>
       <c r="Q67">
-        <v>-222.364216</v>
+        <v>-227.2707424</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1605620165685651</v>
+        <v>0.1639373699970523</v>
       </c>
       <c r="T67">
-        <v>2.236925309350443</v>
+        <v>2.302717230213691</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04073695049860999</v>
+        <v>0.04011972397590378</v>
       </c>
       <c r="W67">
-        <v>0.2261942270724278</v>
+        <v>0.2263397690864819</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.20368475249305</v>
+        <v>0.2005986198795189</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2051229533960758</v>
+        <v>0.2070229533960758</v>
       </c>
       <c r="C68">
-        <v>-1036.047987631212</v>
+        <v>-1069.945777779657</v>
       </c>
       <c r="D68">
-        <v>669.3120123687877</v>
+        <v>661.4242222203432</v>
       </c>
       <c r="E68">
-        <v>1674.56</v>
+        <v>1700.57</v>
       </c>
       <c r="F68">
-        <v>1716.66</v>
+        <v>1742.67</v>
       </c>
       <c r="G68">
         <v>11.3</v>
@@ -6869,37 +6869,37 @@
         <v>81.2</v>
       </c>
       <c r="M68">
-        <v>404.788428</v>
+        <v>410.921586</v>
       </c>
       <c r="N68">
-        <v>-323.588428</v>
+        <v>-329.7215860000001</v>
       </c>
       <c r="O68">
-        <v>-64.71768560000001</v>
+        <v>-65.94431720000001</v>
       </c>
       <c r="P68">
-        <v>-258.8707424</v>
+        <v>-263.7772688000001</v>
       </c>
       <c r="Q68">
-        <v>-227.2707424</v>
+        <v>-232.1772688000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1639373699970523</v>
+        <v>0.1675172902999933</v>
       </c>
       <c r="T68">
-        <v>2.302717230213691</v>
+        <v>2.372496540220167</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04011972397590378</v>
+        <v>0.03952092212551715</v>
       </c>
       <c r="W68">
-        <v>0.2263397690864819</v>
+        <v>0.2264809665628031</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2005986198795189</v>
+        <v>0.1976046106275857</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2070229533960758</v>
+        <v>0.2089229533960759</v>
       </c>
       <c r="C69">
-        <v>-1069.945777779657</v>
+        <v>-1103.659819400135</v>
       </c>
       <c r="D69">
-        <v>661.4242222203432</v>
+        <v>653.7201805998652</v>
       </c>
       <c r="E69">
-        <v>1700.57</v>
+        <v>1726.58</v>
       </c>
       <c r="F69">
-        <v>1742.67</v>
+        <v>1768.68</v>
       </c>
       <c r="G69">
         <v>11.3</v>
@@ -6951,37 +6951,37 @@
         <v>81.2</v>
       </c>
       <c r="M69">
-        <v>410.921586</v>
+        <v>417.054744</v>
       </c>
       <c r="N69">
-        <v>-329.7215860000001</v>
+        <v>-335.854744</v>
       </c>
       <c r="O69">
-        <v>-65.94431720000001</v>
+        <v>-67.17094880000001</v>
       </c>
       <c r="P69">
-        <v>-263.7772688000001</v>
+        <v>-268.6837952</v>
       </c>
       <c r="Q69">
-        <v>-232.1772688000001</v>
+        <v>-237.0837952</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1675172902999933</v>
+        <v>0.1713209556218681</v>
       </c>
       <c r="T69">
-        <v>2.372496540220167</v>
+        <v>2.446637057102047</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03952092212551715</v>
+        <v>0.03893973209425955</v>
       </c>
       <c r="W69">
-        <v>0.2264809665628031</v>
+        <v>0.2266180111721736</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1976046106275857</v>
+        <v>0.1946986604712977</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2089229533960759</v>
+        <v>0.2108229533960758</v>
       </c>
       <c r="C70">
-        <v>-1103.659819400135</v>
+        <v>-1137.196459286155</v>
       </c>
       <c r="D70">
-        <v>653.7201805998652</v>
+        <v>646.1935407138451</v>
       </c>
       <c r="E70">
-        <v>1726.58</v>
+        <v>1752.59</v>
       </c>
       <c r="F70">
-        <v>1768.68</v>
+        <v>1794.69</v>
       </c>
       <c r="G70">
         <v>11.3</v>
@@ -7033,37 +7033,37 @@
         <v>81.2</v>
       </c>
       <c r="M70">
-        <v>417.054744</v>
+        <v>423.187902</v>
       </c>
       <c r="N70">
-        <v>-335.854744</v>
+        <v>-341.987902</v>
       </c>
       <c r="O70">
-        <v>-67.17094880000001</v>
+        <v>-68.39758040000001</v>
       </c>
       <c r="P70">
-        <v>-268.6837952</v>
+        <v>-273.5903216</v>
       </c>
       <c r="Q70">
-        <v>-237.0837952</v>
+        <v>-241.9903216</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1713209556218681</v>
+        <v>0.1753700187064445</v>
       </c>
       <c r="T70">
-        <v>2.446637057102047</v>
+        <v>2.525560833137597</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03893973209425955</v>
+        <v>0.03837538815086448</v>
       </c>
       <c r="W70">
-        <v>0.2266180111721736</v>
+        <v>0.2267510834740262</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1946986604712977</v>
+        <v>0.1918769407543224</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2108229533960758</v>
+        <v>0.2127229533960759</v>
       </c>
       <c r="C71">
-        <v>-1137.196459286155</v>
+        <v>-1170.561755261796</v>
       </c>
       <c r="D71">
-        <v>646.1935407138451</v>
+        <v>638.8382447382039</v>
       </c>
       <c r="E71">
-        <v>1752.59</v>
+        <v>1778.6</v>
       </c>
       <c r="F71">
-        <v>1794.69</v>
+        <v>1820.7</v>
       </c>
       <c r="G71">
         <v>11.3</v>
@@ -7115,37 +7115,37 @@
         <v>81.2</v>
       </c>
       <c r="M71">
-        <v>423.187902</v>
+        <v>429.3210600000001</v>
       </c>
       <c r="N71">
-        <v>-341.987902</v>
+        <v>-348.1210600000001</v>
       </c>
       <c r="O71">
-        <v>-68.39758040000001</v>
+        <v>-69.62421200000003</v>
       </c>
       <c r="P71">
-        <v>-273.5903216</v>
+        <v>-278.4968480000001</v>
       </c>
       <c r="Q71">
-        <v>-241.9903216</v>
+        <v>-246.8968480000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1753700187064445</v>
+        <v>0.1796890193299926</v>
       </c>
       <c r="T71">
-        <v>2.525560833137597</v>
+        <v>2.609746194242184</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03837538815086448</v>
+        <v>0.03782716832013784</v>
       </c>
       <c r="W71">
-        <v>0.2267510834740262</v>
+        <v>0.2268803537101115</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1918769407543224</v>
+        <v>0.1891358416006892</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2127229533960759</v>
+        <v>0.2146229533960758</v>
       </c>
       <c r="C72">
-        <v>-1170.561755261796</v>
+        <v>-1203.761492442587</v>
       </c>
       <c r="D72">
-        <v>638.8382447382039</v>
+        <v>631.6485075574134</v>
       </c>
       <c r="E72">
-        <v>1778.6</v>
+        <v>1804.61</v>
       </c>
       <c r="F72">
-        <v>1820.7</v>
+        <v>1846.71</v>
       </c>
       <c r="G72">
         <v>11.3</v>
@@ -7197,37 +7197,37 @@
         <v>81.2</v>
       </c>
       <c r="M72">
-        <v>429.3210600000001</v>
+        <v>435.4542180000001</v>
       </c>
       <c r="N72">
-        <v>-348.1210600000001</v>
+        <v>-354.2542180000001</v>
       </c>
       <c r="O72">
-        <v>-69.62421200000003</v>
+        <v>-70.85084360000002</v>
       </c>
       <c r="P72">
-        <v>-278.4968480000001</v>
+        <v>-283.4033744000001</v>
       </c>
       <c r="Q72">
-        <v>-246.8968480000001</v>
+        <v>-251.8033744000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1796890193299926</v>
+        <v>0.1843058820655096</v>
       </c>
       <c r="T72">
-        <v>2.609746194242184</v>
+        <v>2.6997374423195</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03782716832013784</v>
+        <v>0.03729439130154435</v>
       </c>
       <c r="W72">
-        <v>0.2268803537101115</v>
+        <v>0.2270059825310959</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1891358416006892</v>
+        <v>0.1864719565077217</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2146229533960758</v>
+        <v>0.2165229533960758</v>
       </c>
       <c r="C73">
-        <v>-1203.761492442587</v>
+        <v>-1236.801198410564</v>
       </c>
       <c r="D73">
-        <v>631.6485075574134</v>
+        <v>624.6188015894365</v>
       </c>
       <c r="E73">
-        <v>1804.61</v>
+        <v>1830.62</v>
       </c>
       <c r="F73">
-        <v>1846.71</v>
+        <v>1872.72</v>
       </c>
       <c r="G73">
         <v>11.3</v>
@@ -7279,37 +7279,37 @@
         <v>81.2</v>
       </c>
       <c r="M73">
-        <v>435.454218</v>
+        <v>441.587376</v>
       </c>
       <c r="N73">
-        <v>-354.254218</v>
+        <v>-360.387376</v>
       </c>
       <c r="O73">
-        <v>-70.8508436</v>
+        <v>-72.07747520000001</v>
       </c>
       <c r="P73">
-        <v>-283.4033744</v>
+        <v>-288.3099008</v>
       </c>
       <c r="Q73">
-        <v>-251.8033744</v>
+        <v>-256.7099008</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1843058820655096</v>
+        <v>0.1892525207107063</v>
       </c>
       <c r="T73">
-        <v>2.6997374423195</v>
+        <v>2.796156636688053</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03729439130154436</v>
+        <v>0.03677641364457847</v>
       </c>
       <c r="W73">
-        <v>0.2270059825310959</v>
+        <v>0.2271281216626084</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1864719565077217</v>
+        <v>0.1838820682228923</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2165229533960758</v>
+        <v>0.2184229533960758</v>
       </c>
       <c r="C74">
-        <v>-1236.801198410564</v>
+        <v>-1269.686157387177</v>
       </c>
       <c r="D74">
-        <v>624.6188015894365</v>
+        <v>617.7438426128225</v>
       </c>
       <c r="E74">
-        <v>1830.62</v>
+        <v>1856.63</v>
       </c>
       <c r="F74">
-        <v>1872.72</v>
+        <v>1898.73</v>
       </c>
       <c r="G74">
         <v>11.3</v>
@@ -7361,37 +7361,37 @@
         <v>81.2</v>
       </c>
       <c r="M74">
-        <v>441.587376</v>
+        <v>447.720534</v>
       </c>
       <c r="N74">
-        <v>-360.387376</v>
+        <v>-366.5205340000001</v>
       </c>
       <c r="O74">
-        <v>-72.07747520000001</v>
+        <v>-73.30410680000001</v>
       </c>
       <c r="P74">
-        <v>-288.3099008</v>
+        <v>-293.2164272000001</v>
       </c>
       <c r="Q74">
-        <v>-256.7099008</v>
+        <v>-261.6164272000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1892525207107063</v>
+        <v>0.1945655770333251</v>
       </c>
       <c r="T74">
-        <v>2.796156636688053</v>
+        <v>2.899717993602426</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03677641364457847</v>
+        <v>0.03627262715629657</v>
       </c>
       <c r="W74">
-        <v>0.2271281216626084</v>
+        <v>0.2272469145165453</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1838820682228923</v>
+        <v>0.1813631357814828</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2184229533960758</v>
+        <v>0.2203229533960758</v>
       </c>
       <c r="C75">
-        <v>-1269.686157387177</v>
+        <v>-1302.421423480404</v>
       </c>
       <c r="D75">
-        <v>617.7438426128225</v>
+        <v>611.018576519596</v>
       </c>
       <c r="E75">
-        <v>1856.63</v>
+        <v>1882.64</v>
       </c>
       <c r="F75">
-        <v>1898.73</v>
+        <v>1924.74</v>
       </c>
       <c r="G75">
         <v>11.3</v>
@@ -7443,37 +7443,37 @@
         <v>81.2</v>
       </c>
       <c r="M75">
-        <v>447.720534</v>
+        <v>453.853692</v>
       </c>
       <c r="N75">
-        <v>-366.5205340000001</v>
+        <v>-372.653692</v>
       </c>
       <c r="O75">
-        <v>-73.30410680000001</v>
+        <v>-74.5307384</v>
       </c>
       <c r="P75">
-        <v>-293.2164272000001</v>
+        <v>-298.1229536</v>
       </c>
       <c r="Q75">
-        <v>-261.6164272000001</v>
+        <v>-266.5229536000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1945655770333251</v>
+        <v>0.2002873299961453</v>
       </c>
       <c r="T75">
-        <v>2.899717993602426</v>
+        <v>3.01124560874098</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03627262715629657</v>
+        <v>0.03578245651904931</v>
       </c>
       <c r="W75">
-        <v>0.2272469145165453</v>
+        <v>0.2273624967528082</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1813631357814828</v>
+        <v>0.1789122825952465</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2203229533960758</v>
+        <v>0.2222229533960758</v>
       </c>
       <c r="C76">
-        <v>-1302.421423480404</v>
+        <v>-1335.011833075865</v>
       </c>
       <c r="D76">
-        <v>611.018576519596</v>
+        <v>604.4381669241349</v>
       </c>
       <c r="E76">
-        <v>1882.64</v>
+        <v>1908.65</v>
       </c>
       <c r="F76">
-        <v>1924.74</v>
+        <v>1950.75</v>
       </c>
       <c r="G76">
         <v>11.3</v>
@@ -7525,37 +7525,37 @@
         <v>81.2</v>
       </c>
       <c r="M76">
-        <v>453.853692</v>
+        <v>459.98685</v>
       </c>
       <c r="N76">
-        <v>-372.653692</v>
+        <v>-378.78685</v>
       </c>
       <c r="O76">
-        <v>-74.5307384</v>
+        <v>-75.75737000000001</v>
       </c>
       <c r="P76">
-        <v>-298.1229536</v>
+        <v>-303.02948</v>
       </c>
       <c r="Q76">
-        <v>-266.5229536000001</v>
+        <v>-271.42948</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2002873299961453</v>
+        <v>0.2064668231959911</v>
       </c>
       <c r="T76">
-        <v>3.01124560874098</v>
+        <v>3.131695433090619</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03578245651904931</v>
+        <v>0.03530535709879533</v>
       </c>
       <c r="W76">
-        <v>0.2273624967528082</v>
+        <v>0.2274749967961041</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1789122825952465</v>
+        <v>0.1765267854939766</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2222229533960758</v>
+        <v>0.2241229533960759</v>
       </c>
       <c r="C77">
-        <v>-1335.011833075865</v>
+        <v>-1367.462016435801</v>
       </c>
       <c r="D77">
-        <v>604.4381669241349</v>
+        <v>597.9979835641994</v>
       </c>
       <c r="E77">
-        <v>1908.65</v>
+        <v>1934.66</v>
       </c>
       <c r="F77">
-        <v>1950.75</v>
+        <v>1976.76</v>
       </c>
       <c r="G77">
         <v>11.3</v>
@@ -7607,37 +7607,37 @@
         <v>81.2</v>
       </c>
       <c r="M77">
-        <v>459.98685</v>
+        <v>466.120008</v>
       </c>
       <c r="N77">
-        <v>-378.78685</v>
+        <v>-384.9200080000001</v>
       </c>
       <c r="O77">
-        <v>-75.75737000000001</v>
+        <v>-76.98400160000001</v>
       </c>
       <c r="P77">
-        <v>-303.02948</v>
+        <v>-307.9360064000001</v>
       </c>
       <c r="Q77">
-        <v>-271.42948</v>
+        <v>-276.3360064000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2064668231959911</v>
+        <v>0.2131612741624907</v>
       </c>
       <c r="T77">
-        <v>3.131695433090619</v>
+        <v>3.262182742802728</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03530535709879533</v>
+        <v>0.03484081292644275</v>
       </c>
       <c r="W77">
-        <v>0.2274749967961041</v>
+        <v>0.2275845363119448</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1765267854939766</v>
+        <v>0.1742040646322137</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2241229533960759</v>
+        <v>0.2260229533960758</v>
       </c>
       <c r="C78">
-        <v>-1367.462016435801</v>
+        <v>-1399.776408564338</v>
       </c>
       <c r="D78">
-        <v>597.9979835641994</v>
+        <v>591.6935914356621</v>
       </c>
       <c r="E78">
-        <v>1934.66</v>
+        <v>1960.67</v>
       </c>
       <c r="F78">
-        <v>1976.76</v>
+        <v>2002.77</v>
       </c>
       <c r="G78">
         <v>11.3</v>
@@ -7689,37 +7689,37 @@
         <v>81.2</v>
       </c>
       <c r="M78">
-        <v>466.120008</v>
+        <v>472.253166</v>
       </c>
       <c r="N78">
-        <v>-384.9200080000001</v>
+        <v>-391.053166</v>
       </c>
       <c r="O78">
-        <v>-76.98400160000001</v>
+        <v>-78.21063320000002</v>
       </c>
       <c r="P78">
-        <v>-307.9360064000001</v>
+        <v>-312.8425328</v>
       </c>
       <c r="Q78">
-        <v>-276.3360064000001</v>
+        <v>-281.2425328</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2131612741624907</v>
+        <v>0.2204378512999904</v>
       </c>
       <c r="T78">
-        <v>3.262182742802728</v>
+        <v>3.4040167750985</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03484081292644275</v>
+        <v>0.03438833483648895</v>
       </c>
       <c r="W78">
-        <v>0.2275845363119448</v>
+        <v>0.2276912306455559</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1742040646322137</v>
+        <v>0.1719416741824448</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2260229533960758</v>
+        <v>0.2279229533960759</v>
       </c>
       <c r="C79">
-        <v>-1399.776408564338</v>
+        <v>-1431.959259392662</v>
       </c>
       <c r="D79">
-        <v>591.6935914356621</v>
+        <v>585.5207406073383</v>
       </c>
       <c r="E79">
-        <v>1960.67</v>
+        <v>1986.68</v>
       </c>
       <c r="F79">
-        <v>2002.77</v>
+        <v>2028.78</v>
       </c>
       <c r="G79">
         <v>11.3</v>
@@ -7771,37 +7771,37 @@
         <v>81.2</v>
       </c>
       <c r="M79">
-        <v>472.253166</v>
+        <v>478.386324</v>
       </c>
       <c r="N79">
-        <v>-391.053166</v>
+        <v>-397.186324</v>
       </c>
       <c r="O79">
-        <v>-78.21063320000002</v>
+        <v>-79.43726480000001</v>
       </c>
       <c r="P79">
-        <v>-312.8425328</v>
+        <v>-317.7490592</v>
       </c>
       <c r="Q79">
-        <v>-281.2425328</v>
+        <v>-286.1490592</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2204378512999904</v>
+        <v>0.2283759354499899</v>
       </c>
       <c r="T79">
-        <v>3.4040167750985</v>
+        <v>3.55874481033025</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03438833483648895</v>
+        <v>0.03394745874884166</v>
       </c>
       <c r="W79">
-        <v>0.2276912306455559</v>
+        <v>0.2277951892270232</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1719416741824448</v>
+        <v>0.1697372937442083</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2279229533960759</v>
+        <v>0.2298229533960758</v>
       </c>
       <c r="C80">
-        <v>-1431.959259392662</v>
+        <v>-1464.014643333216</v>
       </c>
       <c r="D80">
-        <v>585.5207406073383</v>
+        <v>579.4753566667844</v>
       </c>
       <c r="E80">
-        <v>1986.68</v>
+        <v>2012.69</v>
       </c>
       <c r="F80">
-        <v>2028.78</v>
+        <v>2054.79</v>
       </c>
       <c r="G80">
         <v>11.3</v>
@@ -7853,37 +7853,37 @@
         <v>81.2</v>
       </c>
       <c r="M80">
-        <v>478.386324</v>
+        <v>484.519482</v>
       </c>
       <c r="N80">
-        <v>-397.186324</v>
+        <v>-403.3194820000001</v>
       </c>
       <c r="O80">
-        <v>-79.43726480000001</v>
+        <v>-80.66389640000001</v>
       </c>
       <c r="P80">
-        <v>-317.7490592</v>
+        <v>-322.6555856000001</v>
       </c>
       <c r="Q80">
-        <v>-286.1490592</v>
+        <v>-291.0555856000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2283759354499899</v>
+        <v>0.2370700276142751</v>
       </c>
       <c r="T80">
-        <v>3.55874481033025</v>
+        <v>3.728208848917404</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03394745874884166</v>
+        <v>0.0335177440811348</v>
       </c>
       <c r="W80">
-        <v>0.2277951892270232</v>
+        <v>0.2278965159456684</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1697372937442083</v>
+        <v>0.167588720405674</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2298229533960758</v>
+        <v>0.2317229533960758</v>
       </c>
       <c r="C81">
-        <v>-1464.014643333216</v>
+        <v>-1495.946468248085</v>
       </c>
       <c r="D81">
-        <v>579.4753566667844</v>
+        <v>573.5535317519153</v>
       </c>
       <c r="E81">
-        <v>2012.69</v>
+        <v>2038.7</v>
       </c>
       <c r="F81">
-        <v>2054.79</v>
+        <v>2080.8</v>
       </c>
       <c r="G81">
         <v>11.3</v>
@@ -7935,37 +7935,37 @@
         <v>81.2</v>
       </c>
       <c r="M81">
-        <v>484.519482</v>
+        <v>490.6526400000001</v>
       </c>
       <c r="N81">
-        <v>-403.3194820000001</v>
+        <v>-409.4526400000001</v>
       </c>
       <c r="O81">
-        <v>-80.66389640000001</v>
+        <v>-81.89052800000002</v>
       </c>
       <c r="P81">
-        <v>-322.6555856000001</v>
+        <v>-327.5621120000001</v>
       </c>
       <c r="Q81">
-        <v>-291.0555856000001</v>
+        <v>-295.962112</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2370700276142751</v>
+        <v>0.2466335289949889</v>
       </c>
       <c r="T81">
-        <v>3.728208848917404</v>
+        <v>3.914619291363275</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0335177440811348</v>
+        <v>0.03309877228012061</v>
       </c>
       <c r="W81">
-        <v>0.2278965159456684</v>
+        <v>0.2279953094963476</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.167588720405674</v>
+        <v>0.1654938614006031</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2317229533960758</v>
+        <v>0.2336229533960758</v>
       </c>
       <c r="C82">
-        <v>-1495.946468248085</v>
+        <v>-1527.758483873036</v>
       </c>
       <c r="D82">
-        <v>573.5535317519153</v>
+        <v>567.7515161269636</v>
       </c>
       <c r="E82">
-        <v>2038.7</v>
+        <v>2064.71</v>
       </c>
       <c r="F82">
-        <v>2080.8</v>
+        <v>2106.81</v>
       </c>
       <c r="G82">
         <v>11.3</v>
@@ -8017,37 +8017,37 @@
         <v>81.2</v>
       </c>
       <c r="M82">
-        <v>490.6526400000001</v>
+        <v>496.785798</v>
       </c>
       <c r="N82">
-        <v>-409.4526400000001</v>
+        <v>-415.585798</v>
       </c>
       <c r="O82">
-        <v>-81.89052800000002</v>
+        <v>-83.11715960000001</v>
       </c>
       <c r="P82">
-        <v>-327.5621120000001</v>
+        <v>-332.4686384</v>
       </c>
       <c r="Q82">
-        <v>-295.962112</v>
+        <v>-300.8686384</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2466335289949889</v>
+        <v>0.2572037147315673</v>
       </c>
       <c r="T82">
-        <v>3.914619291363275</v>
+        <v>4.120651885645553</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03309877228012061</v>
+        <v>0.03269014546184753</v>
       </c>
       <c r="W82">
-        <v>0.2279953094963476</v>
+        <v>0.2280916637000963</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1654938614006031</v>
+        <v>0.1634507273092376</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2336229533960758</v>
+        <v>0.2355229533960758</v>
       </c>
       <c r="C83">
-        <v>-1527.758483873036</v>
+        <v>-1559.454289735384</v>
       </c>
       <c r="D83">
-        <v>567.7515161269636</v>
+        <v>562.0657102646163</v>
       </c>
       <c r="E83">
-        <v>2064.71</v>
+        <v>2090.72</v>
       </c>
       <c r="F83">
-        <v>2106.81</v>
+        <v>2132.82</v>
       </c>
       <c r="G83">
         <v>11.3</v>
@@ -8099,37 +8099,37 @@
         <v>81.2</v>
       </c>
       <c r="M83">
-        <v>496.785798</v>
+        <v>502.918956</v>
       </c>
       <c r="N83">
-        <v>-415.585798</v>
+        <v>-421.718956</v>
       </c>
       <c r="O83">
-        <v>-83.11715960000001</v>
+        <v>-84.34379120000001</v>
       </c>
       <c r="P83">
-        <v>-332.4686384</v>
+        <v>-337.3751648000001</v>
       </c>
       <c r="Q83">
-        <v>-300.8686384</v>
+        <v>-305.7751648000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2572037147315673</v>
+        <v>0.2689483655499877</v>
       </c>
       <c r="T83">
-        <v>4.120651885645553</v>
+        <v>4.349576990403639</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03269014546184753</v>
+        <v>0.03229148515133719</v>
       </c>
       <c r="W83">
-        <v>0.2280916637000963</v>
+        <v>0.2281856678013147</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1634507273092376</v>
+        <v>0.1614574257566859</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2355229533960758</v>
+        <v>0.2374229533960759</v>
       </c>
       <c r="C84">
-        <v>-1559.454289735384</v>
+        <v>-1591.037342600797</v>
       </c>
       <c r="D84">
-        <v>562.0657102646163</v>
+        <v>556.4926573992037</v>
       </c>
       <c r="E84">
-        <v>2090.72</v>
+        <v>2116.73</v>
       </c>
       <c r="F84">
-        <v>2132.82</v>
+        <v>2158.83</v>
       </c>
       <c r="G84">
         <v>11.3</v>
@@ -8181,37 +8181,37 @@
         <v>81.2</v>
       </c>
       <c r="M84">
-        <v>502.918956</v>
+        <v>509.0521140000001</v>
       </c>
       <c r="N84">
-        <v>-421.718956</v>
+        <v>-427.8521140000001</v>
       </c>
       <c r="O84">
-        <v>-84.34379120000001</v>
+        <v>-85.57042280000003</v>
       </c>
       <c r="P84">
-        <v>-337.3751648000001</v>
+        <v>-342.2816912000001</v>
       </c>
       <c r="Q84">
-        <v>-305.7751648000001</v>
+        <v>-310.6816912000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2689483655499877</v>
+        <v>0.2820747399941047</v>
       </c>
       <c r="T84">
-        <v>4.349576990403639</v>
+        <v>4.605434460427384</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03229148515133719</v>
+        <v>0.03190243111336926</v>
       </c>
       <c r="W84">
-        <v>0.2281856678013147</v>
+        <v>0.2282774067434676</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1614574257566859</v>
+        <v>0.1595121555668463</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2374229533960759</v>
+        <v>0.2393229533960758</v>
       </c>
       <c r="C85">
-        <v>-1591.037342600797</v>
+        <v>-1622.510963481439</v>
       </c>
       <c r="D85">
-        <v>556.4926573992037</v>
+        <v>551.0290365185608</v>
       </c>
       <c r="E85">
-        <v>2116.73</v>
+        <v>2142.74</v>
       </c>
       <c r="F85">
-        <v>2158.83</v>
+        <v>2184.84</v>
       </c>
       <c r="G85">
         <v>11.3</v>
@@ -8263,37 +8263,37 @@
         <v>81.2</v>
       </c>
       <c r="M85">
-        <v>509.0521140000001</v>
+        <v>515.1852720000001</v>
       </c>
       <c r="N85">
-        <v>-427.8521140000001</v>
+        <v>-433.9852720000001</v>
       </c>
       <c r="O85">
-        <v>-85.57042280000003</v>
+        <v>-86.79705440000002</v>
       </c>
       <c r="P85">
-        <v>-342.2816912000001</v>
+        <v>-347.1882176</v>
       </c>
       <c r="Q85">
-        <v>-310.6816912000002</v>
+        <v>-315.5882176</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2820747399941047</v>
+        <v>0.2968419112437363</v>
       </c>
       <c r="T85">
-        <v>4.605434460427384</v>
+        <v>4.893274114204096</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03190243111336926</v>
+        <v>0.03152264026678154</v>
       </c>
       <c r="W85">
-        <v>0.2282774067434676</v>
+        <v>0.2283669614250929</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1595121555668463</v>
+        <v>0.1576132013339077</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2393229533960758</v>
+        <v>0.2412229533960759</v>
       </c>
       <c r="C86">
-        <v>-1622.510963481439</v>
+        <v>-1653.878344235292</v>
       </c>
       <c r="D86">
-        <v>551.0290365185615</v>
+        <v>545.6716557647079</v>
       </c>
       <c r="E86">
-        <v>2142.74</v>
+        <v>2168.75</v>
       </c>
       <c r="F86">
-        <v>2184.84</v>
+        <v>2210.85</v>
       </c>
       <c r="G86">
         <v>11.3</v>
@@ -8345,37 +8345,37 @@
         <v>81.2</v>
       </c>
       <c r="M86">
-        <v>515.1852720000001</v>
+        <v>521.31843</v>
       </c>
       <c r="N86">
-        <v>-433.9852720000001</v>
+        <v>-440.11843</v>
       </c>
       <c r="O86">
-        <v>-86.79705440000002</v>
+        <v>-88.02368600000001</v>
       </c>
       <c r="P86">
-        <v>-347.1882176</v>
+        <v>-352.094744</v>
       </c>
       <c r="Q86">
-        <v>-315.5882176</v>
+        <v>-320.4947440000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2968419112437361</v>
+        <v>0.3135780386599852</v>
       </c>
       <c r="T86">
-        <v>4.893274114204092</v>
+        <v>5.219492388484365</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03152264026678154</v>
+        <v>0.03115178567540764</v>
       </c>
       <c r="W86">
-        <v>0.2283669614250929</v>
+        <v>0.2284544089377389</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1576132013339077</v>
+        <v>0.1557589283770382</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2412229533960759</v>
+        <v>0.2431229533960758</v>
       </c>
       <c r="C87">
-        <v>-1653.878344235292</v>
+        <v>-1685.142553784203</v>
       </c>
       <c r="D87">
-        <v>545.6716557647079</v>
+        <v>540.4174462157976</v>
       </c>
       <c r="E87">
-        <v>2168.75</v>
+        <v>2194.76</v>
       </c>
       <c r="F87">
-        <v>2210.85</v>
+        <v>2236.86</v>
       </c>
       <c r="G87">
         <v>11.3</v>
@@ -8427,37 +8427,37 @@
         <v>81.2</v>
       </c>
       <c r="M87">
-        <v>521.31843</v>
+        <v>527.451588</v>
       </c>
       <c r="N87">
-        <v>-440.11843</v>
+        <v>-446.251588</v>
       </c>
       <c r="O87">
-        <v>-88.02368600000001</v>
+        <v>-89.25031760000002</v>
       </c>
       <c r="P87">
-        <v>-352.094744</v>
+        <v>-357.0012704</v>
       </c>
       <c r="Q87">
-        <v>-320.4947440000001</v>
+        <v>-325.4012704</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3135780386599852</v>
+        <v>0.3327050414214127</v>
       </c>
       <c r="T87">
-        <v>5.219492388484365</v>
+        <v>5.592313273376107</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03115178567540764</v>
+        <v>0.03078955560941453</v>
       </c>
       <c r="W87">
-        <v>0.2284544089377389</v>
+        <v>0.2285398227873001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1557589283770382</v>
+        <v>0.1539477780470726</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2431229533960758</v>
+        <v>0.2450229533960758</v>
       </c>
       <c r="C88">
-        <v>-1685.142553784203</v>
+        <v>-1716.306543976129</v>
       </c>
       <c r="D88">
-        <v>540.4174462157976</v>
+        <v>535.2634560238705</v>
       </c>
       <c r="E88">
-        <v>2194.76</v>
+        <v>2220.77</v>
       </c>
       <c r="F88">
-        <v>2236.86</v>
+        <v>2262.87</v>
       </c>
       <c r="G88">
         <v>11.3</v>
@@ -8509,37 +8509,37 @@
         <v>81.2</v>
       </c>
       <c r="M88">
-        <v>527.451588</v>
+        <v>533.584746</v>
       </c>
       <c r="N88">
-        <v>-446.251588</v>
+        <v>-452.384746</v>
       </c>
       <c r="O88">
-        <v>-89.25031760000002</v>
+        <v>-90.47694920000001</v>
       </c>
       <c r="P88">
-        <v>-357.0012704</v>
+        <v>-361.9077968</v>
       </c>
       <c r="Q88">
-        <v>-325.4012704</v>
+        <v>-330.3077968</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3327050414214127</v>
+        <v>0.3547746599922906</v>
       </c>
       <c r="T88">
-        <v>5.592313273376107</v>
+        <v>6.02249121748196</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03078955560941453</v>
+        <v>0.03043565267137528</v>
       </c>
       <c r="W88">
-        <v>0.2285398227873001</v>
+        <v>0.2286232731000897</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1539477780470726</v>
+        <v>0.1521782633568763</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2450229533960758</v>
+        <v>0.2469229533960758</v>
       </c>
       <c r="C89">
-        <v>-1716.306543976129</v>
+        <v>-1747.3731551151</v>
       </c>
       <c r="D89">
-        <v>535.2634560238705</v>
+        <v>530.2068448848996</v>
       </c>
       <c r="E89">
-        <v>2220.77</v>
+        <v>2246.78</v>
       </c>
       <c r="F89">
-        <v>2262.87</v>
+        <v>2288.88</v>
       </c>
       <c r="G89">
         <v>11.3</v>
@@ -8591,37 +8591,37 @@
         <v>81.2</v>
       </c>
       <c r="M89">
-        <v>533.584746</v>
+        <v>539.7179040000001</v>
       </c>
       <c r="N89">
-        <v>-452.384746</v>
+        <v>-458.5179040000001</v>
       </c>
       <c r="O89">
-        <v>-90.47694920000001</v>
+        <v>-91.70358080000003</v>
       </c>
       <c r="P89">
-        <v>-361.9077968</v>
+        <v>-366.8143232000001</v>
       </c>
       <c r="Q89">
-        <v>-330.3077968</v>
+        <v>-335.2143232000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3547746599922906</v>
+        <v>0.3805225483249815</v>
       </c>
       <c r="T89">
-        <v>6.02249121748196</v>
+        <v>6.524365485605458</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03043565267137528</v>
+        <v>0.03008979298192783</v>
       </c>
       <c r="W89">
-        <v>0.2286232731000897</v>
+        <v>0.2287048268148614</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1521782633568763</v>
+        <v>0.1504489649096391</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2469229533960758</v>
+        <v>0.2488229533960759</v>
       </c>
       <c r="C90">
-        <v>-1747.3731551151</v>
+        <v>-1778.345121180662</v>
       </c>
       <c r="D90">
-        <v>530.2068448848996</v>
+        <v>525.2448788193383</v>
       </c>
       <c r="E90">
-        <v>2246.78</v>
+        <v>2272.79</v>
       </c>
       <c r="F90">
-        <v>2288.88</v>
+        <v>2314.89</v>
       </c>
       <c r="G90">
         <v>11.3</v>
@@ -8673,37 +8673,37 @@
         <v>81.2</v>
       </c>
       <c r="M90">
-        <v>539.7179040000001</v>
+        <v>545.851062</v>
       </c>
       <c r="N90">
-        <v>-458.5179040000001</v>
+        <v>-464.651062</v>
       </c>
       <c r="O90">
-        <v>-91.70358080000003</v>
+        <v>-92.9302124</v>
       </c>
       <c r="P90">
-        <v>-366.8143232000001</v>
+        <v>-371.7208496</v>
       </c>
       <c r="Q90">
-        <v>-335.2143232000001</v>
+        <v>-340.1208495999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3805225483249815</v>
+        <v>0.4109518708999799</v>
       </c>
       <c r="T90">
-        <v>6.524365485605458</v>
+        <v>7.117489620660501</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03008979298192783</v>
+        <v>0.02975170542033314</v>
       </c>
       <c r="W90">
-        <v>0.2287048268148614</v>
+        <v>0.2287845478618855</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1504489649096391</v>
+        <v>0.1487585271016657</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2488229533960759</v>
+        <v>0.2507229533960758</v>
       </c>
       <c r="C91">
-        <v>-1778.345121180662</v>
+        <v>-1809.22507475696</v>
       </c>
       <c r="D91">
-        <v>525.2448788193383</v>
+        <v>520.3749252430405</v>
       </c>
       <c r="E91">
-        <v>2272.79</v>
+        <v>2298.8</v>
       </c>
       <c r="F91">
-        <v>2314.89</v>
+        <v>2340.9</v>
       </c>
       <c r="G91">
         <v>11.3</v>
@@ -8755,37 +8755,37 @@
         <v>81.2</v>
       </c>
       <c r="M91">
-        <v>545.851062</v>
+        <v>551.9842200000001</v>
       </c>
       <c r="N91">
-        <v>-464.651062</v>
+        <v>-470.7842200000001</v>
       </c>
       <c r="O91">
-        <v>-92.9302124</v>
+        <v>-94.15684400000002</v>
       </c>
       <c r="P91">
-        <v>-371.7208496</v>
+        <v>-376.627376</v>
       </c>
       <c r="Q91">
-        <v>-340.1208495999999</v>
+        <v>-345.027376</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4109518708999799</v>
+        <v>0.4474670579899779</v>
       </c>
       <c r="T91">
-        <v>7.117489620660501</v>
+        <v>7.829238582726551</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02975170542033314</v>
+        <v>0.02942113091566277</v>
       </c>
       <c r="W91">
-        <v>0.2287845478618855</v>
+        <v>0.2288624973300867</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1487585271016657</v>
+        <v>0.1471056545783138</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2507229533960758</v>
+        <v>0.2526229533960758</v>
       </c>
       <c r="C92">
-        <v>-1809.22507475696</v>
+        <v>-1840.015551690138</v>
       </c>
       <c r="D92">
-        <v>520.3749252430405</v>
+        <v>515.5944483098621</v>
       </c>
       <c r="E92">
-        <v>2298.8</v>
+        <v>2324.81</v>
       </c>
       <c r="F92">
-        <v>2340.9</v>
+        <v>2366.91</v>
       </c>
       <c r="G92">
         <v>11.3</v>
@@ -8837,37 +8837,37 @@
         <v>81.2</v>
       </c>
       <c r="M92">
-        <v>551.9842200000001</v>
+        <v>558.117378</v>
       </c>
       <c r="N92">
-        <v>-470.7842200000001</v>
+        <v>-476.917378</v>
       </c>
       <c r="O92">
-        <v>-94.15684400000002</v>
+        <v>-95.38347560000001</v>
       </c>
       <c r="P92">
-        <v>-376.627376</v>
+        <v>-381.5339024</v>
       </c>
       <c r="Q92">
-        <v>-345.027376</v>
+        <v>-349.9339024000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4474670579899779</v>
+        <v>0.4920967310999754</v>
       </c>
       <c r="T92">
-        <v>7.829238582726551</v>
+        <v>8.699153980807278</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02942113091566277</v>
+        <v>0.02909782178472142</v>
       </c>
       <c r="W92">
-        <v>0.2288624973300867</v>
+        <v>0.2289387336231627</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1471056545783138</v>
+        <v>0.1454891089236071</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2526229533960758</v>
+        <v>0.2545229533960758</v>
       </c>
       <c r="C93">
-        <v>-1840.015551690138</v>
+        <v>-1870.718995491356</v>
       </c>
       <c r="D93">
-        <v>515.5944483098621</v>
+        <v>510.901004508644</v>
       </c>
       <c r="E93">
-        <v>2324.81</v>
+        <v>2350.82</v>
       </c>
       <c r="F93">
-        <v>2366.91</v>
+        <v>2392.92</v>
       </c>
       <c r="G93">
         <v>11.3</v>
@@ -8919,37 +8919,37 @@
         <v>81.2</v>
       </c>
       <c r="M93">
-        <v>558.117378</v>
+        <v>564.250536</v>
       </c>
       <c r="N93">
-        <v>-476.917378</v>
+        <v>-483.050536</v>
       </c>
       <c r="O93">
-        <v>-95.38347560000001</v>
+        <v>-96.61010720000002</v>
       </c>
       <c r="P93">
-        <v>-381.5339024</v>
+        <v>-386.4404288</v>
       </c>
       <c r="Q93">
-        <v>-349.9339024000001</v>
+        <v>-354.8404288</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4920967310999754</v>
+        <v>0.5478838224874725</v>
       </c>
       <c r="T93">
-        <v>8.699153980807278</v>
+        <v>9.786548228408192</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02909782178472142</v>
+        <v>0.02878154111314836</v>
       </c>
       <c r="W93">
-        <v>0.2289387336231627</v>
+        <v>0.2290133126055196</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1454891089236071</v>
+        <v>0.1439077055657418</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2545229533960758</v>
+        <v>0.2564229533960758</v>
       </c>
       <c r="C94">
-        <v>-1870.718995491356</v>
+        <v>-1901.337761501493</v>
       </c>
       <c r="D94">
-        <v>510.901004508644</v>
+        <v>506.2922384985076</v>
       </c>
       <c r="E94">
-        <v>2350.82</v>
+        <v>2376.83</v>
       </c>
       <c r="F94">
-        <v>2392.92</v>
+        <v>2418.93</v>
       </c>
       <c r="G94">
         <v>11.3</v>
@@ -9001,37 +9001,37 @@
         <v>81.2</v>
       </c>
       <c r="M94">
-        <v>564.250536</v>
+        <v>570.3836940000001</v>
       </c>
       <c r="N94">
-        <v>-483.050536</v>
+        <v>-489.1836940000001</v>
       </c>
       <c r="O94">
-        <v>-96.61010720000002</v>
+        <v>-97.83673880000003</v>
       </c>
       <c r="P94">
-        <v>-386.4404288</v>
+        <v>-391.3469552000001</v>
       </c>
       <c r="Q94">
-        <v>-354.8404288</v>
+        <v>-359.7469552000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5478838224874725</v>
+        <v>0.6196100828428257</v>
       </c>
       <c r="T94">
-        <v>9.786548228408192</v>
+        <v>11.18462654675222</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02878154111314836</v>
+        <v>0.02847206217644784</v>
       </c>
       <c r="W94">
-        <v>0.2290133126055196</v>
+        <v>0.2290862877387936</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1439077055657418</v>
+        <v>0.1423603108822392</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2564229533960758</v>
+        <v>0.2583229533960758</v>
       </c>
       <c r="C95">
-        <v>-1901.337761501493</v>
+        <v>-1931.874120832451</v>
       </c>
       <c r="D95">
-        <v>506.2922384985076</v>
+        <v>501.7658791675493</v>
       </c>
       <c r="E95">
-        <v>2376.83</v>
+        <v>2402.84</v>
       </c>
       <c r="F95">
-        <v>2418.93</v>
+        <v>2444.94</v>
       </c>
       <c r="G95">
         <v>11.3</v>
@@ -9083,37 +9083,37 @@
         <v>81.2</v>
       </c>
       <c r="M95">
-        <v>570.3836940000001</v>
+        <v>576.5168520000001</v>
       </c>
       <c r="N95">
-        <v>-489.1836940000001</v>
+        <v>-495.3168520000001</v>
       </c>
       <c r="O95">
-        <v>-97.83673880000003</v>
+        <v>-99.06337040000003</v>
       </c>
       <c r="P95">
-        <v>-391.3469552000001</v>
+        <v>-396.2534816000001</v>
       </c>
       <c r="Q95">
-        <v>-359.7469552000001</v>
+        <v>-364.6534816000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6196100828428257</v>
+        <v>0.7152450966499636</v>
       </c>
       <c r="T95">
-        <v>11.18462654675222</v>
+        <v>13.04873097121093</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02847206217644784</v>
+        <v>0.02816916789797499</v>
       </c>
       <c r="W95">
-        <v>0.2290862877387936</v>
+        <v>0.2291577102096575</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1423603108822392</v>
+        <v>0.1408458394898749</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2583229533960758</v>
+        <v>0.2602229533960759</v>
       </c>
       <c r="C96">
-        <v>-1931.874120832451</v>
+        <v>-1962.33026409892</v>
       </c>
       <c r="D96">
-        <v>501.7658791675493</v>
+        <v>497.3197359010802</v>
       </c>
       <c r="E96">
-        <v>2402.84</v>
+        <v>2428.85</v>
       </c>
       <c r="F96">
-        <v>2444.94</v>
+        <v>2470.95</v>
       </c>
       <c r="G96">
         <v>11.3</v>
@@ -9165,37 +9165,37 @@
         <v>81.2</v>
       </c>
       <c r="M96">
-        <v>576.5168520000001</v>
+        <v>582.6500100000001</v>
       </c>
       <c r="N96">
-        <v>-495.3168520000001</v>
+        <v>-501.4500100000001</v>
       </c>
       <c r="O96">
-        <v>-99.06337040000003</v>
+        <v>-100.290002</v>
       </c>
       <c r="P96">
-        <v>-396.2534816000001</v>
+        <v>-401.1600080000001</v>
       </c>
       <c r="Q96">
-        <v>-364.6534816000001</v>
+        <v>-369.560008</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7152450966499636</v>
+        <v>0.8491341159799567</v>
       </c>
       <c r="T96">
-        <v>13.04873097121093</v>
+        <v>15.65847716545312</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02816916789797499</v>
+        <v>0.0278726503411542</v>
       </c>
       <c r="W96">
-        <v>0.2291577102096575</v>
+        <v>0.2292276290495558</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1408458394898749</v>
+        <v>0.139363251705771</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2602229533960759</v>
+        <v>0.2621229533960758</v>
       </c>
       <c r="C97">
-        <v>-1962.33026409892</v>
+        <v>-1992.708304953475</v>
       </c>
       <c r="D97">
-        <v>497.3197359010802</v>
+        <v>492.9516950465253</v>
       </c>
       <c r="E97">
-        <v>2428.85</v>
+        <v>2454.86</v>
       </c>
       <c r="F97">
-        <v>2470.95</v>
+        <v>2496.96</v>
       </c>
       <c r="G97">
         <v>11.3</v>
@@ -9247,37 +9247,37 @@
         <v>81.2</v>
       </c>
       <c r="M97">
-        <v>582.6500100000001</v>
+        <v>588.783168</v>
       </c>
       <c r="N97">
-        <v>-501.4500100000001</v>
+        <v>-507.5831680000001</v>
       </c>
       <c r="O97">
-        <v>-100.290002</v>
+        <v>-101.5166336</v>
       </c>
       <c r="P97">
-        <v>-401.1600080000001</v>
+        <v>-406.0665344</v>
       </c>
       <c r="Q97">
-        <v>-369.560008</v>
+        <v>-374.4665344</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8491341159799567</v>
+        <v>1.049967644974946</v>
       </c>
       <c r="T97">
-        <v>15.65847716545312</v>
+        <v>19.57309645681641</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0278726503411542</v>
+        <v>0.02758231023343384</v>
       </c>
       <c r="W97">
-        <v>0.2292276290495558</v>
+        <v>0.2292960912469563</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.139363251705771</v>
+        <v>0.1379115511671692</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2621229533960758</v>
+        <v>0.2640229533960758</v>
       </c>
       <c r="C98">
-        <v>-1992.708304953475</v>
+        <v>-2023.010283437005</v>
       </c>
       <c r="D98">
-        <v>492.9516950465253</v>
+        <v>488.659716562995</v>
       </c>
       <c r="E98">
-        <v>2454.86</v>
+        <v>2480.87</v>
       </c>
       <c r="F98">
-        <v>2496.96</v>
+        <v>2522.97</v>
       </c>
       <c r="G98">
         <v>11.3</v>
@@ -9329,37 +9329,37 @@
         <v>81.2</v>
       </c>
       <c r="M98">
-        <v>588.783168</v>
+        <v>594.916326</v>
       </c>
       <c r="N98">
-        <v>-507.5831680000001</v>
+        <v>-513.716326</v>
       </c>
       <c r="O98">
-        <v>-101.5166336</v>
+        <v>-102.7432652</v>
       </c>
       <c r="P98">
-        <v>-406.0665344</v>
+        <v>-410.9730608</v>
       </c>
       <c r="Q98">
-        <v>-374.4665344</v>
+        <v>-379.3730608</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.049967644974944</v>
+        <v>1.384690193299925</v>
       </c>
       <c r="T98">
-        <v>19.57309645681636</v>
+        <v>26.09746194242181</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02758231023343384</v>
+        <v>0.02729795651968711</v>
       </c>
       <c r="W98">
-        <v>0.2292960912469563</v>
+        <v>0.2293631418526578</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1379115511671692</v>
+        <v>0.1364897825984356</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2640229533960758</v>
+        <v>0.2659229533960759</v>
       </c>
       <c r="C99">
-        <v>-2023.010283437005</v>
+        <v>-2053.238169155625</v>
       </c>
       <c r="D99">
-        <v>488.659716562995</v>
+        <v>484.441830844375</v>
       </c>
       <c r="E99">
-        <v>2480.87</v>
+        <v>2506.88</v>
       </c>
       <c r="F99">
-        <v>2522.97</v>
+        <v>2548.98</v>
       </c>
       <c r="G99">
         <v>11.3</v>
@@ -9411,37 +9411,37 @@
         <v>81.2</v>
       </c>
       <c r="M99">
-        <v>594.916326</v>
+        <v>601.049484</v>
       </c>
       <c r="N99">
-        <v>-513.716326</v>
+        <v>-519.849484</v>
       </c>
       <c r="O99">
-        <v>-102.7432652</v>
+        <v>-103.9698968</v>
       </c>
       <c r="P99">
-        <v>-410.9730608</v>
+        <v>-415.8795871999999</v>
       </c>
       <c r="Q99">
-        <v>-379.3730608</v>
+        <v>-384.2795871999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.384690193299925</v>
+        <v>2.054135289949887</v>
       </c>
       <c r="T99">
-        <v>26.09746194242181</v>
+        <v>39.14619291363271</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02729795651968711</v>
+        <v>0.02701940594295561</v>
       </c>
       <c r="W99">
-        <v>0.2293631418526578</v>
+        <v>0.2294288240786511</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1364897825984356</v>
+        <v>0.1350970297147781</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2659229533960759</v>
+        <v>0.2678229533960758</v>
       </c>
       <c r="C100">
-        <v>-2053.238169155625</v>
+        <v>-2083.393864294461</v>
       </c>
       <c r="D100">
-        <v>484.441830844375</v>
+        <v>480.2961357055385</v>
       </c>
       <c r="E100">
-        <v>2506.88</v>
+        <v>2532.89</v>
       </c>
       <c r="F100">
-        <v>2548.98</v>
+        <v>2574.99</v>
       </c>
       <c r="G100">
         <v>11.3</v>
@@ -9493,37 +9493,37 @@
         <v>81.2</v>
       </c>
       <c r="M100">
-        <v>601.049484</v>
+        <v>607.182642</v>
       </c>
       <c r="N100">
-        <v>-519.849484</v>
+        <v>-525.9826419999999</v>
       </c>
       <c r="O100">
-        <v>-103.9698968</v>
+        <v>-105.1965284</v>
       </c>
       <c r="P100">
-        <v>-415.8795871999999</v>
+        <v>-420.7861136</v>
       </c>
       <c r="Q100">
-        <v>-384.2795871999999</v>
+        <v>-389.1861136</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.054135289949887</v>
+        <v>4.062470579899774</v>
       </c>
       <c r="T100">
-        <v>39.14619291363271</v>
+        <v>78.29238582726542</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02701940594295561</v>
+        <v>0.02674648265060252</v>
       </c>
       <c r="W100">
-        <v>0.2294288240786511</v>
+        <v>0.2294931793909879</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1350970297147781</v>
+        <v>0.1337324132530127</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2678229533960758</v>
-      </c>
-      <c r="C101">
-        <v>-2083.393864294461</v>
-      </c>
-      <c r="D101">
-        <v>480.2961357055385</v>
-      </c>
-      <c r="E101">
-        <v>2532.89</v>
-      </c>
-      <c r="F101">
-        <v>2574.99</v>
-      </c>
-      <c r="G101">
-        <v>11.3</v>
-      </c>
-      <c r="H101">
-        <v>2558.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>112.8</v>
-      </c>
-      <c r="K101">
-        <v>31.59999999999999</v>
-      </c>
-      <c r="L101">
-        <v>81.2</v>
-      </c>
-      <c r="M101">
-        <v>607.182642</v>
-      </c>
-      <c r="N101">
-        <v>-525.9826419999999</v>
-      </c>
-      <c r="O101">
-        <v>-105.1965284</v>
-      </c>
-      <c r="P101">
-        <v>-420.7861136</v>
-      </c>
-      <c r="Q101">
-        <v>-389.1861136</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.062470579899774</v>
-      </c>
-      <c r="T101">
-        <v>78.29238582726542</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02674648265060252</v>
-      </c>
-      <c r="W101">
-        <v>0.2294931793909879</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1337324132530127</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
